--- a/research/traditional_assets/database/data/morocco/morocco_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cbse_ris" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.231</v>
+        <v>-0.12</v>
       </c>
       <c r="G2">
-        <v>0.03176470588235294</v>
+        <v>0.09002695417789756</v>
       </c>
       <c r="H2">
-        <v>0.03176470588235294</v>
+        <v>0.09002695417789756</v>
       </c>
       <c r="I2">
-        <v>-0.4729411764705883</v>
+        <v>0.0866576819407008</v>
       </c>
       <c r="J2">
-        <v>-0.4729411764705883</v>
+        <v>0.0866576819407008</v>
       </c>
       <c r="K2">
-        <v>-40.5</v>
+        <v>-1.42</v>
       </c>
       <c r="L2">
-        <v>-0.9529411764705882</v>
+        <v>-0.01913746630727763</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>28.8</v>
+        <v>42.2</v>
       </c>
       <c r="V2">
-        <v>0.1694117647058823</v>
+        <v>0.2699936020473448</v>
       </c>
       <c r="W2">
-        <v>-0.2662721893491125</v>
+        <v>-0.01142397425583266</v>
       </c>
       <c r="X2">
-        <v>0.1304243710878453</v>
+        <v>0.1874835758510827</v>
       </c>
       <c r="Y2">
-        <v>-0.3966965604369578</v>
+        <v>-0.1989075501069154</v>
       </c>
       <c r="Z2">
-        <v>0.1573491299518697</v>
+        <v>0.2655690765926987</v>
       </c>
       <c r="AA2">
-        <v>-0.07441688263606074</v>
+        <v>0.02301360057265569</v>
       </c>
       <c r="AB2">
-        <v>0.07473326850384276</v>
+        <v>0.1104093898989866</v>
       </c>
       <c r="AC2">
-        <v>-0.1491501511399035</v>
+        <v>-0.08739578932633095</v>
       </c>
       <c r="AD2">
-        <v>215.4</v>
+        <v>212.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>215.4</v>
+        <v>212.7</v>
       </c>
       <c r="AG2">
-        <v>186.6</v>
+        <v>170.5</v>
       </c>
       <c r="AH2">
-        <v>0.5588998443175922</v>
+        <v>0.5764227642276423</v>
       </c>
       <c r="AI2">
-        <v>0.6164854035489411</v>
+        <v>0.6453276699029126</v>
       </c>
       <c r="AJ2">
-        <v>0.5232753785754346</v>
+        <v>0.5217258261933905</v>
       </c>
       <c r="AK2">
-        <v>0.5820336868371803</v>
+        <v>0.593249826026444</v>
       </c>
       <c r="AL2">
-        <v>12.7</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AM2">
-        <v>12.7</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AN2">
-        <v>-53.31683168316832</v>
+        <v>10.3252427184466</v>
       </c>
       <c r="AO2">
-        <v>-1.582677165354331</v>
+        <v>0.6789862724392819</v>
       </c>
       <c r="AP2">
-        <v>-46.18811881188119</v>
+        <v>8.276699029126213</v>
       </c>
       <c r="AQ2">
-        <v>-1.582677165354331</v>
+        <v>0.6789862724392819</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.231</v>
+        <v>-0.12</v>
       </c>
       <c r="G3">
-        <v>0.03176470588235294</v>
+        <v>0.09002695417789756</v>
       </c>
       <c r="H3">
-        <v>0.03176470588235294</v>
+        <v>0.09002695417789756</v>
       </c>
       <c r="I3">
-        <v>-0.4729411764705883</v>
+        <v>0.0866576819407008</v>
       </c>
       <c r="J3">
-        <v>-0.4729411764705883</v>
+        <v>0.0866576819407008</v>
       </c>
       <c r="K3">
-        <v>-40.5</v>
+        <v>-1.42</v>
       </c>
       <c r="L3">
-        <v>-0.9529411764705882</v>
+        <v>-0.01913746630727763</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>28.8</v>
+        <v>42.2</v>
       </c>
       <c r="V3">
-        <v>0.1694117647058823</v>
+        <v>0.2699936020473448</v>
       </c>
       <c r="W3">
-        <v>-0.2662721893491125</v>
+        <v>-0.01142397425583266</v>
       </c>
       <c r="X3">
-        <v>0.1304243710878453</v>
+        <v>0.1874835758510827</v>
       </c>
       <c r="Y3">
-        <v>-0.3966965604369578</v>
+        <v>-0.1989075501069154</v>
       </c>
       <c r="Z3">
-        <v>0.1573491299518697</v>
+        <v>0.2655690765926987</v>
       </c>
       <c r="AA3">
-        <v>-0.07441688263606074</v>
+        <v>0.02301360057265569</v>
       </c>
       <c r="AB3">
-        <v>0.07473326850384276</v>
+        <v>0.1104093898989866</v>
       </c>
       <c r="AC3">
-        <v>-0.1491501511399035</v>
+        <v>-0.08739578932633095</v>
       </c>
       <c r="AD3">
-        <v>215.4</v>
+        <v>212.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>215.4</v>
+        <v>212.7</v>
       </c>
       <c r="AG3">
-        <v>186.6</v>
+        <v>170.5</v>
       </c>
       <c r="AH3">
-        <v>0.5588998443175922</v>
+        <v>0.5764227642276423</v>
       </c>
       <c r="AI3">
-        <v>0.6164854035489411</v>
+        <v>0.6453276699029126</v>
       </c>
       <c r="AJ3">
-        <v>0.5232753785754346</v>
+        <v>0.5217258261933905</v>
       </c>
       <c r="AK3">
-        <v>0.5820336868371803</v>
+        <v>0.593249826026444</v>
       </c>
       <c r="AL3">
-        <v>12.7</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AM3">
-        <v>12.7</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AN3">
-        <v>-53.31683168316832</v>
+        <v>10.3252427184466</v>
       </c>
       <c r="AO3">
-        <v>-1.582677165354331</v>
+        <v>0.6789862724392819</v>
       </c>
       <c r="AP3">
-        <v>-46.18811881188119</v>
+        <v>8.276699029126213</v>
       </c>
       <c r="AQ3">
-        <v>-1.582677165354331</v>
+        <v>0.6789862724392819</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Risma (CBSE:RIS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CBSE:RIS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.576422764227642</v>
+      </c>
+      <c r="F2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G2">
+        <v>156.3</v>
+      </c>
+      <c r="H2">
+        <v>328.571875944324</v>
+      </c>
+      <c r="I2">
+        <v>326.8</v>
+      </c>
+      <c r="J2">
+        <v>312.201875944324</v>
+      </c>
+      <c r="K2">
+        <v>212.7</v>
+      </c>
+      <c r="L2">
+        <v>25.83</v>
+      </c>
+      <c r="M2">
+        <v>0.110409389898987</v>
+      </c>
+      <c r="N2">
+        <v>0.113757745043025</v>
+      </c>
+      <c r="O2">
+        <v>0.0537723646788991</v>
+      </c>
+      <c r="P2">
+        <v>0.03795</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.187483575851083</v>
+      </c>
+      <c r="T2">
+        <v>0.119463704347339</v>
+      </c>
+      <c r="U2">
+        <v>1.45268043148697</v>
+      </c>
+      <c r="V2">
+        <v>0.788107120547008</v>
+      </c>
+      <c r="W2">
+        <v>4.575370429028967</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>156.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.1023511934410034</v>
+      </c>
+      <c r="AC2">
+        <v>0.0779309633027523</v>
+      </c>
+      <c r="AD2">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>20.6</v>
+      </c>
+      <c r="AH2">
+        <v>14.1</v>
+      </c>
+      <c r="AI2">
+        <v>11.2</v>
+      </c>
+      <c r="AJ2">
+        <v>212.7</v>
+      </c>
+      <c r="AK2">
+        <v>212.7</v>
+      </c>
+      <c r="AL2">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AM2">
+        <v>212.7</v>
+      </c>
+      <c r="AN2">
+        <v>42.2</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1154812276837629</v>
+      </c>
+      <c r="C2">
+        <v>347.3848454422197</v>
+      </c>
+      <c r="D2">
+        <v>305.1848454422197</v>
+      </c>
+      <c r="E2">
+        <v>-212.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>42.2</v>
+      </c>
+      <c r="H2">
+        <v>156.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>20.6</v>
+      </c>
+      <c r="K2">
+        <v>14.1</v>
+      </c>
+      <c r="L2">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="O2">
+        <v>2.015000000000001</v>
+      </c>
+      <c r="P2">
+        <v>4.485000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>18.585</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1154812276837629</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.031533</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1151708458779432</v>
+      </c>
+      <c r="C3">
+        <v>344.935159365003</v>
+      </c>
+      <c r="D3">
+        <v>306.425159365003</v>
+      </c>
+      <c r="E3">
+        <v>-209.01</v>
+      </c>
+      <c r="F3">
+        <v>3.69</v>
+      </c>
+      <c r="G3">
+        <v>42.2</v>
+      </c>
+      <c r="H3">
+        <v>156.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>20.6</v>
+      </c>
+      <c r="K3">
+        <v>14.1</v>
+      </c>
+      <c r="L3">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M3">
+        <v>0.168633</v>
+      </c>
+      <c r="N3">
+        <v>6.331367000000002</v>
+      </c>
+      <c r="O3">
+        <v>1.962723770000001</v>
+      </c>
+      <c r="P3">
+        <v>4.368643230000001</v>
+      </c>
+      <c r="Q3">
+        <v>18.46864323</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1160156726039831</v>
+      </c>
+      <c r="T3">
+        <v>0.754418878842788</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.031533</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>38.54524322048473</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1148604640721236</v>
+      </c>
+      <c r="C4">
+        <v>342.4955960468263</v>
+      </c>
+      <c r="D4">
+        <v>307.6755960468263</v>
+      </c>
+      <c r="E4">
+        <v>-205.32</v>
+      </c>
+      <c r="F4">
+        <v>7.38</v>
+      </c>
+      <c r="G4">
+        <v>42.2</v>
+      </c>
+      <c r="H4">
+        <v>156.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>20.6</v>
+      </c>
+      <c r="K4">
+        <v>14.1</v>
+      </c>
+      <c r="L4">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M4">
+        <v>0.337266</v>
+      </c>
+      <c r="N4">
+        <v>6.162734000000002</v>
+      </c>
+      <c r="O4">
+        <v>1.910447540000001</v>
+      </c>
+      <c r="P4">
+        <v>4.252286460000001</v>
+      </c>
+      <c r="Q4">
+        <v>18.35228646</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1165610245633914</v>
+      </c>
+      <c r="T4">
+        <v>0.7597471211531494</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.031533</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>19.27262161024237</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1145832022663039</v>
+      </c>
+      <c r="C5">
+        <v>339.9312635933996</v>
+      </c>
+      <c r="D5">
+        <v>308.8012635933997</v>
+      </c>
+      <c r="E5">
+        <v>-201.63</v>
+      </c>
+      <c r="F5">
+        <v>11.07</v>
+      </c>
+      <c r="G5">
+        <v>42.2</v>
+      </c>
+      <c r="H5">
+        <v>156.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>20.6</v>
+      </c>
+      <c r="K5">
+        <v>14.1</v>
+      </c>
+      <c r="L5">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M5">
+        <v>0.523611</v>
+      </c>
+      <c r="N5">
+        <v>5.976389000000002</v>
+      </c>
+      <c r="O5">
+        <v>1.852680590000001</v>
+      </c>
+      <c r="P5">
+        <v>4.123708410000001</v>
+      </c>
+      <c r="Q5">
+        <v>18.22370841</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1171176208930968</v>
+      </c>
+      <c r="T5">
+        <v>0.7651852241297037</v>
+      </c>
+      <c r="U5">
+        <v>0.0473</v>
+      </c>
+      <c r="V5">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.032637</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>12.41379573767549</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1143887404604843</v>
+      </c>
+      <c r="C6">
+        <v>337.0356947612157</v>
+      </c>
+      <c r="D6">
+        <v>309.5956947612157</v>
+      </c>
+      <c r="E6">
+        <v>-197.94</v>
+      </c>
+      <c r="F6">
+        <v>14.76</v>
+      </c>
+      <c r="G6">
+        <v>42.2</v>
+      </c>
+      <c r="H6">
+        <v>156.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>20.6</v>
+      </c>
+      <c r="K6">
+        <v>14.1</v>
+      </c>
+      <c r="L6">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M6">
+        <v>0.754236</v>
+      </c>
+      <c r="N6">
+        <v>5.745764000000002</v>
+      </c>
+      <c r="O6">
+        <v>1.781186840000001</v>
+      </c>
+      <c r="P6">
+        <v>3.964577160000001</v>
+      </c>
+      <c r="Q6">
+        <v>18.06457716</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1176858129796711</v>
+      </c>
+      <c r="T6">
+        <v>0.7707366209182697</v>
+      </c>
+      <c r="U6">
+        <v>0.0511</v>
+      </c>
+      <c r="V6">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.035259</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>8.61799224645867</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1141811686546646</v>
+      </c>
+      <c r="C7">
+        <v>334.198206583233</v>
+      </c>
+      <c r="D7">
+        <v>310.448206583233</v>
+      </c>
+      <c r="E7">
+        <v>-194.25</v>
+      </c>
+      <c r="F7">
+        <v>18.45</v>
+      </c>
+      <c r="G7">
+        <v>42.2</v>
+      </c>
+      <c r="H7">
+        <v>156.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>20.6</v>
+      </c>
+      <c r="K7">
+        <v>14.1</v>
+      </c>
+      <c r="L7">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M7">
+        <v>0.9778500000000001</v>
+      </c>
+      <c r="N7">
+        <v>5.522150000000002</v>
+      </c>
+      <c r="O7">
+        <v>1.711866500000001</v>
+      </c>
+      <c r="P7">
+        <v>3.810283500000001</v>
+      </c>
+      <c r="Q7">
+        <v>17.9102835</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1182659670049101</v>
+      </c>
+      <c r="T7">
+        <v>0.7764048892181739</v>
+      </c>
+      <c r="U7">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.03657</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>6.647236283683593</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1140039568488449</v>
+      </c>
+      <c r="C8">
+        <v>331.2397516987735</v>
+      </c>
+      <c r="D8">
+        <v>311.1797516987735</v>
+      </c>
+      <c r="E8">
+        <v>-190.56</v>
+      </c>
+      <c r="F8">
+        <v>22.14</v>
+      </c>
+      <c r="G8">
+        <v>42.2</v>
+      </c>
+      <c r="H8">
+        <v>156.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>20.6</v>
+      </c>
+      <c r="K8">
+        <v>14.1</v>
+      </c>
+      <c r="L8">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M8">
+        <v>1.2177</v>
+      </c>
+      <c r="N8">
+        <v>5.282300000000002</v>
+      </c>
+      <c r="O8">
+        <v>1.637513000000001</v>
+      </c>
+      <c r="P8">
+        <v>3.644787000000001</v>
+      </c>
+      <c r="Q8">
+        <v>17.744787</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1188584647328137</v>
+      </c>
+      <c r="T8">
+        <v>0.7821937589712674</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.03795</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>5.337932167200462</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1137577450430253</v>
+      </c>
+      <c r="C9">
+        <v>328.571875944324</v>
+      </c>
+      <c r="D9">
+        <v>312.201875944324</v>
+      </c>
+      <c r="E9">
+        <v>-186.87</v>
+      </c>
+      <c r="F9">
+        <v>25.83</v>
+      </c>
+      <c r="G9">
+        <v>42.2</v>
+      </c>
+      <c r="H9">
+        <v>156.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>20.6</v>
+      </c>
+      <c r="K9">
+        <v>14.1</v>
+      </c>
+      <c r="L9">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M9">
+        <v>1.42065</v>
+      </c>
+      <c r="N9">
+        <v>5.079350000000002</v>
+      </c>
+      <c r="O9">
+        <v>1.574598500000001</v>
+      </c>
+      <c r="P9">
+        <v>3.504751500000001</v>
+      </c>
+      <c r="Q9">
+        <v>17.6047515</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.119463704347339</v>
+      </c>
+      <c r="T9">
+        <v>0.7881071205470082</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.03795</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>4.575370429028967</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1143450532372056</v>
+      </c>
+      <c r="C10">
+        <v>322.4547319802468</v>
+      </c>
+      <c r="D10">
+        <v>309.7747319802468</v>
+      </c>
+      <c r="E10">
+        <v>-183.18</v>
+      </c>
+      <c r="F10">
+        <v>29.52</v>
+      </c>
+      <c r="G10">
+        <v>42.2</v>
+      </c>
+      <c r="H10">
+        <v>156.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20.6</v>
+      </c>
+      <c r="K10">
+        <v>14.1</v>
+      </c>
+      <c r="L10">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M10">
+        <v>2.069352</v>
+      </c>
+      <c r="N10">
+        <v>4.430648000000001</v>
+      </c>
+      <c r="O10">
+        <v>1.373500880000001</v>
+      </c>
+      <c r="P10">
+        <v>3.057147120000001</v>
+      </c>
+      <c r="Q10">
+        <v>17.15714712</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1200821013447887</v>
+      </c>
+      <c r="T10">
+        <v>0.7941490334613519</v>
+      </c>
+      <c r="U10">
+        <v>0.0701</v>
+      </c>
+      <c r="V10">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.048369</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>3.141079912938931</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1155257614313859</v>
+      </c>
+      <c r="C11">
+        <v>313.9977077425508</v>
+      </c>
+      <c r="D11">
+        <v>305.0077077425508</v>
+      </c>
+      <c r="E11">
+        <v>-179.49</v>
+      </c>
+      <c r="F11">
+        <v>33.21</v>
+      </c>
+      <c r="G11">
+        <v>42.2</v>
+      </c>
+      <c r="H11">
+        <v>156.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>20.6</v>
+      </c>
+      <c r="K11">
+        <v>14.1</v>
+      </c>
+      <c r="L11">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M11">
+        <v>3.035394000000001</v>
+      </c>
+      <c r="N11">
+        <v>3.464606000000001</v>
+      </c>
+      <c r="O11">
+        <v>1.074027860000001</v>
+      </c>
+      <c r="P11">
+        <v>2.390578140000001</v>
+      </c>
+      <c r="Q11">
+        <v>16.49057814</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1207140894850395</v>
+      </c>
+      <c r="T11">
+        <v>0.8003237356705165</v>
+      </c>
+      <c r="U11">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.063066</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>2.14140240113804</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1169866096255663</v>
+      </c>
+      <c r="C12">
+        <v>304.608906359544</v>
+      </c>
+      <c r="D12">
+        <v>299.308906359544</v>
+      </c>
+      <c r="E12">
+        <v>-175.8</v>
+      </c>
+      <c r="F12">
+        <v>36.9</v>
+      </c>
+      <c r="G12">
+        <v>42.2</v>
+      </c>
+      <c r="H12">
+        <v>156.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>20.6</v>
+      </c>
+      <c r="K12">
+        <v>14.1</v>
+      </c>
+      <c r="L12">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M12">
+        <v>4.15125</v>
+      </c>
+      <c r="N12">
+        <v>2.348750000000002</v>
+      </c>
+      <c r="O12">
+        <v>0.7281125000000006</v>
+      </c>
+      <c r="P12">
+        <v>1.620637500000001</v>
+      </c>
+      <c r="Q12">
+        <v>15.7206375</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1213601218061847</v>
+      </c>
+      <c r="T12">
+        <v>0.8066356534843292</v>
+      </c>
+      <c r="U12">
+        <v>0.1125</v>
+      </c>
+      <c r="V12">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.077625</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>1.565793435712135</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1252486475259199</v>
+      </c>
+      <c r="C13">
+        <v>272.313467188104</v>
+      </c>
+      <c r="D13">
+        <v>270.703467188104</v>
+      </c>
+      <c r="E13">
+        <v>-172.11</v>
+      </c>
+      <c r="F13">
+        <v>40.59</v>
+      </c>
+      <c r="G13">
+        <v>42.2</v>
+      </c>
+      <c r="H13">
+        <v>156.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>20.6</v>
+      </c>
+      <c r="K13">
+        <v>14.1</v>
+      </c>
+      <c r="L13">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M13">
+        <v>7.979994</v>
+      </c>
+      <c r="N13">
+        <v>-1.479993999999999</v>
+      </c>
+      <c r="O13">
+        <v>-0.4587981399999997</v>
+      </c>
+      <c r="P13">
+        <v>-1.021195859999999</v>
+      </c>
+      <c r="Q13">
+        <v>13.07880414</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1225655641943438</v>
+      </c>
+      <c r="T13">
+        <v>0.8184131652810424</v>
+      </c>
+      <c r="U13">
+        <v>0.1966</v>
+      </c>
+      <c r="V13">
+        <v>0.2525064555186384</v>
+      </c>
+      <c r="W13">
+        <v>0.1469572308450357</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.8145369532859299</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1290619939219616</v>
+      </c>
+      <c r="C14">
+        <v>257.1869140371707</v>
+      </c>
+      <c r="D14">
+        <v>259.2669140371707</v>
+      </c>
+      <c r="E14">
+        <v>-168.42</v>
+      </c>
+      <c r="F14">
+        <v>44.28</v>
+      </c>
+      <c r="G14">
+        <v>42.2</v>
+      </c>
+      <c r="H14">
+        <v>156.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>20.6</v>
+      </c>
+      <c r="K14">
+        <v>14.1</v>
+      </c>
+      <c r="L14">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M14">
+        <v>9.467064000000001</v>
+      </c>
+      <c r="N14">
+        <v>-2.967063999999999</v>
+      </c>
+      <c r="O14">
+        <v>-0.9197898399999997</v>
+      </c>
+      <c r="P14">
+        <v>-2.047274159999999</v>
+      </c>
+      <c r="Q14">
+        <v>12.05272584</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1237121574193269</v>
+      </c>
+      <c r="T14">
+        <v>0.8296157041712603</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.2128431792581101</v>
+      </c>
+      <c r="W14">
+        <v>0.1682941282746161</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.6865909008326131</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1308119939219616</v>
+      </c>
+      <c r="C15">
+        <v>248.5658492897872</v>
+      </c>
+      <c r="D15">
+        <v>254.3358492897872</v>
+      </c>
+      <c r="E15">
+        <v>-164.73</v>
+      </c>
+      <c r="F15">
+        <v>47.97</v>
+      </c>
+      <c r="G15">
+        <v>42.2</v>
+      </c>
+      <c r="H15">
+        <v>156.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>20.6</v>
+      </c>
+      <c r="K15">
+        <v>14.1</v>
+      </c>
+      <c r="L15">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M15">
+        <v>10.255986</v>
+      </c>
+      <c r="N15">
+        <v>-3.755985999999998</v>
+      </c>
+      <c r="O15">
+        <v>-1.16435566</v>
+      </c>
+      <c r="P15">
+        <v>-2.591630339999999</v>
+      </c>
+      <c r="Q15">
+        <v>11.50836966</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1246881592287444</v>
+      </c>
+      <c r="T15">
+        <v>0.839151516862884</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1964706270074862</v>
+      </c>
+      <c r="W15">
+        <v>0.1717945799457994</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.6337762161531814</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1325619939219616</v>
+      </c>
+      <c r="C16">
+        <v>240.1288540773392</v>
+      </c>
+      <c r="D16">
+        <v>249.5888540773392</v>
+      </c>
+      <c r="E16">
+        <v>-161.04</v>
+      </c>
+      <c r="F16">
+        <v>51.66</v>
+      </c>
+      <c r="G16">
+        <v>42.2</v>
+      </c>
+      <c r="H16">
+        <v>156.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>20.6</v>
+      </c>
+      <c r="K16">
+        <v>14.1</v>
+      </c>
+      <c r="L16">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M16">
+        <v>11.044908</v>
+      </c>
+      <c r="N16">
+        <v>-4.544907999999998</v>
+      </c>
+      <c r="O16">
+        <v>-1.40892148</v>
+      </c>
+      <c r="P16">
+        <v>-3.135986519999998</v>
+      </c>
+      <c r="Q16">
+        <v>10.96401348</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1256868587546601</v>
+      </c>
+      <c r="T16">
+        <v>0.8489090926403594</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1824370107926658</v>
+      </c>
+      <c r="W16">
+        <v>0.174794967092528</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.5885064864279541</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1343119939219616</v>
+      </c>
+      <c r="C17">
+        <v>231.8658106646742</v>
+      </c>
+      <c r="D17">
+        <v>245.0158106646741</v>
+      </c>
+      <c r="E17">
+        <v>-157.35</v>
+      </c>
+      <c r="F17">
+        <v>55.35</v>
+      </c>
+      <c r="G17">
+        <v>42.2</v>
+      </c>
+      <c r="H17">
+        <v>156.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>20.6</v>
+      </c>
+      <c r="K17">
+        <v>14.1</v>
+      </c>
+      <c r="L17">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M17">
+        <v>11.83383</v>
+      </c>
+      <c r="N17">
+        <v>-5.333829999999997</v>
+      </c>
+      <c r="O17">
+        <v>-1.653487299999999</v>
+      </c>
+      <c r="P17">
+        <v>-3.680342699999998</v>
+      </c>
+      <c r="Q17">
+        <v>10.4196573</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1267090570929502</v>
+      </c>
+      <c r="T17">
+        <v>0.8588962584361283</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1702745434064881</v>
+      </c>
+      <c r="W17">
+        <v>0.1773953026196928</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.5492727206660906</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1360619939219616</v>
+      </c>
+      <c r="C18">
+        <v>223.7673294956863</v>
+      </c>
+      <c r="D18">
+        <v>240.6073294956862</v>
+      </c>
+      <c r="E18">
+        <v>-153.66</v>
+      </c>
+      <c r="F18">
+        <v>59.04</v>
+      </c>
+      <c r="G18">
+        <v>42.2</v>
+      </c>
+      <c r="H18">
+        <v>156.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>20.6</v>
+      </c>
+      <c r="K18">
+        <v>14.1</v>
+      </c>
+      <c r="L18">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M18">
+        <v>12.622752</v>
+      </c>
+      <c r="N18">
+        <v>-6.122751999999997</v>
+      </c>
+      <c r="O18">
+        <v>-1.898053119999999</v>
+      </c>
+      <c r="P18">
+        <v>-4.224698879999997</v>
+      </c>
+      <c r="Q18">
+        <v>9.875301120000003</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1277555934869139</v>
+      </c>
+      <c r="T18">
+        <v>0.8691212138937013</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1596323844435826</v>
+      </c>
+      <c r="W18">
+        <v>0.179670596205962</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5149431756244599</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1422670325688162</v>
+      </c>
+      <c r="C19">
+        <v>205.6478272554994</v>
+      </c>
+      <c r="D19">
+        <v>226.1778272554994</v>
+      </c>
+      <c r="E19">
+        <v>-149.97</v>
+      </c>
+      <c r="F19">
+        <v>62.73</v>
+      </c>
+      <c r="G19">
+        <v>42.2</v>
+      </c>
+      <c r="H19">
+        <v>156.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>20.6</v>
+      </c>
+      <c r="K19">
+        <v>14.1</v>
+      </c>
+      <c r="L19">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M19">
+        <v>14.979924</v>
+      </c>
+      <c r="N19">
+        <v>-8.479924</v>
+      </c>
+      <c r="O19">
+        <v>-2.628776440000001</v>
+      </c>
+      <c r="P19">
+        <v>-5.851147559999999</v>
+      </c>
+      <c r="Q19">
+        <v>8.24885244</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1290743821395931</v>
+      </c>
+      <c r="T19">
+        <v>0.8820061506330016</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.1345133660224178</v>
+      </c>
+      <c r="W19">
+        <v>0.2066782081938466</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.4339140839432831</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1442670325688162</v>
+      </c>
+      <c r="C20">
+        <v>197.6687556518602</v>
+      </c>
+      <c r="D20">
+        <v>221.8887556518602</v>
+      </c>
+      <c r="E20">
+        <v>-146.28</v>
+      </c>
+      <c r="F20">
+        <v>66.42</v>
+      </c>
+      <c r="G20">
+        <v>42.2</v>
+      </c>
+      <c r="H20">
+        <v>156.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>20.6</v>
+      </c>
+      <c r="K20">
+        <v>14.1</v>
+      </c>
+      <c r="L20">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M20">
+        <v>15.861096</v>
+      </c>
+      <c r="N20">
+        <v>-9.361096</v>
+      </c>
+      <c r="O20">
+        <v>-2.90193976</v>
+      </c>
+      <c r="P20">
+        <v>-6.45915624</v>
+      </c>
+      <c r="Q20">
+        <v>7.64084376</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1301752892388564</v>
+      </c>
+      <c r="T20">
+        <v>0.8927623232016967</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.1270404012433946</v>
+      </c>
+      <c r="W20">
+        <v>0.2084627521830774</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.409807745946434</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1462670325688162</v>
+      </c>
+      <c r="C21">
+        <v>189.8493263683304</v>
+      </c>
+      <c r="D21">
+        <v>217.7593263683304</v>
+      </c>
+      <c r="E21">
+        <v>-142.59</v>
+      </c>
+      <c r="F21">
+        <v>70.11</v>
+      </c>
+      <c r="G21">
+        <v>42.2</v>
+      </c>
+      <c r="H21">
+        <v>156.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>20.6</v>
+      </c>
+      <c r="K21">
+        <v>14.1</v>
+      </c>
+      <c r="L21">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M21">
+        <v>16.742268</v>
+      </c>
+      <c r="N21">
+        <v>-10.242268</v>
+      </c>
+      <c r="O21">
+        <v>-3.17510308</v>
+      </c>
+      <c r="P21">
+        <v>-7.067164919999998</v>
+      </c>
+      <c r="Q21">
+        <v>7.032835080000002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1313033792294596</v>
+      </c>
+      <c r="T21">
+        <v>0.9037840802782608</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.1203540643358475</v>
+      </c>
+      <c r="W21">
+        <v>0.2100594494365996</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3882389172124112</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1482670325688162</v>
+      </c>
+      <c r="C22">
+        <v>182.1807892460888</v>
+      </c>
+      <c r="D22">
+        <v>213.7807892460888</v>
+      </c>
+      <c r="E22">
+        <v>-138.9</v>
+      </c>
+      <c r="F22">
+        <v>73.8</v>
+      </c>
+      <c r="G22">
+        <v>42.2</v>
+      </c>
+      <c r="H22">
+        <v>156.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>20.6</v>
+      </c>
+      <c r="K22">
+        <v>14.1</v>
+      </c>
+      <c r="L22">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M22">
+        <v>17.62344</v>
+      </c>
+      <c r="N22">
+        <v>-11.12344</v>
+      </c>
+      <c r="O22">
+        <v>-3.4482664</v>
+      </c>
+      <c r="P22">
+        <v>-7.675173599999997</v>
+      </c>
+      <c r="Q22">
+        <v>6.424826400000002</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1324596714698278</v>
+      </c>
+      <c r="T22">
+        <v>0.9150813812817391</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.1143363611190551</v>
+      </c>
+      <c r="W22">
+        <v>0.2114964769647696</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3688269713517907</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1502670325688162</v>
+      </c>
+      <c r="C23">
+        <v>174.6550221260821</v>
+      </c>
+      <c r="D23">
+        <v>209.9450221260821</v>
+      </c>
+      <c r="E23">
+        <v>-135.21</v>
+      </c>
+      <c r="F23">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="G23">
+        <v>42.2</v>
+      </c>
+      <c r="H23">
+        <v>156.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>20.6</v>
+      </c>
+      <c r="K23">
+        <v>14.1</v>
+      </c>
+      <c r="L23">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M23">
+        <v>18.504612</v>
+      </c>
+      <c r="N23">
+        <v>-12.004612</v>
+      </c>
+      <c r="O23">
+        <v>-3.721429719999999</v>
+      </c>
+      <c r="P23">
+        <v>-8.283182279999997</v>
+      </c>
+      <c r="Q23">
+        <v>5.816817720000003</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1336452369314712</v>
+      </c>
+      <c r="T23">
+        <v>0.9266646899055586</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.1088917724943382</v>
+      </c>
+      <c r="W23">
+        <v>0.2127966447283521</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3512637822398007</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1522670325688162</v>
+      </c>
+      <c r="C24">
+        <v>167.2644755025727</v>
+      </c>
+      <c r="D24">
+        <v>206.2444755025727</v>
+      </c>
+      <c r="E24">
+        <v>-131.52</v>
+      </c>
+      <c r="F24">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="G24">
+        <v>42.2</v>
+      </c>
+      <c r="H24">
+        <v>156.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>20.6</v>
+      </c>
+      <c r="K24">
+        <v>14.1</v>
+      </c>
+      <c r="L24">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M24">
+        <v>19.385784</v>
+      </c>
+      <c r="N24">
+        <v>-12.885784</v>
+      </c>
+      <c r="O24">
+        <v>-3.99459304</v>
+      </c>
+      <c r="P24">
+        <v>-8.891190959999999</v>
+      </c>
+      <c r="Q24">
+        <v>5.20880904</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1348612015075157</v>
+      </c>
+      <c r="T24">
+        <v>0.9385450064428094</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.1039421464718683</v>
+      </c>
+      <c r="W24">
+        <v>0.2139786154225179</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3352972466834461</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1542670325688162</v>
+      </c>
+      <c r="C25">
+        <v>160.0021229286092</v>
+      </c>
+      <c r="D25">
+        <v>202.6721229286092</v>
+      </c>
+      <c r="E25">
+        <v>-127.83</v>
+      </c>
+      <c r="F25">
+        <v>84.87</v>
+      </c>
+      <c r="G25">
+        <v>42.2</v>
+      </c>
+      <c r="H25">
+        <v>156.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>20.6</v>
+      </c>
+      <c r="K25">
+        <v>14.1</v>
+      </c>
+      <c r="L25">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M25">
+        <v>20.266956</v>
+      </c>
+      <c r="N25">
+        <v>-13.766956</v>
+      </c>
+      <c r="O25">
+        <v>-4.26775636</v>
+      </c>
+      <c r="P25">
+        <v>-9.499199639999999</v>
+      </c>
+      <c r="Q25">
+        <v>4.600800360000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1361087495790419</v>
+      </c>
+      <c r="T25">
+        <v>0.9507339026303783</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.09942292271222185</v>
+      </c>
+      <c r="W25">
+        <v>0.2150578060563214</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3207191055232962</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1562670325688162</v>
+      </c>
+      <c r="C26">
+        <v>152.8614164878915</v>
+      </c>
+      <c r="D26">
+        <v>199.2214164878914</v>
+      </c>
+      <c r="E26">
+        <v>-124.14</v>
+      </c>
+      <c r="F26">
+        <v>88.56</v>
+      </c>
+      <c r="G26">
+        <v>42.2</v>
+      </c>
+      <c r="H26">
+        <v>156.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>20.6</v>
+      </c>
+      <c r="K26">
+        <v>14.1</v>
+      </c>
+      <c r="L26">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M26">
+        <v>21.148128</v>
+      </c>
+      <c r="N26">
+        <v>-14.648128</v>
+      </c>
+      <c r="O26">
+        <v>-4.540919680000001</v>
+      </c>
+      <c r="P26">
+        <v>-10.10720832</v>
+      </c>
+      <c r="Q26">
+        <v>3.992791679999998</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1373891278629767</v>
+      </c>
+      <c r="T26">
+        <v>0.963243559243936</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.09528030093254591</v>
+      </c>
+      <c r="W26">
+        <v>0.216047064137308</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3073558094598255</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1582670325688162</v>
+      </c>
+      <c r="C27">
+        <v>145.8362467393144</v>
+      </c>
+      <c r="D27">
+        <v>195.8862467393144</v>
+      </c>
+      <c r="E27">
+        <v>-120.45</v>
+      </c>
+      <c r="F27">
+        <v>92.25</v>
+      </c>
+      <c r="G27">
+        <v>42.2</v>
+      </c>
+      <c r="H27">
+        <v>156.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>20.6</v>
+      </c>
+      <c r="K27">
+        <v>14.1</v>
+      </c>
+      <c r="L27">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M27">
+        <v>22.0293</v>
+      </c>
+      <c r="N27">
+        <v>-15.5293</v>
+      </c>
+      <c r="O27">
+        <v>-4.814083000000001</v>
+      </c>
+      <c r="P27">
+        <v>-10.715217</v>
+      </c>
+      <c r="Q27">
+        <v>3.384783000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1387036495678163</v>
+      </c>
+      <c r="T27">
+        <v>0.9760868067005217</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.09146908889524409</v>
+      </c>
+      <c r="W27">
+        <v>0.2169571815718157</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2950615770814325</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1602670325688162</v>
+      </c>
+      <c r="C28">
+        <v>138.9209066186799</v>
+      </c>
+      <c r="D28">
+        <v>192.6609066186798</v>
+      </c>
+      <c r="E28">
+        <v>-116.76</v>
+      </c>
+      <c r="F28">
+        <v>95.94</v>
+      </c>
+      <c r="G28">
+        <v>42.2</v>
+      </c>
+      <c r="H28">
+        <v>156.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>20.6</v>
+      </c>
+      <c r="K28">
+        <v>14.1</v>
+      </c>
+      <c r="L28">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M28">
+        <v>22.910472</v>
+      </c>
+      <c r="N28">
+        <v>-16.410472</v>
+      </c>
+      <c r="O28">
+        <v>-5.08724632</v>
+      </c>
+      <c r="P28">
+        <v>-11.32322568</v>
+      </c>
+      <c r="Q28">
+        <v>2.776774320000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1400536988863004</v>
+      </c>
+      <c r="T28">
+        <v>0.9892771689532316</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.08795104701465778</v>
+      </c>
+      <c r="W28">
+        <v>0.2177972899728997</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2837130548859929</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1622670325688162</v>
+      </c>
+      <c r="C29">
+        <v>132.1100588488706</v>
+      </c>
+      <c r="D29">
+        <v>189.5400588488705</v>
+      </c>
+      <c r="E29">
+        <v>-113.07</v>
+      </c>
+      <c r="F29">
+        <v>99.63000000000001</v>
+      </c>
+      <c r="G29">
+        <v>42.2</v>
+      </c>
+      <c r="H29">
+        <v>156.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>20.6</v>
+      </c>
+      <c r="K29">
+        <v>14.1</v>
+      </c>
+      <c r="L29">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M29">
+        <v>23.79164400000001</v>
+      </c>
+      <c r="N29">
+        <v>-17.29164400000001</v>
+      </c>
+      <c r="O29">
+        <v>-5.360409640000002</v>
+      </c>
+      <c r="P29">
+        <v>-11.93123436</v>
+      </c>
+      <c r="Q29">
+        <v>2.168765639999997</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1414407358573456</v>
+      </c>
+      <c r="T29">
+        <v>1.002828910993687</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.08469360082892971</v>
+      </c>
+      <c r="W29">
+        <v>0.2185751681220516</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2732051639642893</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1642670325688162</v>
+      </c>
+      <c r="C30">
+        <v>125.3987064670022</v>
+      </c>
+      <c r="D30">
+        <v>186.5187064670022</v>
+      </c>
+      <c r="E30">
+        <v>-109.38</v>
+      </c>
+      <c r="F30">
+        <v>103.32</v>
+      </c>
+      <c r="G30">
+        <v>42.2</v>
+      </c>
+      <c r="H30">
+        <v>156.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>20.6</v>
+      </c>
+      <c r="K30">
+        <v>14.1</v>
+      </c>
+      <c r="L30">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M30">
+        <v>24.672816</v>
+      </c>
+      <c r="N30">
+        <v>-18.172816</v>
+      </c>
+      <c r="O30">
+        <v>-5.633572960000002</v>
+      </c>
+      <c r="P30">
+        <v>-12.53924304</v>
+      </c>
+      <c r="Q30">
+        <v>1.560756959999997</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.142866301633142</v>
+      </c>
+      <c r="T30">
+        <v>1.016757090313044</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.08166882937075365</v>
+      </c>
+      <c r="W30">
+        <v>0.219297483546264</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2634478366798504</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1662670325688162</v>
+      </c>
+      <c r="C31">
+        <v>118.7821661262078</v>
+      </c>
+      <c r="D31">
+        <v>183.5921661262077</v>
+      </c>
+      <c r="E31">
+        <v>-105.69</v>
+      </c>
+      <c r="F31">
+        <v>107.01</v>
+      </c>
+      <c r="G31">
+        <v>42.2</v>
+      </c>
+      <c r="H31">
+        <v>156.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>20.6</v>
+      </c>
+      <c r="K31">
+        <v>14.1</v>
+      </c>
+      <c r="L31">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M31">
+        <v>25.553988</v>
+      </c>
+      <c r="N31">
+        <v>-19.053988</v>
+      </c>
+      <c r="O31">
+        <v>-5.90673628</v>
+      </c>
+      <c r="P31">
+        <v>-13.14725172</v>
+      </c>
+      <c r="Q31">
+        <v>0.9527482800000033</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1443320241913553</v>
+      </c>
+      <c r="T31">
+        <v>1.031077612711819</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.07885266284072767</v>
+      </c>
+      <c r="W31">
+        <v>0.2199699841136342</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2543634285184764</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1682670325688162</v>
+      </c>
+      <c r="C32">
+        <v>112.2560438720173</v>
+      </c>
+      <c r="D32">
+        <v>180.7560438720174</v>
+      </c>
+      <c r="E32">
+        <v>-102</v>
+      </c>
+      <c r="F32">
+        <v>110.7</v>
+      </c>
+      <c r="G32">
+        <v>42.2</v>
+      </c>
+      <c r="H32">
+        <v>156.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>20.6</v>
+      </c>
+      <c r="K32">
+        <v>14.1</v>
+      </c>
+      <c r="L32">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M32">
+        <v>26.43516</v>
+      </c>
+      <c r="N32">
+        <v>-19.93516</v>
+      </c>
+      <c r="O32">
+        <v>-6.179899600000002</v>
+      </c>
+      <c r="P32">
+        <v>-13.7552604</v>
+      </c>
+      <c r="Q32">
+        <v>0.3447395999999987</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1458396245369461</v>
+      </c>
+      <c r="T32">
+        <v>1.045807292893416</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.07622424074603674</v>
+      </c>
+      <c r="W32">
+        <v>0.2205976513098464</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2458846475678603</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1702670325688162</v>
+      </c>
+      <c r="C33">
+        <v>105.8162131298135</v>
+      </c>
+      <c r="D33">
+        <v>178.0062131298135</v>
+      </c>
+      <c r="E33">
+        <v>-98.30999999999999</v>
+      </c>
+      <c r="F33">
+        <v>114.39</v>
+      </c>
+      <c r="G33">
+        <v>42.2</v>
+      </c>
+      <c r="H33">
+        <v>156.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>20.6</v>
+      </c>
+      <c r="K33">
+        <v>14.1</v>
+      </c>
+      <c r="L33">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M33">
+        <v>27.316332</v>
+      </c>
+      <c r="N33">
+        <v>-20.816332</v>
+      </c>
+      <c r="O33">
+        <v>-6.453062920000002</v>
+      </c>
+      <c r="P33">
+        <v>-14.36326908</v>
+      </c>
+      <c r="Q33">
+        <v>-0.2632690800000024</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1473909234432786</v>
+      </c>
+      <c r="T33">
+        <v>1.060963920326654</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07376539427035814</v>
+      </c>
+      <c r="W33">
+        <v>0.2211848238482385</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2379528847430906</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1722670325688162</v>
+      </c>
+      <c r="C34">
+        <v>99.45879467143088</v>
+      </c>
+      <c r="D34">
+        <v>175.3387946714309</v>
+      </c>
+      <c r="E34">
+        <v>-94.61999999999999</v>
+      </c>
+      <c r="F34">
+        <v>118.08</v>
+      </c>
+      <c r="G34">
+        <v>42.2</v>
+      </c>
+      <c r="H34">
+        <v>156.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>20.6</v>
+      </c>
+      <c r="K34">
+        <v>14.1</v>
+      </c>
+      <c r="L34">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M34">
+        <v>28.197504</v>
+      </c>
+      <c r="N34">
+        <v>-21.697504</v>
+      </c>
+      <c r="O34">
+        <v>-6.726226240000002</v>
+      </c>
+      <c r="P34">
+        <v>-14.97127776</v>
+      </c>
+      <c r="Q34">
+        <v>-0.8712777599999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1489878487880327</v>
+      </c>
+      <c r="T34">
+        <v>1.076566330919693</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07146022569940945</v>
+      </c>
+      <c r="W34">
+        <v>0.221735298102981</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2305168570948691</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1742670325688162</v>
+      </c>
+      <c r="C35">
+        <v>93.18013835636228</v>
+      </c>
+      <c r="D35">
+        <v>172.7501383563623</v>
+      </c>
+      <c r="E35">
+        <v>-90.92999999999998</v>
+      </c>
+      <c r="F35">
+        <v>121.77</v>
+      </c>
+      <c r="G35">
+        <v>42.2</v>
+      </c>
+      <c r="H35">
+        <v>156.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>20.6</v>
+      </c>
+      <c r="K35">
+        <v>14.1</v>
+      </c>
+      <c r="L35">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M35">
+        <v>29.07867600000001</v>
+      </c>
+      <c r="N35">
+        <v>-22.578676</v>
+      </c>
+      <c r="O35">
+        <v>-6.999389560000002</v>
+      </c>
+      <c r="P35">
+        <v>-15.57928644</v>
+      </c>
+      <c r="Q35">
+        <v>-1.479286440000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1506324435460631</v>
+      </c>
+      <c r="T35">
+        <v>1.092634485112524</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.06929476431457886</v>
+      </c>
+      <c r="W35">
+        <v>0.2222524102816786</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2235314977889641</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1762670325688162</v>
+      </c>
+      <c r="C36">
+        <v>86.9768064668435</v>
+      </c>
+      <c r="D36">
+        <v>170.2368064668435</v>
+      </c>
+      <c r="E36">
+        <v>-87.23999999999998</v>
+      </c>
+      <c r="F36">
+        <v>125.46</v>
+      </c>
+      <c r="G36">
+        <v>42.2</v>
+      </c>
+      <c r="H36">
+        <v>156.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>20.6</v>
+      </c>
+      <c r="K36">
+        <v>14.1</v>
+      </c>
+      <c r="L36">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M36">
+        <v>29.959848</v>
+      </c>
+      <c r="N36">
+        <v>-23.459848</v>
+      </c>
+      <c r="O36">
+        <v>-7.272552880000002</v>
+      </c>
+      <c r="P36">
+        <v>-16.18729512</v>
+      </c>
+      <c r="Q36">
+        <v>-2.087295119999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1523268745088822</v>
+      </c>
+      <c r="T36">
+        <v>1.109189553068775</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.06725668301120889</v>
+      </c>
+      <c r="W36">
+        <v>0.2227391040969233</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2169570419716416</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1782670325688162</v>
+      </c>
+      <c r="C37">
+        <v>80.84555847681619</v>
+      </c>
+      <c r="D37">
+        <v>167.7955584768162</v>
+      </c>
+      <c r="E37">
+        <v>-83.54999999999998</v>
+      </c>
+      <c r="F37">
+        <v>129.15</v>
+      </c>
+      <c r="G37">
+        <v>42.2</v>
+      </c>
+      <c r="H37">
+        <v>156.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>20.6</v>
+      </c>
+      <c r="K37">
+        <v>14.1</v>
+      </c>
+      <c r="L37">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M37">
+        <v>30.84102</v>
+      </c>
+      <c r="N37">
+        <v>-24.34102</v>
+      </c>
+      <c r="O37">
+        <v>-7.545716200000001</v>
+      </c>
+      <c r="P37">
+        <v>-16.7953038</v>
+      </c>
+      <c r="Q37">
+        <v>-2.6953038</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1540734418090189</v>
+      </c>
+      <c r="T37">
+        <v>1.126254007731371</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06533506349660292</v>
+      </c>
+      <c r="W37">
+        <v>0.2231979868370113</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2107582693438804</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1802670325688162</v>
+      </c>
+      <c r="C38">
+        <v>74.78333711287135</v>
+      </c>
+      <c r="D38">
+        <v>165.4233371128713</v>
+      </c>
+      <c r="E38">
+        <v>-79.85999999999999</v>
+      </c>
+      <c r="F38">
+        <v>132.84</v>
+      </c>
+      <c r="G38">
+        <v>42.2</v>
+      </c>
+      <c r="H38">
+        <v>156.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>20.6</v>
+      </c>
+      <c r="K38">
+        <v>14.1</v>
+      </c>
+      <c r="L38">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M38">
+        <v>31.722192</v>
+      </c>
+      <c r="N38">
+        <v>-25.222192</v>
+      </c>
+      <c r="O38">
+        <v>-7.818879520000001</v>
+      </c>
+      <c r="P38">
+        <v>-17.40331248</v>
+      </c>
+      <c r="Q38">
+        <v>-3.303312479999997</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1558745893372848</v>
+      </c>
+      <c r="T38">
+        <v>1.143851726602174</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06352020062169729</v>
+      </c>
+      <c r="W38">
+        <v>0.2236313760915387</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2049038729732171</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1822670325688162</v>
+      </c>
+      <c r="C39">
+        <v>68.7872555810948</v>
+      </c>
+      <c r="D39">
+        <v>163.1172555810948</v>
+      </c>
+      <c r="E39">
+        <v>-76.16999999999999</v>
+      </c>
+      <c r="F39">
+        <v>136.53</v>
+      </c>
+      <c r="G39">
+        <v>42.2</v>
+      </c>
+      <c r="H39">
+        <v>156.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>20.6</v>
+      </c>
+      <c r="K39">
+        <v>14.1</v>
+      </c>
+      <c r="L39">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M39">
+        <v>32.603364</v>
+      </c>
+      <c r="N39">
+        <v>-26.103364</v>
+      </c>
+      <c r="O39">
+        <v>-8.092042840000001</v>
+      </c>
+      <c r="P39">
+        <v>-18.01132116</v>
+      </c>
+      <c r="Q39">
+        <v>-3.911321159999998</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1577329161521623</v>
+      </c>
+      <c r="T39">
+        <v>1.162008103214907</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0618034384427325</v>
+      </c>
+      <c r="W39">
+        <v>0.2240413388998755</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1993659304604274</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1842670325688162</v>
+      </c>
+      <c r="C40">
+        <v>62.85458584760821</v>
+      </c>
+      <c r="D40">
+        <v>160.8745858476082</v>
+      </c>
+      <c r="E40">
+        <v>-72.47999999999999</v>
+      </c>
+      <c r="F40">
+        <v>140.22</v>
+      </c>
+      <c r="G40">
+        <v>42.2</v>
+      </c>
+      <c r="H40">
+        <v>156.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>20.6</v>
+      </c>
+      <c r="K40">
+        <v>14.1</v>
+      </c>
+      <c r="L40">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M40">
+        <v>33.484536</v>
+      </c>
+      <c r="N40">
+        <v>-26.984536</v>
+      </c>
+      <c r="O40">
+        <v>-8.365206160000001</v>
+      </c>
+      <c r="P40">
+        <v>-18.61932984</v>
+      </c>
+      <c r="Q40">
+        <v>-4.519329839999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1596511889933262</v>
+      </c>
+      <c r="T40">
+        <v>1.180750169395792</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06017703216792376</v>
+      </c>
+      <c r="W40">
+        <v>0.2244297247182998</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1941194586062056</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1862670325688162</v>
+      </c>
+      <c r="C41">
+        <v>56.98274787277089</v>
+      </c>
+      <c r="D41">
+        <v>158.6927478727709</v>
+      </c>
+      <c r="E41">
+        <v>-68.78999999999999</v>
+      </c>
+      <c r="F41">
+        <v>143.91</v>
+      </c>
+      <c r="G41">
+        <v>42.2</v>
+      </c>
+      <c r="H41">
+        <v>156.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>20.6</v>
+      </c>
+      <c r="K41">
+        <v>14.1</v>
+      </c>
+      <c r="L41">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M41">
+        <v>34.365708</v>
+      </c>
+      <c r="N41">
+        <v>-27.865708</v>
+      </c>
+      <c r="O41">
+        <v>-8.638369480000001</v>
+      </c>
+      <c r="P41">
+        <v>-19.22733852</v>
+      </c>
+      <c r="Q41">
+        <v>-5.127338519999997</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1616323560260037</v>
+      </c>
+      <c r="T41">
+        <v>1.200106729549822</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.0586340313431052</v>
+      </c>
+      <c r="W41">
+        <v>0.2247981933152665</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1891420365906619</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1882670325688162</v>
+      </c>
+      <c r="C42">
+        <v>51.16929970971577</v>
+      </c>
+      <c r="D42">
+        <v>156.5692997097158</v>
+      </c>
+      <c r="E42">
+        <v>-65.09999999999999</v>
+      </c>
+      <c r="F42">
+        <v>147.6</v>
+      </c>
+      <c r="G42">
+        <v>42.2</v>
+      </c>
+      <c r="H42">
+        <v>156.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>20.6</v>
+      </c>
+      <c r="K42">
+        <v>14.1</v>
+      </c>
+      <c r="L42">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M42">
+        <v>35.24688</v>
+      </c>
+      <c r="N42">
+        <v>-28.74688</v>
+      </c>
+      <c r="O42">
+        <v>-8.911532800000002</v>
+      </c>
+      <c r="P42">
+        <v>-19.83534719999999</v>
+      </c>
+      <c r="Q42">
+        <v>-5.735347199999994</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1636795619597705</v>
+      </c>
+      <c r="T42">
+        <v>1.220108508375652</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.05716818055952757</v>
+      </c>
+      <c r="W42">
+        <v>0.2251482384823848</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1844134856758953</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1902670325688162</v>
+      </c>
+      <c r="C43">
+        <v>45.41192838733139</v>
+      </c>
+      <c r="D43">
+        <v>154.5019283873314</v>
+      </c>
+      <c r="E43">
+        <v>-61.40999999999997</v>
+      </c>
+      <c r="F43">
+        <v>151.29</v>
+      </c>
+      <c r="G43">
+        <v>42.2</v>
+      </c>
+      <c r="H43">
+        <v>156.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>20.6</v>
+      </c>
+      <c r="K43">
+        <v>14.1</v>
+      </c>
+      <c r="L43">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M43">
+        <v>36.128052</v>
+      </c>
+      <c r="N43">
+        <v>-29.628052</v>
+      </c>
+      <c r="O43">
+        <v>-9.184696120000003</v>
+      </c>
+      <c r="P43">
+        <v>-20.44335588</v>
+      </c>
+      <c r="Q43">
+        <v>-6.343355879999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1657961647048513</v>
+      </c>
+      <c r="T43">
+        <v>1.240788313602358</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.05577383469222201</v>
+      </c>
+      <c r="W43">
+        <v>0.2254812082754974</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1799155957813612</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1922670325688162</v>
+      </c>
+      <c r="C44">
+        <v>39.70844150612712</v>
+      </c>
+      <c r="D44">
+        <v>152.4884415061271</v>
+      </c>
+      <c r="E44">
+        <v>-57.72</v>
+      </c>
+      <c r="F44">
+        <v>154.98</v>
+      </c>
+      <c r="G44">
+        <v>42.2</v>
+      </c>
+      <c r="H44">
+        <v>156.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>20.6</v>
+      </c>
+      <c r="K44">
+        <v>14.1</v>
+      </c>
+      <c r="L44">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M44">
+        <v>37.009224</v>
+      </c>
+      <c r="N44">
+        <v>-30.509224</v>
+      </c>
+      <c r="O44">
+        <v>-9.45785944</v>
+      </c>
+      <c r="P44">
+        <v>-21.05136456</v>
+      </c>
+      <c r="Q44">
+        <v>-6.951364559999996</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1679857537514867</v>
+      </c>
+      <c r="T44">
+        <v>1.262181215561019</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05444588624716911</v>
+      </c>
+      <c r="W44">
+        <v>0.225798322364176</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1756318911199003</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1942670325688162</v>
+      </c>
+      <c r="C45">
+        <v>34.05675948278721</v>
+      </c>
+      <c r="D45">
+        <v>150.5267594827872</v>
+      </c>
+      <c r="E45">
+        <v>-54.03</v>
+      </c>
+      <c r="F45">
+        <v>158.67</v>
+      </c>
+      <c r="G45">
+        <v>42.2</v>
+      </c>
+      <c r="H45">
+        <v>156.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>20.6</v>
+      </c>
+      <c r="K45">
+        <v>14.1</v>
+      </c>
+      <c r="L45">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M45">
+        <v>37.890396</v>
+      </c>
+      <c r="N45">
+        <v>-31.390396</v>
+      </c>
+      <c r="O45">
+        <v>-9.73102276</v>
+      </c>
+      <c r="P45">
+        <v>-21.65937323999999</v>
+      </c>
+      <c r="Q45">
+        <v>-7.559373239999994</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1702521704839689</v>
+      </c>
+      <c r="T45">
+        <v>1.284324745658581</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05317970284607216</v>
+      </c>
+      <c r="W45">
+        <v>0.226100686960358</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1715474285357166</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1962670325688162</v>
+      </c>
+      <c r="C46">
+        <v>28.4549083857392</v>
+      </c>
+      <c r="D46">
+        <v>148.6149083857392</v>
+      </c>
+      <c r="E46">
+        <v>-50.33999999999997</v>
+      </c>
+      <c r="F46">
+        <v>162.36</v>
+      </c>
+      <c r="G46">
+        <v>42.2</v>
+      </c>
+      <c r="H46">
+        <v>156.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>20.6</v>
+      </c>
+      <c r="K46">
+        <v>14.1</v>
+      </c>
+      <c r="L46">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M46">
+        <v>38.771568</v>
+      </c>
+      <c r="N46">
+        <v>-32.271568</v>
+      </c>
+      <c r="O46">
+        <v>-10.00418608</v>
+      </c>
+      <c r="P46">
+        <v>-22.26738192</v>
+      </c>
+      <c r="Q46">
+        <v>-8.167381919999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1725995306711826</v>
+      </c>
+      <c r="T46">
+        <v>1.30725911611677</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05197107323593415</v>
+      </c>
+      <c r="W46">
+        <v>0.2263893077112589</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1676486233417229</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1982670325688162</v>
+      </c>
+      <c r="C47">
+        <v>22.90101330985129</v>
+      </c>
+      <c r="D47">
+        <v>146.7510133098513</v>
+      </c>
+      <c r="E47">
+        <v>-46.64999999999998</v>
+      </c>
+      <c r="F47">
+        <v>166.05</v>
+      </c>
+      <c r="G47">
+        <v>42.2</v>
+      </c>
+      <c r="H47">
+        <v>156.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>20.6</v>
+      </c>
+      <c r="K47">
+        <v>14.1</v>
+      </c>
+      <c r="L47">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M47">
+        <v>39.65274</v>
+      </c>
+      <c r="N47">
+        <v>-33.15274</v>
+      </c>
+      <c r="O47">
+        <v>-10.2773494</v>
+      </c>
+      <c r="P47">
+        <v>-22.8753906</v>
+      </c>
+      <c r="Q47">
+        <v>-8.7753906</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1750322494106586</v>
+      </c>
+      <c r="T47">
+        <v>1.33102746368253</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05081616049735783</v>
+      </c>
+      <c r="W47">
+        <v>0.226665100873231</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1639230983785736</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2002670325688162</v>
+      </c>
+      <c r="C48">
+        <v>17.39329224351155</v>
+      </c>
+      <c r="D48">
+        <v>144.9332922435115</v>
+      </c>
+      <c r="E48">
+        <v>-42.95999999999998</v>
+      </c>
+      <c r="F48">
+        <v>169.74</v>
+      </c>
+      <c r="G48">
+        <v>42.2</v>
+      </c>
+      <c r="H48">
+        <v>156.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>20.6</v>
+      </c>
+      <c r="K48">
+        <v>14.1</v>
+      </c>
+      <c r="L48">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M48">
+        <v>40.533912</v>
+      </c>
+      <c r="N48">
+        <v>-34.033912</v>
+      </c>
+      <c r="O48">
+        <v>-10.55051272</v>
+      </c>
+      <c r="P48">
+        <v>-23.48339928</v>
+      </c>
+      <c r="Q48">
+        <v>-9.383399280000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1775550688441894</v>
+      </c>
+      <c r="T48">
+        <v>1.355676120417391</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.04971146135611092</v>
+      </c>
+      <c r="W48">
+        <v>0.2269289030281607</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.160359552761648</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2022670325688162</v>
+      </c>
+      <c r="C49">
+        <v>11.93005038592173</v>
+      </c>
+      <c r="D49">
+        <v>143.1600503859217</v>
+      </c>
+      <c r="E49">
+        <v>-39.26999999999998</v>
+      </c>
+      <c r="F49">
+        <v>173.43</v>
+      </c>
+      <c r="G49">
+        <v>42.2</v>
+      </c>
+      <c r="H49">
+        <v>156.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>20.6</v>
+      </c>
+      <c r="K49">
+        <v>14.1</v>
+      </c>
+      <c r="L49">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M49">
+        <v>41.415084</v>
+      </c>
+      <c r="N49">
+        <v>-34.915084</v>
+      </c>
+      <c r="O49">
+        <v>-10.82367604</v>
+      </c>
+      <c r="P49">
+        <v>-24.09140796</v>
+      </c>
+      <c r="Q49">
+        <v>-9.991407959999998</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1801730890110609</v>
+      </c>
+      <c r="T49">
+        <v>1.381254915142248</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04865377068895962</v>
+      </c>
+      <c r="W49">
+        <v>0.2271814795594765</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1569476473837407</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2042670325688162</v>
+      </c>
+      <c r="C50">
+        <v>6.50967487651161</v>
+      </c>
+      <c r="D50">
+        <v>141.4296748765116</v>
+      </c>
+      <c r="E50">
+        <v>-35.57999999999998</v>
+      </c>
+      <c r="F50">
+        <v>177.12</v>
+      </c>
+      <c r="G50">
+        <v>42.2</v>
+      </c>
+      <c r="H50">
+        <v>156.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>20.6</v>
+      </c>
+      <c r="K50">
+        <v>14.1</v>
+      </c>
+      <c r="L50">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M50">
+        <v>42.29625600000001</v>
+      </c>
+      <c r="N50">
+        <v>-35.79625600000001</v>
+      </c>
+      <c r="O50">
+        <v>-11.09683936</v>
+      </c>
+      <c r="P50">
+        <v>-24.69941664</v>
+      </c>
+      <c r="Q50">
+        <v>-10.59941664</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1828918022612736</v>
+      </c>
+      <c r="T50">
+        <v>1.407817509664214</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.04764015046627296</v>
+      </c>
+      <c r="W50">
+        <v>0.227423532068654</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1536779047299127</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2062670325688162</v>
+      </c>
+      <c r="C51">
+        <v>1.130629902022179</v>
+      </c>
+      <c r="D51">
+        <v>139.7406299020222</v>
+      </c>
+      <c r="E51">
+        <v>-31.88999999999999</v>
+      </c>
+      <c r="F51">
+        <v>180.81</v>
+      </c>
+      <c r="G51">
+        <v>42.2</v>
+      </c>
+      <c r="H51">
+        <v>156.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>20.6</v>
+      </c>
+      <c r="K51">
+        <v>14.1</v>
+      </c>
+      <c r="L51">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M51">
+        <v>43.17742800000001</v>
+      </c>
+      <c r="N51">
+        <v>-36.67742800000001</v>
+      </c>
+      <c r="O51">
+        <v>-11.37000268</v>
+      </c>
+      <c r="P51">
+        <v>-25.30742532</v>
+      </c>
+      <c r="Q51">
+        <v>-11.20742532</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.185717131717377</v>
+      </c>
+      <c r="T51">
+        <v>1.435421774559591</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04666790249757352</v>
+      </c>
+      <c r="W51">
+        <v>0.2276557048835794</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1505416209599145</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2082670325688162</v>
+      </c>
+      <c r="C52">
+        <v>-4.208547849942931</v>
+      </c>
+      <c r="D52">
+        <v>138.0914521500571</v>
+      </c>
+      <c r="E52">
+        <v>-28.19999999999999</v>
+      </c>
+      <c r="F52">
+        <v>184.5</v>
+      </c>
+      <c r="G52">
+        <v>42.2</v>
+      </c>
+      <c r="H52">
+        <v>156.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>20.6</v>
+      </c>
+      <c r="K52">
+        <v>14.1</v>
+      </c>
+      <c r="L52">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M52">
+        <v>44.05860000000001</v>
+      </c>
+      <c r="N52">
+        <v>-37.55860000000001</v>
+      </c>
+      <c r="O52">
+        <v>-11.643166</v>
+      </c>
+      <c r="P52">
+        <v>-25.915434</v>
+      </c>
+      <c r="Q52">
+        <v>-11.815434</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1886554743517245</v>
+      </c>
+      <c r="T52">
+        <v>1.464130210050783</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.04573454444762205</v>
+      </c>
+      <c r="W52">
+        <v>0.2278785907859079</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1475307885407162</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2102670325688162</v>
+      </c>
+      <c r="C53">
+        <v>-9.509253419185654</v>
+      </c>
+      <c r="D53">
+        <v>136.4807465808143</v>
+      </c>
+      <c r="E53">
+        <v>-24.50999999999999</v>
+      </c>
+      <c r="F53">
+        <v>188.19</v>
+      </c>
+      <c r="G53">
+        <v>42.2</v>
+      </c>
+      <c r="H53">
+        <v>156.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>20.6</v>
+      </c>
+      <c r="K53">
+        <v>14.1</v>
+      </c>
+      <c r="L53">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M53">
+        <v>44.939772</v>
+      </c>
+      <c r="N53">
+        <v>-38.439772</v>
+      </c>
+      <c r="O53">
+        <v>-11.91632932</v>
+      </c>
+      <c r="P53">
+        <v>-26.52344268</v>
+      </c>
+      <c r="Q53">
+        <v>-12.42344268</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1917137493384944</v>
+      </c>
+      <c r="T53">
+        <v>1.494010418419166</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04483778867413926</v>
+      </c>
+      <c r="W53">
+        <v>0.2280927360646156</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1446380279810944</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2122670325688162</v>
+      </c>
+      <c r="C54">
+        <v>-14.77281750868116</v>
+      </c>
+      <c r="D54">
+        <v>134.9071824913188</v>
+      </c>
+      <c r="E54">
+        <v>-20.81999999999999</v>
+      </c>
+      <c r="F54">
+        <v>191.88</v>
+      </c>
+      <c r="G54">
+        <v>42.2</v>
+      </c>
+      <c r="H54">
+        <v>156.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>20.6</v>
+      </c>
+      <c r="K54">
+        <v>14.1</v>
+      </c>
+      <c r="L54">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M54">
+        <v>45.820944</v>
+      </c>
+      <c r="N54">
+        <v>-39.320944</v>
+      </c>
+      <c r="O54">
+        <v>-12.18949264</v>
+      </c>
+      <c r="P54">
+        <v>-27.13145136</v>
+      </c>
+      <c r="Q54">
+        <v>-13.03145136</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.194899452449713</v>
+      </c>
+      <c r="T54">
+        <v>1.525135635469565</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04397552350732889</v>
+      </c>
+      <c r="W54">
+        <v>0.2282986449864499</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1418565274429964</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2142670325688162</v>
+      </c>
+      <c r="C55">
+        <v>-20.00051015118268</v>
+      </c>
+      <c r="D55">
+        <v>133.3694898488174</v>
+      </c>
+      <c r="E55">
+        <v>-17.12999999999997</v>
+      </c>
+      <c r="F55">
+        <v>195.57</v>
+      </c>
+      <c r="G55">
+        <v>42.2</v>
+      </c>
+      <c r="H55">
+        <v>156.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>20.6</v>
+      </c>
+      <c r="K55">
+        <v>14.1</v>
+      </c>
+      <c r="L55">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M55">
+        <v>46.70211600000001</v>
+      </c>
+      <c r="N55">
+        <v>-40.20211600000001</v>
+      </c>
+      <c r="O55">
+        <v>-12.46265596</v>
+      </c>
+      <c r="P55">
+        <v>-27.73946004</v>
+      </c>
+      <c r="Q55">
+        <v>-13.63946004</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1982207173954516</v>
+      </c>
+      <c r="T55">
+        <v>1.557585329841258</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04314579664870003</v>
+      </c>
+      <c r="W55">
+        <v>0.2284967837602905</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1391799891893549</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2162670325688162</v>
+      </c>
+      <c r="C56">
+        <v>-25.19354412789718</v>
+      </c>
+      <c r="D56">
+        <v>131.8664558721028</v>
+      </c>
+      <c r="E56">
+        <v>-13.43999999999997</v>
+      </c>
+      <c r="F56">
+        <v>199.26</v>
+      </c>
+      <c r="G56">
+        <v>42.2</v>
+      </c>
+      <c r="H56">
+        <v>156.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>20.6</v>
+      </c>
+      <c r="K56">
+        <v>14.1</v>
+      </c>
+      <c r="L56">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M56">
+        <v>47.58328800000001</v>
+      </c>
+      <c r="N56">
+        <v>-41.08328800000001</v>
+      </c>
+      <c r="O56">
+        <v>-12.73581928</v>
+      </c>
+      <c r="P56">
+        <v>-28.34746872000001</v>
+      </c>
+      <c r="Q56">
+        <v>-14.24746872000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2016863851649179</v>
+      </c>
+      <c r="T56">
+        <v>1.591445880489981</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04234680041446486</v>
+      </c>
+      <c r="W56">
+        <v>0.2286875840610258</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1366025819821446</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2182670325688162</v>
+      </c>
+      <c r="C57">
+        <v>-30.35307815857257</v>
+      </c>
+      <c r="D57">
+        <v>130.3969218414274</v>
+      </c>
+      <c r="E57">
+        <v>-9.749999999999972</v>
+      </c>
+      <c r="F57">
+        <v>202.95</v>
+      </c>
+      <c r="G57">
+        <v>42.2</v>
+      </c>
+      <c r="H57">
+        <v>156.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>20.6</v>
+      </c>
+      <c r="K57">
+        <v>14.1</v>
+      </c>
+      <c r="L57">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M57">
+        <v>48.46446000000001</v>
+      </c>
+      <c r="N57">
+        <v>-41.96446000000001</v>
+      </c>
+      <c r="O57">
+        <v>-13.0089826</v>
+      </c>
+      <c r="P57">
+        <v>-28.95547740000001</v>
+      </c>
+      <c r="Q57">
+        <v>-14.85547740000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2053060826130272</v>
+      </c>
+      <c r="T57">
+        <v>1.62681134450087</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04157685858874731</v>
+      </c>
+      <c r="W57">
+        <v>0.2288714461690072</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1341188986733783</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2202670325688162</v>
+      </c>
+      <c r="C58">
+        <v>-35.48021988063144</v>
+      </c>
+      <c r="D58">
+        <v>128.9597801193686</v>
+      </c>
+      <c r="E58">
+        <v>-6.059999999999974</v>
+      </c>
+      <c r="F58">
+        <v>206.64</v>
+      </c>
+      <c r="G58">
+        <v>42.2</v>
+      </c>
+      <c r="H58">
+        <v>156.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>20.6</v>
+      </c>
+      <c r="K58">
+        <v>14.1</v>
+      </c>
+      <c r="L58">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M58">
+        <v>49.34563200000001</v>
+      </c>
+      <c r="N58">
+        <v>-42.84563200000001</v>
+      </c>
+      <c r="O58">
+        <v>-13.28214592</v>
+      </c>
+      <c r="P58">
+        <v>-29.56348608</v>
+      </c>
+      <c r="Q58">
+        <v>-15.46348608</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2090903117633233</v>
+      </c>
+      <c r="T58">
+        <v>1.663784329603162</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04083441468537682</v>
+      </c>
+      <c r="W58">
+        <v>0.229048741773132</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1317239183399251</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2222670325688162</v>
+      </c>
+      <c r="C59">
+        <v>-40.57602863344911</v>
+      </c>
+      <c r="D59">
+        <v>127.5539713665509</v>
+      </c>
+      <c r="E59">
+        <v>-2.369999999999976</v>
+      </c>
+      <c r="F59">
+        <v>210.33</v>
+      </c>
+      <c r="G59">
+        <v>42.2</v>
+      </c>
+      <c r="H59">
+        <v>156.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>20.6</v>
+      </c>
+      <c r="K59">
+        <v>14.1</v>
+      </c>
+      <c r="L59">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M59">
+        <v>50.22680400000001</v>
+      </c>
+      <c r="N59">
+        <v>-43.72680400000001</v>
+      </c>
+      <c r="O59">
+        <v>-13.55530924000001</v>
+      </c>
+      <c r="P59">
+        <v>-30.17149476</v>
+      </c>
+      <c r="Q59">
+        <v>-16.07149476</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2130505515717727</v>
+      </c>
+      <c r="T59">
+        <v>1.702476988431143</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04011802144528249</v>
+      </c>
+      <c r="W59">
+        <v>0.2292198164788666</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1294129724041371</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2242670325688162</v>
+      </c>
+      <c r="C60">
+        <v>-45.6415180624852</v>
+      </c>
+      <c r="D60">
+        <v>126.1784819375148</v>
+      </c>
+      <c r="E60">
+        <v>1.319999999999993</v>
+      </c>
+      <c r="F60">
+        <v>214.02</v>
+      </c>
+      <c r="G60">
+        <v>42.2</v>
+      </c>
+      <c r="H60">
+        <v>156.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>20.6</v>
+      </c>
+      <c r="K60">
+        <v>14.1</v>
+      </c>
+      <c r="L60">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M60">
+        <v>51.107976</v>
+      </c>
+      <c r="N60">
+        <v>-44.607976</v>
+      </c>
+      <c r="O60">
+        <v>-13.82847256</v>
+      </c>
+      <c r="P60">
+        <v>-30.77950344</v>
+      </c>
+      <c r="Q60">
+        <v>-16.67950344</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2171993742282435</v>
+      </c>
+      <c r="T60">
+        <v>1.74301215482236</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03942633142036384</v>
+      </c>
+      <c r="W60">
+        <v>0.2293849920568171</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1271817142592381</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2262670325688162</v>
+      </c>
+      <c r="C61">
+        <v>-50.67765855672059</v>
+      </c>
+      <c r="D61">
+        <v>124.8323414432794</v>
+      </c>
+      <c r="E61">
+        <v>5.009999999999991</v>
+      </c>
+      <c r="F61">
+        <v>217.71</v>
+      </c>
+      <c r="G61">
+        <v>42.2</v>
+      </c>
+      <c r="H61">
+        <v>156.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>20.6</v>
+      </c>
+      <c r="K61">
+        <v>14.1</v>
+      </c>
+      <c r="L61">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M61">
+        <v>51.989148</v>
+      </c>
+      <c r="N61">
+        <v>-45.489148</v>
+      </c>
+      <c r="O61">
+        <v>-14.10163588</v>
+      </c>
+      <c r="P61">
+        <v>-31.38751212</v>
+      </c>
+      <c r="Q61">
+        <v>-17.28751212</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2215505784777128</v>
+      </c>
+      <c r="T61">
+        <v>1.785524646403393</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03875808851493394</v>
+      </c>
+      <c r="W61">
+        <v>0.2295445684626338</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1250260919836578</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2282670325688162</v>
+      </c>
+      <c r="C62">
+        <v>-55.68537953171867</v>
+      </c>
+      <c r="D62">
+        <v>123.5146204682814</v>
+      </c>
+      <c r="E62">
+        <v>8.700000000000017</v>
+      </c>
+      <c r="F62">
+        <v>221.4</v>
+      </c>
+      <c r="G62">
+        <v>42.2</v>
+      </c>
+      <c r="H62">
+        <v>156.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>20.6</v>
+      </c>
+      <c r="K62">
+        <v>14.1</v>
+      </c>
+      <c r="L62">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M62">
+        <v>52.87032000000001</v>
+      </c>
+      <c r="N62">
+        <v>-46.37032000000001</v>
+      </c>
+      <c r="O62">
+        <v>-14.37479920000001</v>
+      </c>
+      <c r="P62">
+        <v>-31.9955208</v>
+      </c>
+      <c r="Q62">
+        <v>-17.8955208</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2261193429396557</v>
+      </c>
+      <c r="T62">
+        <v>1.830162762563478</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03811212037301837</v>
+      </c>
+      <c r="W62">
+        <v>0.2296988256549232</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1229423237839302</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2302670325688162</v>
+      </c>
+      <c r="C63">
+        <v>-60.6655715695974</v>
+      </c>
+      <c r="D63">
+        <v>122.2244284304026</v>
+      </c>
+      <c r="E63">
+        <v>12.39000000000001</v>
+      </c>
+      <c r="F63">
+        <v>225.09</v>
+      </c>
+      <c r="G63">
+        <v>42.2</v>
+      </c>
+      <c r="H63">
+        <v>156.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>20.6</v>
+      </c>
+      <c r="K63">
+        <v>14.1</v>
+      </c>
+      <c r="L63">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M63">
+        <v>53.75149200000001</v>
+      </c>
+      <c r="N63">
+        <v>-47.25149200000001</v>
+      </c>
+      <c r="O63">
+        <v>-14.64796252</v>
+      </c>
+      <c r="P63">
+        <v>-32.60352948000001</v>
+      </c>
+      <c r="Q63">
+        <v>-18.50352948</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2309224030150314</v>
+      </c>
+      <c r="T63">
+        <v>1.877090012885619</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.0374873315144443</v>
+      </c>
+      <c r="W63">
+        <v>0.2298480252343507</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1209268758530461</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2322670325688162</v>
+      </c>
+      <c r="C64">
+        <v>-65.61908842626835</v>
+      </c>
+      <c r="D64">
+        <v>120.9609115737317</v>
+      </c>
+      <c r="E64">
+        <v>16.08000000000001</v>
+      </c>
+      <c r="F64">
+        <v>228.78</v>
+      </c>
+      <c r="G64">
+        <v>42.2</v>
+      </c>
+      <c r="H64">
+        <v>156.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>20.6</v>
+      </c>
+      <c r="K64">
+        <v>14.1</v>
+      </c>
+      <c r="L64">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M64">
+        <v>54.63266400000001</v>
+      </c>
+      <c r="N64">
+        <v>-48.13266400000001</v>
+      </c>
+      <c r="O64">
+        <v>-14.92112584</v>
+      </c>
+      <c r="P64">
+        <v>-33.21153816</v>
+      </c>
+      <c r="Q64">
+        <v>-19.11153816</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2359782557259533</v>
+      </c>
+      <c r="T64">
+        <v>1.926487118487872</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03688269713517907</v>
+      </c>
+      <c r="W64">
+        <v>0.2299924119241192</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1189764423715454</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2342670325688162</v>
+      </c>
+      <c r="C65">
+        <v>-70.54674891544721</v>
+      </c>
+      <c r="D65">
+        <v>119.7232510845528</v>
+      </c>
+      <c r="E65">
+        <v>19.77000000000001</v>
+      </c>
+      <c r="F65">
+        <v>232.47</v>
+      </c>
+      <c r="G65">
+        <v>42.2</v>
+      </c>
+      <c r="H65">
+        <v>156.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>20.6</v>
+      </c>
+      <c r="K65">
+        <v>14.1</v>
+      </c>
+      <c r="L65">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M65">
+        <v>55.513836</v>
+      </c>
+      <c r="N65">
+        <v>-49.013836</v>
+      </c>
+      <c r="O65">
+        <v>-15.19428916</v>
+      </c>
+      <c r="P65">
+        <v>-33.81954684</v>
+      </c>
+      <c r="Q65">
+        <v>-19.71954684</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2413073977726007</v>
+      </c>
+      <c r="T65">
+        <v>1.978554337906463</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03629725749811274</v>
+      </c>
+      <c r="W65">
+        <v>0.2301322149094507</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1170879274132668</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2362670325688162</v>
+      </c>
+      <c r="C66">
+        <v>-75.44933867817466</v>
+      </c>
+      <c r="D66">
+        <v>118.5106613218253</v>
+      </c>
+      <c r="E66">
+        <v>23.46000000000001</v>
+      </c>
+      <c r="F66">
+        <v>236.16</v>
+      </c>
+      <c r="G66">
+        <v>42.2</v>
+      </c>
+      <c r="H66">
+        <v>156.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>20.6</v>
+      </c>
+      <c r="K66">
+        <v>14.1</v>
+      </c>
+      <c r="L66">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M66">
+        <v>56.395008</v>
+      </c>
+      <c r="N66">
+        <v>-49.895008</v>
+      </c>
+      <c r="O66">
+        <v>-15.46745248</v>
+      </c>
+      <c r="P66">
+        <v>-34.42755552</v>
+      </c>
+      <c r="Q66">
+        <v>-20.32755552</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2469326032662841</v>
+      </c>
+      <c r="T66">
+        <v>2.033514180626087</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03573011284970472</v>
+      </c>
+      <c r="W66">
+        <v>0.2302676490514905</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1152584285474345</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2382670325688162</v>
+      </c>
+      <c r="C67">
+        <v>-80.32761184588159</v>
+      </c>
+      <c r="D67">
+        <v>117.3223881541184</v>
+      </c>
+      <c r="E67">
+        <v>27.15000000000001</v>
+      </c>
+      <c r="F67">
+        <v>239.85</v>
+      </c>
+      <c r="G67">
+        <v>42.2</v>
+      </c>
+      <c r="H67">
+        <v>156.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>20.6</v>
+      </c>
+      <c r="K67">
+        <v>14.1</v>
+      </c>
+      <c r="L67">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M67">
+        <v>57.27618</v>
+      </c>
+      <c r="N67">
+        <v>-50.77618</v>
+      </c>
+      <c r="O67">
+        <v>-15.7406158</v>
+      </c>
+      <c r="P67">
+        <v>-35.0355642</v>
+      </c>
+      <c r="Q67">
+        <v>-20.93556419999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2528792490738923</v>
+      </c>
+      <c r="T67">
+        <v>2.091614585786833</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03518041880586312</v>
+      </c>
+      <c r="W67">
+        <v>0.2303989159891599</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1134852219543971</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2402670325688162</v>
+      </c>
+      <c r="C68">
+        <v>-85.18229260439773</v>
+      </c>
+      <c r="D68">
+        <v>116.1577073956023</v>
+      </c>
+      <c r="E68">
+        <v>30.84000000000003</v>
+      </c>
+      <c r="F68">
+        <v>243.54</v>
+      </c>
+      <c r="G68">
+        <v>42.2</v>
+      </c>
+      <c r="H68">
+        <v>156.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>20.6</v>
+      </c>
+      <c r="K68">
+        <v>14.1</v>
+      </c>
+      <c r="L68">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M68">
+        <v>58.15735200000001</v>
+      </c>
+      <c r="N68">
+        <v>-51.65735200000001</v>
+      </c>
+      <c r="O68">
+        <v>-16.01377912000001</v>
+      </c>
+      <c r="P68">
+        <v>-35.64357288000001</v>
+      </c>
+      <c r="Q68">
+        <v>-21.54357288000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2591756975760655</v>
+      </c>
+      <c r="T68">
+        <v>2.153132661839386</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03464738215728943</v>
+      </c>
+      <c r="W68">
+        <v>0.2305262051408393</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.111765748894482</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2422670325688162</v>
+      </c>
+      <c r="C69">
+        <v>-90.01407666571791</v>
+      </c>
+      <c r="D69">
+        <v>115.0159233342821</v>
+      </c>
+      <c r="E69">
+        <v>34.53000000000003</v>
+      </c>
+      <c r="F69">
+        <v>247.23</v>
+      </c>
+      <c r="G69">
+        <v>42.2</v>
+      </c>
+      <c r="H69">
+        <v>156.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>20.6</v>
+      </c>
+      <c r="K69">
+        <v>14.1</v>
+      </c>
+      <c r="L69">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M69">
+        <v>59.03852400000001</v>
+      </c>
+      <c r="N69">
+        <v>-52.53852400000001</v>
+      </c>
+      <c r="O69">
+        <v>-16.28694244</v>
+      </c>
+      <c r="P69">
+        <v>-36.25158156000001</v>
+      </c>
+      <c r="Q69">
+        <v>-22.15158156</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2658537490177644</v>
+      </c>
+      <c r="T69">
+        <v>2.21837910613755</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03413025705046421</v>
+      </c>
+      <c r="W69">
+        <v>0.2306496946163492</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1100976033885942</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2442670325688162</v>
+      </c>
+      <c r="C70">
+        <v>-94.82363265381309</v>
+      </c>
+      <c r="D70">
+        <v>113.8963673461869</v>
+      </c>
+      <c r="E70">
+        <v>38.22000000000003</v>
+      </c>
+      <c r="F70">
+        <v>250.92</v>
+      </c>
+      <c r="G70">
+        <v>42.2</v>
+      </c>
+      <c r="H70">
+        <v>156.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>20.6</v>
+      </c>
+      <c r="K70">
+        <v>14.1</v>
+      </c>
+      <c r="L70">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M70">
+        <v>59.91969600000001</v>
+      </c>
+      <c r="N70">
+        <v>-53.41969600000001</v>
+      </c>
+      <c r="O70">
+        <v>-16.56010576000001</v>
+      </c>
+      <c r="P70">
+        <v>-36.85959024</v>
+      </c>
+      <c r="Q70">
+        <v>-22.75959024</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2729491786745696</v>
+      </c>
+      <c r="T70">
+        <v>2.287703453204348</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03362834150560445</v>
+      </c>
+      <c r="W70">
+        <v>0.2307695520484617</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1084785209858208</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2462670325688162</v>
+      </c>
+      <c r="C71">
+        <v>-99.61160341028412</v>
+      </c>
+      <c r="D71">
+        <v>112.7983965897159</v>
+      </c>
+      <c r="E71">
+        <v>41.91000000000003</v>
+      </c>
+      <c r="F71">
+        <v>254.61</v>
+      </c>
+      <c r="G71">
+        <v>42.2</v>
+      </c>
+      <c r="H71">
+        <v>156.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>20.6</v>
+      </c>
+      <c r="K71">
+        <v>14.1</v>
+      </c>
+      <c r="L71">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M71">
+        <v>60.80086800000001</v>
+      </c>
+      <c r="N71">
+        <v>-54.30086800000001</v>
+      </c>
+      <c r="O71">
+        <v>-16.83326908</v>
+      </c>
+      <c r="P71">
+        <v>-37.46759892</v>
+      </c>
+      <c r="Q71">
+        <v>-23.36759892</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2805023779866525</v>
+      </c>
+      <c r="T71">
+        <v>2.361500338791585</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03314097423740728</v>
+      </c>
+      <c r="W71">
+        <v>0.2308859353521072</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1069063685077654</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2482670325688162</v>
+      </c>
+      <c r="C72">
+        <v>-104.3786072252177</v>
+      </c>
+      <c r="D72">
+        <v>111.7213927747823</v>
+      </c>
+      <c r="E72">
+        <v>45.60000000000002</v>
+      </c>
+      <c r="F72">
+        <v>258.3</v>
+      </c>
+      <c r="G72">
+        <v>42.2</v>
+      </c>
+      <c r="H72">
+        <v>156.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>20.6</v>
+      </c>
+      <c r="K72">
+        <v>14.1</v>
+      </c>
+      <c r="L72">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M72">
+        <v>61.68204000000001</v>
+      </c>
+      <c r="N72">
+        <v>-55.18204000000001</v>
+      </c>
+      <c r="O72">
+        <v>-17.10643240000001</v>
+      </c>
+      <c r="P72">
+        <v>-38.0756076</v>
+      </c>
+      <c r="Q72">
+        <v>-23.9756076</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2885591239195409</v>
+      </c>
+      <c r="T72">
+        <v>2.440217016751305</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03266753174830146</v>
+      </c>
+      <c r="W72">
+        <v>0.2309989934185056</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1053791346719402</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2502670325688162</v>
+      </c>
+      <c r="C73">
+        <v>-109.1252389981956</v>
+      </c>
+      <c r="D73">
+        <v>110.6647610018044</v>
+      </c>
+      <c r="E73">
+        <v>49.29000000000002</v>
+      </c>
+      <c r="F73">
+        <v>261.99</v>
+      </c>
+      <c r="G73">
+        <v>42.2</v>
+      </c>
+      <c r="H73">
+        <v>156.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>20.6</v>
+      </c>
+      <c r="K73">
+        <v>14.1</v>
+      </c>
+      <c r="L73">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M73">
+        <v>62.56321200000001</v>
+      </c>
+      <c r="N73">
+        <v>-56.06321200000001</v>
+      </c>
+      <c r="O73">
+        <v>-17.37959572</v>
+      </c>
+      <c r="P73">
+        <v>-38.68361628</v>
+      </c>
+      <c r="Q73">
+        <v>-24.58361628</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2971715075029733</v>
+      </c>
+      <c r="T73">
+        <v>2.524362431122039</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03220742566733947</v>
+      </c>
+      <c r="W73">
+        <v>0.2311088667506394</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1038949215075466</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2522670325688162</v>
+      </c>
+      <c r="C74">
+        <v>-113.8520713340377</v>
+      </c>
+      <c r="D74">
+        <v>109.6279286659623</v>
+      </c>
+      <c r="E74">
+        <v>52.98000000000002</v>
+      </c>
+      <c r="F74">
+        <v>265.68</v>
+      </c>
+      <c r="G74">
+        <v>42.2</v>
+      </c>
+      <c r="H74">
+        <v>156.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>20.6</v>
+      </c>
+      <c r="K74">
+        <v>14.1</v>
+      </c>
+      <c r="L74">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M74">
+        <v>63.44438400000001</v>
+      </c>
+      <c r="N74">
+        <v>-56.94438400000001</v>
+      </c>
+      <c r="O74">
+        <v>-17.65275904000001</v>
+      </c>
+      <c r="P74">
+        <v>-39.29162496</v>
+      </c>
+      <c r="Q74">
+        <v>-25.19162496</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3063990613423652</v>
+      </c>
+      <c r="T74">
+        <v>2.61451823223354</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03176010031084864</v>
+      </c>
+      <c r="W74">
+        <v>0.2312156880457694</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1024519364866084</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2542670325688162</v>
+      </c>
+      <c r="C75">
+        <v>-118.5596555775201</v>
+      </c>
+      <c r="D75">
+        <v>108.6103444224799</v>
+      </c>
+      <c r="E75">
+        <v>56.67000000000002</v>
+      </c>
+      <c r="F75">
+        <v>269.37</v>
+      </c>
+      <c r="G75">
+        <v>42.2</v>
+      </c>
+      <c r="H75">
+        <v>156.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>20.6</v>
+      </c>
+      <c r="K75">
+        <v>14.1</v>
+      </c>
+      <c r="L75">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M75">
+        <v>64.32555600000001</v>
+      </c>
+      <c r="N75">
+        <v>-57.82555600000001</v>
+      </c>
+      <c r="O75">
+        <v>-17.92592236</v>
+      </c>
+      <c r="P75">
+        <v>-39.89963364</v>
+      </c>
+      <c r="Q75">
+        <v>-25.79963364</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3163101376883787</v>
+      </c>
+      <c r="T75">
+        <v>2.711352240834783</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03132503044357674</v>
+      </c>
+      <c r="W75">
+        <v>0.2313195827300739</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1010484853018604</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2562670325688162</v>
+      </c>
+      <c r="C76">
+        <v>-123.2485227909963</v>
+      </c>
+      <c r="D76">
+        <v>107.6114772090037</v>
+      </c>
+      <c r="E76">
+        <v>60.36000000000001</v>
+      </c>
+      <c r="F76">
+        <v>273.06</v>
+      </c>
+      <c r="G76">
+        <v>42.2</v>
+      </c>
+      <c r="H76">
+        <v>156.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>20.6</v>
+      </c>
+      <c r="K76">
+        <v>14.1</v>
+      </c>
+      <c r="L76">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M76">
+        <v>65.206728</v>
+      </c>
+      <c r="N76">
+        <v>-58.706728</v>
+      </c>
+      <c r="O76">
+        <v>-18.19908568</v>
+      </c>
+      <c r="P76">
+        <v>-40.50764232</v>
+      </c>
+      <c r="Q76">
+        <v>-26.40764231999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3269836045225471</v>
+      </c>
+      <c r="T76">
+        <v>2.815635019328428</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03090171922136625</v>
+      </c>
+      <c r="W76">
+        <v>0.2314206694499378</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.09968296523021369</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2582670325688162</v>
+      </c>
+      <c r="C77">
+        <v>-127.9191846785648</v>
+      </c>
+      <c r="D77">
+        <v>106.6308153214352</v>
+      </c>
+      <c r="E77">
+        <v>64.05000000000001</v>
+      </c>
+      <c r="F77">
+        <v>276.75</v>
+      </c>
+      <c r="G77">
+        <v>42.2</v>
+      </c>
+      <c r="H77">
+        <v>156.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>20.6</v>
+      </c>
+      <c r="K77">
+        <v>14.1</v>
+      </c>
+      <c r="L77">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M77">
+        <v>66.0879</v>
+      </c>
+      <c r="N77">
+        <v>-59.5879</v>
+      </c>
+      <c r="O77">
+        <v>-18.47224900000001</v>
+      </c>
+      <c r="P77">
+        <v>-41.115651</v>
+      </c>
+      <c r="Q77">
+        <v>-27.015651</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3385109487034491</v>
+      </c>
+      <c r="T77">
+        <v>2.928260420101565</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0304896962984147</v>
+      </c>
+      <c r="W77">
+        <v>0.2315190605239386</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.09835385902714411</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2602670325688162</v>
+      </c>
+      <c r="C78">
+        <v>-132.5721344601609</v>
+      </c>
+      <c r="D78">
+        <v>105.6678655398391</v>
+      </c>
+      <c r="E78">
+        <v>67.74000000000001</v>
+      </c>
+      <c r="F78">
+        <v>280.44</v>
+      </c>
+      <c r="G78">
+        <v>42.2</v>
+      </c>
+      <c r="H78">
+        <v>156.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>20.6</v>
+      </c>
+      <c r="K78">
+        <v>14.1</v>
+      </c>
+      <c r="L78">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M78">
+        <v>66.969072</v>
+      </c>
+      <c r="N78">
+        <v>-60.469072</v>
+      </c>
+      <c r="O78">
+        <v>-18.74541232</v>
+      </c>
+      <c r="P78">
+        <v>-41.72365968</v>
+      </c>
+      <c r="Q78">
+        <v>-27.62365968</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3509989048994261</v>
+      </c>
+      <c r="T78">
+        <v>3.05027127093913</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03008851608396188</v>
+      </c>
+      <c r="W78">
+        <v>0.2316148623591499</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.0970597293031028</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2622670325688162</v>
+      </c>
+      <c r="C79">
+        <v>-137.2078476987103</v>
+      </c>
+      <c r="D79">
+        <v>104.7221523012897</v>
+      </c>
+      <c r="E79">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="F79">
+        <v>284.13</v>
+      </c>
+      <c r="G79">
+        <v>42.2</v>
+      </c>
+      <c r="H79">
+        <v>156.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>20.6</v>
+      </c>
+      <c r="K79">
+        <v>14.1</v>
+      </c>
+      <c r="L79">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M79">
+        <v>67.850244</v>
+      </c>
+      <c r="N79">
+        <v>-61.350244</v>
+      </c>
+      <c r="O79">
+        <v>-19.01857564000001</v>
+      </c>
+      <c r="P79">
+        <v>-42.33166835999999</v>
+      </c>
+      <c r="Q79">
+        <v>-28.23166835999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3645727703298359</v>
+      </c>
+      <c r="T79">
+        <v>3.182891760979962</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02969775613481951</v>
+      </c>
+      <c r="W79">
+        <v>0.2317081758350051</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.09579921333812746</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2642670325688162</v>
+      </c>
+      <c r="C80">
+        <v>-141.82678308326</v>
+      </c>
+      <c r="D80">
+        <v>103.7932169167401</v>
+      </c>
+      <c r="E80">
+        <v>75.12</v>
+      </c>
+      <c r="F80">
+        <v>287.82</v>
+      </c>
+      <c r="G80">
+        <v>42.2</v>
+      </c>
+      <c r="H80">
+        <v>156.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>20.6</v>
+      </c>
+      <c r="K80">
+        <v>14.1</v>
+      </c>
+      <c r="L80">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M80">
+        <v>68.731416</v>
+      </c>
+      <c r="N80">
+        <v>-62.231416</v>
+      </c>
+      <c r="O80">
+        <v>-19.29173896</v>
+      </c>
+      <c r="P80">
+        <v>-42.93967703999999</v>
+      </c>
+      <c r="Q80">
+        <v>-28.83967703999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3793806235266467</v>
+      </c>
+      <c r="T80">
+        <v>3.327568659206324</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0293170156715526</v>
+      </c>
+      <c r="W80">
+        <v>0.2317990966576332</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.09457101829533088</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2662670325688162</v>
+      </c>
+      <c r="C81">
+        <v>-146.4293831707943</v>
+      </c>
+      <c r="D81">
+        <v>102.8806168292057</v>
+      </c>
+      <c r="E81">
+        <v>78.81</v>
+      </c>
+      <c r="F81">
+        <v>291.51</v>
+      </c>
+      <c r="G81">
+        <v>42.2</v>
+      </c>
+      <c r="H81">
+        <v>156.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>20.6</v>
+      </c>
+      <c r="K81">
+        <v>14.1</v>
+      </c>
+      <c r="L81">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M81">
+        <v>69.612588</v>
+      </c>
+      <c r="N81">
+        <v>-63.112588</v>
+      </c>
+      <c r="O81">
+        <v>-19.56490228000001</v>
+      </c>
+      <c r="P81">
+        <v>-43.54768572</v>
+      </c>
+      <c r="Q81">
+        <v>-29.44768572</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.395598748456487</v>
+      </c>
+      <c r="T81">
+        <v>3.486024309644721</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02894591420735573</v>
+      </c>
+      <c r="W81">
+        <v>0.2318877156872835</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.09337391679792162</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2682670325688162</v>
+      </c>
+      <c r="C82">
+        <v>-151.0160750892584</v>
+      </c>
+      <c r="D82">
+        <v>101.9839249107415</v>
+      </c>
+      <c r="E82">
+        <v>82.5</v>
+      </c>
+      <c r="F82">
+        <v>295.2</v>
+      </c>
+      <c r="G82">
+        <v>42.2</v>
+      </c>
+      <c r="H82">
+        <v>156.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>20.6</v>
+      </c>
+      <c r="K82">
+        <v>14.1</v>
+      </c>
+      <c r="L82">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M82">
+        <v>70.49375999999999</v>
+      </c>
+      <c r="N82">
+        <v>-63.99375999999999</v>
+      </c>
+      <c r="O82">
+        <v>-19.8380656</v>
+      </c>
+      <c r="P82">
+        <v>-44.15569439999999</v>
+      </c>
+      <c r="Q82">
+        <v>-30.05569439999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4134386858793113</v>
+      </c>
+      <c r="T82">
+        <v>3.660325525126957</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02858409027976378</v>
+      </c>
+      <c r="W82">
+        <v>0.2319741192411924</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.09220674283794761</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2702670325688162</v>
+      </c>
+      <c r="C83">
+        <v>-155.5872712041344</v>
+      </c>
+      <c r="D83">
+        <v>101.1027287958657</v>
+      </c>
+      <c r="E83">
+        <v>86.19000000000005</v>
+      </c>
+      <c r="F83">
+        <v>298.89</v>
+      </c>
+      <c r="G83">
+        <v>42.2</v>
+      </c>
+      <c r="H83">
+        <v>156.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>20.6</v>
+      </c>
+      <c r="K83">
+        <v>14.1</v>
+      </c>
+      <c r="L83">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M83">
+        <v>71.37493200000002</v>
+      </c>
+      <c r="N83">
+        <v>-64.87493200000002</v>
+      </c>
+      <c r="O83">
+        <v>-20.11122892000001</v>
+      </c>
+      <c r="P83">
+        <v>-44.76370308000001</v>
+      </c>
+      <c r="Q83">
+        <v>-30.66370308</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4331565114519067</v>
+      </c>
+      <c r="T83">
+        <v>3.852974236975744</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0282312002763099</v>
+      </c>
+      <c r="W83">
+        <v>0.2320583893740172</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.09106838798809647</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2722670325688162</v>
+      </c>
+      <c r="C84">
+        <v>-160.1433697507552</v>
+      </c>
+      <c r="D84">
+        <v>100.2366302492448</v>
+      </c>
+      <c r="E84">
+        <v>89.88000000000005</v>
+      </c>
+      <c r="F84">
+        <v>302.58</v>
+      </c>
+      <c r="G84">
+        <v>42.2</v>
+      </c>
+      <c r="H84">
+        <v>156.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>20.6</v>
+      </c>
+      <c r="K84">
+        <v>14.1</v>
+      </c>
+      <c r="L84">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M84">
+        <v>72.25610400000001</v>
+      </c>
+      <c r="N84">
+        <v>-65.75610400000001</v>
+      </c>
+      <c r="O84">
+        <v>-20.38439224000001</v>
+      </c>
+      <c r="P84">
+        <v>-45.37171176</v>
+      </c>
+      <c r="Q84">
+        <v>-31.27171176</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4550652065325682</v>
+      </c>
+      <c r="T84">
+        <v>4.067028361252174</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02788691734611101</v>
+      </c>
+      <c r="W84">
+        <v>0.2321406041377487</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.08995779789068059</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2742670325688162</v>
+      </c>
+      <c r="C85">
+        <v>-164.6847554343961</v>
+      </c>
+      <c r="D85">
+        <v>99.38524456560395</v>
+      </c>
+      <c r="E85">
+        <v>93.57000000000005</v>
+      </c>
+      <c r="F85">
+        <v>306.27</v>
+      </c>
+      <c r="G85">
+        <v>42.2</v>
+      </c>
+      <c r="H85">
+        <v>156.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>20.6</v>
+      </c>
+      <c r="K85">
+        <v>14.1</v>
+      </c>
+      <c r="L85">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M85">
+        <v>73.13727600000001</v>
+      </c>
+      <c r="N85">
+        <v>-66.63727600000001</v>
+      </c>
+      <c r="O85">
+        <v>-20.65755556000001</v>
+      </c>
+      <c r="P85">
+        <v>-45.97972044000001</v>
+      </c>
+      <c r="Q85">
+        <v>-31.87972044000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4795513951521311</v>
+      </c>
+      <c r="T85">
+        <v>4.306265323678774</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02755093039013376</v>
+      </c>
+      <c r="W85">
+        <v>0.2322208378228361</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.08887396900043143</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2762670325688162</v>
+      </c>
+      <c r="C86">
+        <v>-169.2118000000395</v>
+      </c>
+      <c r="D86">
+        <v>98.5481999999605</v>
+      </c>
+      <c r="E86">
+        <v>97.25999999999999</v>
+      </c>
+      <c r="F86">
+        <v>309.96</v>
+      </c>
+      <c r="G86">
+        <v>42.2</v>
+      </c>
+      <c r="H86">
+        <v>156.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>20.6</v>
+      </c>
+      <c r="K86">
+        <v>14.1</v>
+      </c>
+      <c r="L86">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M86">
+        <v>74.01844799999999</v>
+      </c>
+      <c r="N86">
+        <v>-67.51844799999999</v>
+      </c>
+      <c r="O86">
+        <v>-20.93071888</v>
+      </c>
+      <c r="P86">
+        <v>-46.58772911999999</v>
+      </c>
+      <c r="Q86">
+        <v>-32.48772911999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.507098357349139</v>
+      </c>
+      <c r="T86">
+        <v>4.575406906408695</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02722294312358456</v>
+      </c>
+      <c r="W86">
+        <v>0.232299161182088</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.08781594555995009</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2782670325688162</v>
+      </c>
+      <c r="C87">
+        <v>-173.7248627735896</v>
+      </c>
+      <c r="D87">
+        <v>97.72513722641033</v>
+      </c>
+      <c r="E87">
+        <v>100.95</v>
+      </c>
+      <c r="F87">
+        <v>313.65</v>
+      </c>
+      <c r="G87">
+        <v>42.2</v>
+      </c>
+      <c r="H87">
+        <v>156.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>20.6</v>
+      </c>
+      <c r="K87">
+        <v>14.1</v>
+      </c>
+      <c r="L87">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M87">
+        <v>74.89962</v>
+      </c>
+      <c r="N87">
+        <v>-68.39962</v>
+      </c>
+      <c r="O87">
+        <v>-21.2038822</v>
+      </c>
+      <c r="P87">
+        <v>-47.1957378</v>
+      </c>
+      <c r="Q87">
+        <v>-33.09573779999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5383182478390817</v>
+      </c>
+      <c r="T87">
+        <v>4.880434033502608</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02690267320448356</v>
+      </c>
+      <c r="W87">
+        <v>0.2323756416387693</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.08678281678865662</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2802670325688162</v>
+      </c>
+      <c r="C88">
+        <v>-178.22429117619</v>
+      </c>
+      <c r="D88">
+        <v>96.91570882380996</v>
+      </c>
+      <c r="E88">
+        <v>104.64</v>
+      </c>
+      <c r="F88">
+        <v>317.34</v>
+      </c>
+      <c r="G88">
+        <v>42.2</v>
+      </c>
+      <c r="H88">
+        <v>156.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>20.6</v>
+      </c>
+      <c r="K88">
+        <v>14.1</v>
+      </c>
+      <c r="L88">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M88">
+        <v>75.78079199999999</v>
+      </c>
+      <c r="N88">
+        <v>-69.28079199999999</v>
+      </c>
+      <c r="O88">
+        <v>-21.47704552</v>
+      </c>
+      <c r="P88">
+        <v>-47.80374647999999</v>
+      </c>
+      <c r="Q88">
+        <v>-33.70374647999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5739981226847304</v>
+      </c>
+      <c r="T88">
+        <v>5.229036464467081</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02658985142303608</v>
+      </c>
+      <c r="W88">
+        <v>0.232450343480179</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.08577371426785829</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2822670325688162</v>
+      </c>
+      <c r="C89">
+        <v>-182.7104212131914</v>
+      </c>
+      <c r="D89">
+        <v>96.11957878680862</v>
+      </c>
+      <c r="E89">
+        <v>108.33</v>
+      </c>
+      <c r="F89">
+        <v>321.03</v>
+      </c>
+      <c r="G89">
+        <v>42.2</v>
+      </c>
+      <c r="H89">
+        <v>156.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>20.6</v>
+      </c>
+      <c r="K89">
+        <v>14.1</v>
+      </c>
+      <c r="L89">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M89">
+        <v>76.661964</v>
+      </c>
+      <c r="N89">
+        <v>-70.161964</v>
+      </c>
+      <c r="O89">
+        <v>-21.75020884</v>
+      </c>
+      <c r="P89">
+        <v>-48.41175516</v>
+      </c>
+      <c r="Q89">
+        <v>-34.31175516</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6151672090450941</v>
+      </c>
+      <c r="T89">
+        <v>5.631270038656855</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02628422094690923</v>
+      </c>
+      <c r="W89">
+        <v>0.2325233280378781</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.08478780950615872</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2842670325688162</v>
+      </c>
+      <c r="C90">
+        <v>-187.1835779392162</v>
+      </c>
+      <c r="D90">
+        <v>95.33642206078383</v>
+      </c>
+      <c r="E90">
+        <v>112.02</v>
+      </c>
+      <c r="F90">
+        <v>324.72</v>
+      </c>
+      <c r="G90">
+        <v>42.2</v>
+      </c>
+      <c r="H90">
+        <v>156.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>20.6</v>
+      </c>
+      <c r="K90">
+        <v>14.1</v>
+      </c>
+      <c r="L90">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M90">
+        <v>77.543136</v>
+      </c>
+      <c r="N90">
+        <v>-71.043136</v>
+      </c>
+      <c r="O90">
+        <v>-22.02337216</v>
+      </c>
+      <c r="P90">
+        <v>-49.01976384</v>
+      </c>
+      <c r="Q90">
+        <v>-34.91976383999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6631978097988522</v>
+      </c>
+      <c r="T90">
+        <v>6.10054254187826</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02598553661796707</v>
+      </c>
+      <c r="W90">
+        <v>0.2325946538556295</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.08382431167086146</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2862670325688162</v>
+      </c>
+      <c r="C91">
+        <v>-191.6440759006711</v>
+      </c>
+      <c r="D91">
+        <v>94.56592409932894</v>
+      </c>
+      <c r="E91">
+        <v>115.71</v>
+      </c>
+      <c r="F91">
+        <v>328.41</v>
+      </c>
+      <c r="G91">
+        <v>42.2</v>
+      </c>
+      <c r="H91">
+        <v>156.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>20.6</v>
+      </c>
+      <c r="K91">
+        <v>14.1</v>
+      </c>
+      <c r="L91">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M91">
+        <v>78.42430800000001</v>
+      </c>
+      <c r="N91">
+        <v>-71.92430800000001</v>
+      </c>
+      <c r="O91">
+        <v>-22.29653548000001</v>
+      </c>
+      <c r="P91">
+        <v>-49.62777252000001</v>
+      </c>
+      <c r="Q91">
+        <v>-35.52777252000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7199612470532935</v>
+      </c>
+      <c r="T91">
+        <v>6.655137318412649</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02569356429641688</v>
+      </c>
+      <c r="W91">
+        <v>0.2326643768460157</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.08288246547231248</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2882670325688162</v>
+      </c>
+      <c r="C92">
+        <v>-196.0922195569736</v>
+      </c>
+      <c r="D92">
+        <v>93.8077804430264</v>
+      </c>
+      <c r="E92">
+        <v>119.4</v>
+      </c>
+      <c r="F92">
+        <v>332.1</v>
+      </c>
+      <c r="G92">
+        <v>42.2</v>
+      </c>
+      <c r="H92">
+        <v>156.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>20.6</v>
+      </c>
+      <c r="K92">
+        <v>14.1</v>
+      </c>
+      <c r="L92">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M92">
+        <v>79.30548</v>
+      </c>
+      <c r="N92">
+        <v>-72.80548</v>
+      </c>
+      <c r="O92">
+        <v>-22.5696988</v>
+      </c>
+      <c r="P92">
+        <v>-50.2357812</v>
+      </c>
+      <c r="Q92">
+        <v>-36.1357812</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7880773717586227</v>
+      </c>
+      <c r="T92">
+        <v>7.320651050253914</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02540808024867892</v>
+      </c>
+      <c r="W92">
+        <v>0.2327325504366155</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.08196154918928678</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2902670325688161</v>
+      </c>
+      <c r="C93">
+        <v>-200.5283036816777</v>
+      </c>
+      <c r="D93">
+        <v>93.06169631832229</v>
+      </c>
+      <c r="E93">
+        <v>123.09</v>
+      </c>
+      <c r="F93">
+        <v>335.79</v>
+      </c>
+      <c r="G93">
+        <v>42.2</v>
+      </c>
+      <c r="H93">
+        <v>156.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>20.6</v>
+      </c>
+      <c r="K93">
+        <v>14.1</v>
+      </c>
+      <c r="L93">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M93">
+        <v>80.18665200000001</v>
+      </c>
+      <c r="N93">
+        <v>-73.68665200000001</v>
+      </c>
+      <c r="O93">
+        <v>-22.84286212000001</v>
+      </c>
+      <c r="P93">
+        <v>-50.84378988</v>
+      </c>
+      <c r="Q93">
+        <v>-36.74378988</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8713304130651363</v>
+      </c>
+      <c r="T93">
+        <v>8.134056722504349</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02512887057561651</v>
+      </c>
+      <c r="W93">
+        <v>0.2327992257065428</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.08106087282456931</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2922670325688162</v>
+      </c>
+      <c r="C94">
+        <v>-204.9526137446092</v>
+      </c>
+      <c r="D94">
+        <v>92.32738625539088</v>
+      </c>
+      <c r="E94">
+        <v>126.78</v>
+      </c>
+      <c r="F94">
+        <v>339.48</v>
+      </c>
+      <c r="G94">
+        <v>42.2</v>
+      </c>
+      <c r="H94">
+        <v>156.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>20.6</v>
+      </c>
+      <c r="K94">
+        <v>14.1</v>
+      </c>
+      <c r="L94">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M94">
+        <v>81.067824</v>
+      </c>
+      <c r="N94">
+        <v>-74.567824</v>
+      </c>
+      <c r="O94">
+        <v>-23.11602544</v>
+      </c>
+      <c r="P94">
+        <v>-51.45179856</v>
+      </c>
+      <c r="Q94">
+        <v>-37.35179856</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9753967146982787</v>
+      </c>
+      <c r="T94">
+        <v>9.150813812817397</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02485573067805546</v>
+      </c>
+      <c r="W94">
+        <v>0.2328644515140804</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.08017977638082407</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2942670325688162</v>
+      </c>
+      <c r="C95">
+        <v>-209.3654262760501</v>
+      </c>
+      <c r="D95">
+        <v>91.6045737239499</v>
+      </c>
+      <c r="E95">
+        <v>130.47</v>
+      </c>
+      <c r="F95">
+        <v>343.17</v>
+      </c>
+      <c r="G95">
+        <v>42.2</v>
+      </c>
+      <c r="H95">
+        <v>156.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>20.6</v>
+      </c>
+      <c r="K95">
+        <v>14.1</v>
+      </c>
+      <c r="L95">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M95">
+        <v>81.94899600000001</v>
+      </c>
+      <c r="N95">
+        <v>-75.44899600000001</v>
+      </c>
+      <c r="O95">
+        <v>-23.38918876000001</v>
+      </c>
+      <c r="P95">
+        <v>-52.05980724</v>
+      </c>
+      <c r="Q95">
+        <v>-37.95980724</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.109196245369461</v>
+      </c>
+      <c r="T95">
+        <v>10.45807292893417</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02458846475678604</v>
+      </c>
+      <c r="W95">
+        <v>0.2329282746160795</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.07931762824769684</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2962670325688162</v>
+      </c>
+      <c r="C96">
+        <v>-213.7670092139508</v>
+      </c>
+      <c r="D96">
+        <v>90.89299078604917</v>
+      </c>
+      <c r="E96">
+        <v>134.16</v>
+      </c>
+      <c r="F96">
+        <v>346.86</v>
+      </c>
+      <c r="G96">
+        <v>42.2</v>
+      </c>
+      <c r="H96">
+        <v>156.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>20.6</v>
+      </c>
+      <c r="K96">
+        <v>14.1</v>
+      </c>
+      <c r="L96">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M96">
+        <v>82.830168</v>
+      </c>
+      <c r="N96">
+        <v>-76.330168</v>
+      </c>
+      <c r="O96">
+        <v>-23.66235208000001</v>
+      </c>
+      <c r="P96">
+        <v>-52.66781592</v>
+      </c>
+      <c r="Q96">
+        <v>-38.56781591999999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.287595619597705</v>
+      </c>
+      <c r="T96">
+        <v>12.20108508375653</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02432688534447981</v>
+      </c>
+      <c r="W96">
+        <v>0.2329907397797382</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.07847382369187028</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2982670325688162</v>
+      </c>
+      <c r="C97">
+        <v>-218.1576222350825</v>
+      </c>
+      <c r="D97">
+        <v>90.19237776491751</v>
+      </c>
+      <c r="E97">
+        <v>137.85</v>
+      </c>
+      <c r="F97">
+        <v>350.55</v>
+      </c>
+      <c r="G97">
+        <v>42.2</v>
+      </c>
+      <c r="H97">
+        <v>156.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>20.6</v>
+      </c>
+      <c r="K97">
+        <v>14.1</v>
+      </c>
+      <c r="L97">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M97">
+        <v>83.71134000000001</v>
+      </c>
+      <c r="N97">
+        <v>-77.21134000000001</v>
+      </c>
+      <c r="O97">
+        <v>-23.93551540000001</v>
+      </c>
+      <c r="P97">
+        <v>-53.2758246</v>
+      </c>
+      <c r="Q97">
+        <v>-39.1758246</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.537354743517247</v>
+      </c>
+      <c r="T97">
+        <v>14.64130210050785</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0240708128671695</v>
+      </c>
+      <c r="W97">
+        <v>0.2330518898873199</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.07764778344248224</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3002670325688162</v>
+      </c>
+      <c r="C98">
+        <v>-222.5375170709921</v>
+      </c>
+      <c r="D98">
+        <v>89.50248292900793</v>
+      </c>
+      <c r="E98">
+        <v>141.54</v>
+      </c>
+      <c r="F98">
+        <v>354.24</v>
+      </c>
+      <c r="G98">
+        <v>42.2</v>
+      </c>
+      <c r="H98">
+        <v>156.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>20.6</v>
+      </c>
+      <c r="K98">
+        <v>14.1</v>
+      </c>
+      <c r="L98">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M98">
+        <v>84.59251200000001</v>
+      </c>
+      <c r="N98">
+        <v>-78.09251200000001</v>
+      </c>
+      <c r="O98">
+        <v>-24.20867872000001</v>
+      </c>
+      <c r="P98">
+        <v>-53.88383328</v>
+      </c>
+      <c r="Q98">
+        <v>-39.78383328</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.911993429396555</v>
+      </c>
+      <c r="T98">
+        <v>18.30162762563477</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02382007523313648</v>
+      </c>
+      <c r="W98">
+        <v>0.233111766034327</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.0768389523649563</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3022670325688162</v>
+      </c>
+      <c r="C99">
+        <v>-226.9069378095669</v>
+      </c>
+      <c r="D99">
+        <v>88.82306219043313</v>
+      </c>
+      <c r="E99">
+        <v>145.23</v>
+      </c>
+      <c r="F99">
+        <v>357.93</v>
+      </c>
+      <c r="G99">
+        <v>42.2</v>
+      </c>
+      <c r="H99">
+        <v>156.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>20.6</v>
+      </c>
+      <c r="K99">
+        <v>14.1</v>
+      </c>
+      <c r="L99">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M99">
+        <v>85.47368400000001</v>
+      </c>
+      <c r="N99">
+        <v>-78.97368400000001</v>
+      </c>
+      <c r="O99">
+        <v>-24.48184204000001</v>
+      </c>
+      <c r="P99">
+        <v>-54.49184196</v>
+      </c>
+      <c r="Q99">
+        <v>-40.39184196</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.536391239195407</v>
+      </c>
+      <c r="T99">
+        <v>24.40217016751302</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02357450744722786</v>
+      </c>
+      <c r="W99">
+        <v>0.233170407621602</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.076046798216864</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3042670325688162</v>
+      </c>
+      <c r="C100">
+        <v>-231.2661211829668</v>
+      </c>
+      <c r="D100">
+        <v>88.15387881703322</v>
+      </c>
+      <c r="E100">
+        <v>148.92</v>
+      </c>
+      <c r="F100">
+        <v>361.62</v>
+      </c>
+      <c r="G100">
+        <v>42.2</v>
+      </c>
+      <c r="H100">
+        <v>156.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>20.6</v>
+      </c>
+      <c r="K100">
+        <v>14.1</v>
+      </c>
+      <c r="L100">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M100">
+        <v>86.35485600000001</v>
+      </c>
+      <c r="N100">
+        <v>-79.85485600000001</v>
+      </c>
+      <c r="O100">
+        <v>-24.75500536000001</v>
+      </c>
+      <c r="P100">
+        <v>-55.09985064</v>
+      </c>
+      <c r="Q100">
+        <v>-40.99985064</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.785186858793109</v>
+      </c>
+      <c r="T100">
+        <v>36.60325525126953</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02333395124878676</v>
+      </c>
+      <c r="W100">
+        <v>0.2332278524417897</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.07527081047995721</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3062670325688162</v>
+      </c>
+      <c r="C101">
+        <v>-235.6152968426388</v>
+      </c>
+      <c r="D101">
+        <v>87.49470315736119</v>
+      </c>
+      <c r="E101">
+        <v>152.61</v>
+      </c>
+      <c r="F101">
+        <v>365.31</v>
+      </c>
+      <c r="G101">
+        <v>42.2</v>
+      </c>
+      <c r="H101">
+        <v>156.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>20.6</v>
+      </c>
+      <c r="K101">
+        <v>14.1</v>
+      </c>
+      <c r="L101">
+        <v>6.500000000000002</v>
+      </c>
+      <c r="M101">
+        <v>87.236028</v>
+      </c>
+      <c r="N101">
+        <v>-80.736028</v>
+      </c>
+      <c r="O101">
+        <v>-25.02816868000001</v>
+      </c>
+      <c r="P101">
+        <v>-55.70785932</v>
+      </c>
+      <c r="Q101">
+        <v>-41.60785932</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.531573717586219</v>
+      </c>
+      <c r="T101">
+        <v>73.20651050253906</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02309825477152629</v>
+      </c>
+      <c r="W101">
+        <v>0.2332841367605595</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.07451049926298803</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/morocco/morocco_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_hotel_gaming.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1031948963688802</v>
+        <v>0.1028952727004998</v>
       </c>
       <c r="C2">
-        <v>488.598970745421</v>
+        <v>485.6435276446102</v>
       </c>
       <c r="D2">
-        <v>411.898970745421</v>
+        <v>414.0605276446103</v>
       </c>
       <c r="E2">
-        <v>-194.9</v>
+        <v>-189.783</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.117000000000001</v>
       </c>
       <c r="G2">
         <v>76.7</v>
@@ -1451,28 +1451,28 @@
         <v>30.95</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2573851</v>
       </c>
       <c r="N2">
-        <v>30.95</v>
+        <v>30.6926149</v>
       </c>
       <c r="O2">
-        <v>9.904</v>
+        <v>9.821636767999999</v>
       </c>
       <c r="P2">
-        <v>21.046</v>
+        <v>20.870978132</v>
       </c>
       <c r="Q2">
-        <v>38.346</v>
+        <v>38.170978132</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1031948963688802</v>
+        <v>0.1035891239398987</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7531860115015515</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>120.2478309738986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1028952727004998</v>
+        <v>0.1025956490321193</v>
       </c>
       <c r="C3">
-        <v>485.6435276446102</v>
+        <v>482.7108909953002</v>
       </c>
       <c r="D3">
-        <v>414.0605276446103</v>
+        <v>416.2448909953002</v>
       </c>
       <c r="E3">
-        <v>-189.783</v>
+        <v>-184.666</v>
       </c>
       <c r="F3">
-        <v>5.117000000000001</v>
+        <v>10.234</v>
       </c>
       <c r="G3">
         <v>76.7</v>
@@ -1533,28 +1533,28 @@
         <v>30.95</v>
       </c>
       <c r="M3">
-        <v>0.2573851</v>
+        <v>0.5147702000000001</v>
       </c>
       <c r="N3">
-        <v>30.6926149</v>
+        <v>30.4352298</v>
       </c>
       <c r="O3">
-        <v>9.821636767999999</v>
+        <v>9.739273535999999</v>
       </c>
       <c r="P3">
-        <v>20.870978132</v>
+        <v>20.695956264</v>
       </c>
       <c r="Q3">
-        <v>38.170978132</v>
+        <v>37.995956264</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1035891239398987</v>
+        <v>0.1039913969715504</v>
       </c>
       <c r="T3">
-        <v>0.7531860115015515</v>
+        <v>0.7584289776444439</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>120.2478309738986</v>
+        <v>60.12391548694931</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1025956490321193</v>
+        <v>0.1022960253637389</v>
       </c>
       <c r="C4">
-        <v>482.7108909953002</v>
+        <v>479.8014236559016</v>
       </c>
       <c r="D4">
-        <v>416.2448909953002</v>
+        <v>418.4524236559016</v>
       </c>
       <c r="E4">
-        <v>-184.666</v>
+        <v>-179.549</v>
       </c>
       <c r="F4">
-        <v>10.234</v>
+        <v>15.351</v>
       </c>
       <c r="G4">
         <v>76.7</v>
@@ -1615,28 +1615,28 @@
         <v>30.95</v>
       </c>
       <c r="M4">
-        <v>0.5147702000000001</v>
+        <v>0.7721553</v>
       </c>
       <c r="N4">
-        <v>30.4352298</v>
+        <v>30.1778447</v>
       </c>
       <c r="O4">
-        <v>9.739273535999999</v>
+        <v>9.656910304</v>
       </c>
       <c r="P4">
-        <v>20.695956264</v>
+        <v>20.520934396</v>
       </c>
       <c r="Q4">
-        <v>37.995956264</v>
+        <v>37.820934396</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1039913969715504</v>
+        <v>0.1044019642925144</v>
       </c>
       <c r="T4">
-        <v>0.7584289776444439</v>
+        <v>0.7637800461820353</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.12391548694931</v>
+        <v>40.08261032463288</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1022960253637389</v>
+        <v>0.1019964016953585</v>
       </c>
       <c r="C5">
-        <v>479.8014236559016</v>
+        <v>476.915496223468</v>
       </c>
       <c r="D5">
-        <v>418.4524236559016</v>
+        <v>420.6834962234681</v>
       </c>
       <c r="E5">
-        <v>-179.549</v>
+        <v>-174.432</v>
       </c>
       <c r="F5">
-        <v>15.351</v>
+        <v>20.468</v>
       </c>
       <c r="G5">
         <v>76.7</v>
@@ -1697,28 +1697,28 @@
         <v>30.95</v>
       </c>
       <c r="M5">
-        <v>0.7721553</v>
+        <v>1.0295404</v>
       </c>
       <c r="N5">
-        <v>30.1778447</v>
+        <v>29.9204596</v>
       </c>
       <c r="O5">
-        <v>9.656910304</v>
+        <v>9.574547072</v>
       </c>
       <c r="P5">
-        <v>20.520934396</v>
+        <v>20.345912528</v>
       </c>
       <c r="Q5">
-        <v>37.820934396</v>
+        <v>37.645912528</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1044019642925144</v>
+        <v>0.1048210850993318</v>
       </c>
       <c r="T5">
-        <v>0.7637800461820353</v>
+        <v>0.7692425953141598</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.08261032463288</v>
+        <v>30.06195774347466</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1019964016953585</v>
+        <v>0.1016967780269781</v>
       </c>
       <c r="C6">
-        <v>476.915496223468</v>
+        <v>474.0534872411031</v>
       </c>
       <c r="D6">
-        <v>420.6834962234681</v>
+        <v>422.9384872411031</v>
       </c>
       <c r="E6">
-        <v>-174.432</v>
+        <v>-169.315</v>
       </c>
       <c r="F6">
-        <v>20.468</v>
+        <v>25.585</v>
       </c>
       <c r="G6">
         <v>76.7</v>
@@ -1779,28 +1779,28 @@
         <v>30.95</v>
       </c>
       <c r="M6">
-        <v>1.0295404</v>
+        <v>1.2869255</v>
       </c>
       <c r="N6">
-        <v>29.9204596</v>
+        <v>29.6630745</v>
       </c>
       <c r="O6">
-        <v>9.574547072</v>
+        <v>9.492183840000001</v>
       </c>
       <c r="P6">
-        <v>20.345912528</v>
+        <v>20.17089066</v>
       </c>
       <c r="Q6">
-        <v>37.645912528</v>
+        <v>37.47089065999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1048210850993318</v>
+        <v>0.1052490295020822</v>
       </c>
       <c r="T6">
-        <v>0.7692425953141598</v>
+        <v>0.7748201454806448</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.06195774347466</v>
+        <v>24.04956619477973</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1016967780269781</v>
+        <v>0.1013971543585977</v>
       </c>
       <c r="C7">
-        <v>474.0534872411031</v>
+        <v>471.2157834120743</v>
       </c>
       <c r="D7">
-        <v>422.9384872411031</v>
+        <v>425.2177834120743</v>
       </c>
       <c r="E7">
-        <v>-169.315</v>
+        <v>-164.198</v>
       </c>
       <c r="F7">
-        <v>25.585</v>
+        <v>30.70200000000001</v>
       </c>
       <c r="G7">
         <v>76.7</v>
@@ -1861,28 +1861,28 @@
         <v>30.95</v>
       </c>
       <c r="M7">
-        <v>1.2869255</v>
+        <v>1.5443106</v>
       </c>
       <c r="N7">
-        <v>29.6630745</v>
+        <v>29.4056894</v>
       </c>
       <c r="O7">
-        <v>9.492183840000001</v>
+        <v>9.409820608</v>
       </c>
       <c r="P7">
-        <v>20.17089066</v>
+        <v>19.995868792</v>
       </c>
       <c r="Q7">
-        <v>37.47089065999999</v>
+        <v>37.295868792</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1052490295020822</v>
+        <v>0.1056860791048912</v>
       </c>
       <c r="T7">
-        <v>0.7748201454806448</v>
+        <v>0.7805163669272678</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.04956619477973</v>
+        <v>20.04130516231644</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1013971543585977</v>
+        <v>0.1010975306902173</v>
       </c>
       <c r="C8">
-        <v>471.2157834120743</v>
+        <v>468.4027798208876</v>
       </c>
       <c r="D8">
-        <v>425.2177834120743</v>
+        <v>427.5217798208876</v>
       </c>
       <c r="E8">
-        <v>-164.198</v>
+        <v>-159.081</v>
       </c>
       <c r="F8">
-        <v>30.702</v>
+        <v>35.819</v>
       </c>
       <c r="G8">
         <v>76.7</v>
@@ -1943,28 +1943,28 @@
         <v>30.95</v>
       </c>
       <c r="M8">
-        <v>1.5443106</v>
+        <v>1.8016957</v>
       </c>
       <c r="N8">
-        <v>29.4056894</v>
+        <v>29.1483043</v>
       </c>
       <c r="O8">
-        <v>9.409820608</v>
+        <v>9.327457376</v>
       </c>
       <c r="P8">
-        <v>19.995868792</v>
+        <v>19.820846924</v>
       </c>
       <c r="Q8">
-        <v>37.295868792</v>
+        <v>37.12084692400001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1056860791048912</v>
+        <v>0.1061325276238895</v>
       </c>
       <c r="T8">
-        <v>0.7805163669272678</v>
+        <v>0.7863350877598397</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.04130516231644</v>
+        <v>17.17826156769981</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1010975306902173</v>
+        <v>0.1007979070218368</v>
       </c>
       <c r="C9">
-        <v>468.4027798208877</v>
+        <v>465.6148801615898</v>
       </c>
       <c r="D9">
-        <v>427.5217798208877</v>
+        <v>429.8508801615898</v>
       </c>
       <c r="E9">
-        <v>-159.081</v>
+        <v>-153.964</v>
       </c>
       <c r="F9">
-        <v>35.81900000000001</v>
+        <v>40.93600000000001</v>
       </c>
       <c r="G9">
         <v>76.7</v>
@@ -2025,28 +2025,28 @@
         <v>30.95</v>
       </c>
       <c r="M9">
-        <v>1.8016957</v>
+        <v>2.0590808</v>
       </c>
       <c r="N9">
-        <v>29.1483043</v>
+        <v>28.8909192</v>
       </c>
       <c r="O9">
-        <v>9.327457376</v>
+        <v>9.245094143999999</v>
       </c>
       <c r="P9">
-        <v>19.820846924</v>
+        <v>19.645825056</v>
       </c>
       <c r="Q9">
-        <v>37.12084692400001</v>
+        <v>36.945825056</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1061325276238895</v>
+        <v>0.1065886815454748</v>
       </c>
       <c r="T9">
-        <v>0.7863350877598397</v>
+        <v>0.7922803025235543</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.1782615676998</v>
+        <v>15.03097887173733</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1007979070218368</v>
+        <v>0.1004982833534564</v>
       </c>
       <c r="C10">
-        <v>465.6148801615898</v>
+        <v>462.852496973571</v>
       </c>
       <c r="D10">
-        <v>429.8508801615898</v>
+        <v>432.205496973571</v>
       </c>
       <c r="E10">
-        <v>-153.964</v>
+        <v>-148.847</v>
       </c>
       <c r="F10">
-        <v>40.93600000000001</v>
+        <v>46.053</v>
       </c>
       <c r="G10">
         <v>76.7</v>
@@ -2107,28 +2107,28 @@
         <v>30.95</v>
       </c>
       <c r="M10">
-        <v>2.0590808</v>
+        <v>2.3164659</v>
       </c>
       <c r="N10">
-        <v>28.8909192</v>
+        <v>28.6335341</v>
       </c>
       <c r="O10">
-        <v>9.245094143999999</v>
+        <v>9.162730911999999</v>
       </c>
       <c r="P10">
-        <v>19.645825056</v>
+        <v>19.470803188</v>
       </c>
       <c r="Q10">
-        <v>36.945825056</v>
+        <v>36.770803188</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1065886815454748</v>
+        <v>0.1070548608279741</v>
       </c>
       <c r="T10">
-        <v>0.7922803025235543</v>
+        <v>0.7983561813480101</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.03097887173733</v>
+        <v>13.36087010821096</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1004982833534564</v>
+        <v>0.100300659685076</v>
       </c>
       <c r="C11">
-        <v>462.852496973571</v>
+        <v>459.3027080183484</v>
       </c>
       <c r="D11">
-        <v>432.205496973571</v>
+        <v>433.7727080183484</v>
       </c>
       <c r="E11">
-        <v>-148.847</v>
+        <v>-143.73</v>
       </c>
       <c r="F11">
-        <v>46.053</v>
+        <v>51.17</v>
       </c>
       <c r="G11">
         <v>76.7</v>
@@ -2189,45 +2189,45 @@
         <v>30.95</v>
       </c>
       <c r="M11">
-        <v>2.3164659</v>
+        <v>2.650606</v>
       </c>
       <c r="N11">
-        <v>28.6335341</v>
+        <v>28.299394</v>
       </c>
       <c r="O11">
-        <v>9.162730911999999</v>
+        <v>9.05580608</v>
       </c>
       <c r="P11">
-        <v>19.470803188</v>
+        <v>19.24358792</v>
       </c>
       <c r="Q11">
-        <v>36.770803188</v>
+        <v>36.54358792</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1070548608279741</v>
+        <v>0.1075313996500845</v>
       </c>
       <c r="T11">
-        <v>0.7983561813480101</v>
+        <v>0.8045670797018981</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.36087010821096</v>
+        <v>11.67657509263919</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.100300659685076</v>
+        <v>0.1000112360166956</v>
       </c>
       <c r="C12">
-        <v>459.3027080183484</v>
+        <v>456.5015395252949</v>
       </c>
       <c r="D12">
-        <v>433.7727080183484</v>
+        <v>436.0885395252949</v>
       </c>
       <c r="E12">
-        <v>-143.73</v>
+        <v>-138.613</v>
       </c>
       <c r="F12">
-        <v>51.17000000000001</v>
+        <v>56.28700000000001</v>
       </c>
       <c r="G12">
         <v>76.7</v>
@@ -2271,28 +2271,28 @@
         <v>30.95</v>
       </c>
       <c r="M12">
-        <v>2.650606</v>
+        <v>2.9156666</v>
       </c>
       <c r="N12">
-        <v>28.299394</v>
+        <v>28.0343334</v>
       </c>
       <c r="O12">
-        <v>9.05580608</v>
+        <v>8.970986688</v>
       </c>
       <c r="P12">
-        <v>19.24358792</v>
+        <v>19.063346712</v>
       </c>
       <c r="Q12">
-        <v>36.54358792</v>
+        <v>36.36334671199999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1075313996500845</v>
+        <v>0.1080186472097703</v>
       </c>
       <c r="T12">
-        <v>0.8045670797018981</v>
+        <v>0.8109175488053116</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.67657509263919</v>
+        <v>10.61506826603563</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1000112360166956</v>
+        <v>0.0998605323483152</v>
       </c>
       <c r="C13">
-        <v>456.5015395252949</v>
+        <v>452.6002164672398</v>
       </c>
       <c r="D13">
-        <v>436.0885395252949</v>
+        <v>437.3042164672397</v>
       </c>
       <c r="E13">
-        <v>-138.613</v>
+        <v>-133.496</v>
       </c>
       <c r="F13">
-        <v>56.28700000000001</v>
+        <v>61.404</v>
       </c>
       <c r="G13">
         <v>76.7</v>
@@ -2353,45 +2353,45 @@
         <v>30.95</v>
       </c>
       <c r="M13">
-        <v>2.9156666</v>
+        <v>3.285114</v>
       </c>
       <c r="N13">
-        <v>28.0343334</v>
+        <v>27.664886</v>
       </c>
       <c r="O13">
-        <v>8.970986688</v>
+        <v>8.85276352</v>
       </c>
       <c r="P13">
-        <v>19.063346712</v>
+        <v>18.81212248</v>
       </c>
       <c r="Q13">
-        <v>36.36334671199999</v>
+        <v>36.11212248</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1080186472097703</v>
+        <v>0.1085169685776309</v>
       </c>
       <c r="T13">
-        <v>0.8109175488053116</v>
+        <v>0.8174123467519848</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.61506826603563</v>
+        <v>9.421286445462774</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0998605323483152</v>
+        <v>0.09958266867993477</v>
       </c>
       <c r="C14">
-        <v>452.6002164672398</v>
+        <v>449.742512198899</v>
       </c>
       <c r="D14">
-        <v>437.3042164672397</v>
+        <v>439.5635121988989</v>
       </c>
       <c r="E14">
-        <v>-133.496</v>
+        <v>-128.379</v>
       </c>
       <c r="F14">
-        <v>61.404</v>
+        <v>66.52100000000002</v>
       </c>
       <c r="G14">
         <v>76.7</v>
@@ -2435,28 +2435,28 @@
         <v>30.95</v>
       </c>
       <c r="M14">
-        <v>3.285114</v>
+        <v>3.558873500000001</v>
       </c>
       <c r="N14">
-        <v>27.664886</v>
+        <v>27.3911265</v>
       </c>
       <c r="O14">
-        <v>8.85276352</v>
+        <v>8.76516048</v>
       </c>
       <c r="P14">
-        <v>18.81212248</v>
+        <v>18.62596602</v>
       </c>
       <c r="Q14">
-        <v>36.11212248</v>
+        <v>35.92596602</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1085169685776309</v>
+        <v>0.1090267456091204</v>
       </c>
       <c r="T14">
-        <v>0.8174123467519848</v>
+        <v>0.8240564503985813</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.421286445462774</v>
+        <v>8.696572103504099</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09958266867993477</v>
+        <v>0.09930480501155435</v>
       </c>
       <c r="C15">
-        <v>449.742512198899</v>
+        <v>446.9082740921418</v>
       </c>
       <c r="D15">
-        <v>439.5635121988989</v>
+        <v>441.8462740921418</v>
       </c>
       <c r="E15">
-        <v>-128.379</v>
+        <v>-123.262</v>
       </c>
       <c r="F15">
-        <v>66.52100000000002</v>
+        <v>71.63800000000002</v>
       </c>
       <c r="G15">
         <v>76.7</v>
@@ -2517,28 +2517,28 @@
         <v>30.95</v>
       </c>
       <c r="M15">
-        <v>3.558873500000001</v>
+        <v>3.832633000000001</v>
       </c>
       <c r="N15">
-        <v>27.3911265</v>
+        <v>27.117367</v>
       </c>
       <c r="O15">
-        <v>8.76516048</v>
+        <v>8.677557439999999</v>
       </c>
       <c r="P15">
-        <v>18.62596602</v>
+        <v>18.43980956</v>
       </c>
       <c r="Q15">
-        <v>35.92596602</v>
+        <v>35.73980956</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1090267456091204</v>
+        <v>0.109548377920412</v>
       </c>
       <c r="T15">
-        <v>0.8240564503985813</v>
+        <v>0.8308550680834708</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.696572103504099</v>
+        <v>8.075388381825235</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09930480501155435</v>
+        <v>0.09910854134317394</v>
       </c>
       <c r="C16">
-        <v>446.9082740921418</v>
+        <v>443.4179997242557</v>
       </c>
       <c r="D16">
-        <v>441.8462740921418</v>
+        <v>443.4729997242556</v>
       </c>
       <c r="E16">
-        <v>-123.262</v>
+        <v>-118.145</v>
       </c>
       <c r="F16">
-        <v>71.63800000000002</v>
+        <v>76.75500000000002</v>
       </c>
       <c r="G16">
         <v>76.7</v>
@@ -2599,45 +2599,45 @@
         <v>30.95</v>
       </c>
       <c r="M16">
-        <v>3.832633000000001</v>
+        <v>4.167796500000001</v>
       </c>
       <c r="N16">
-        <v>27.117367</v>
+        <v>26.7822035</v>
       </c>
       <c r="O16">
-        <v>8.677557439999999</v>
+        <v>8.570305119999999</v>
       </c>
       <c r="P16">
-        <v>18.43980956</v>
+        <v>18.21189838</v>
       </c>
       <c r="Q16">
-        <v>35.73980956</v>
+        <v>35.51189838000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.109548377920412</v>
+        <v>0.1100822839331458</v>
       </c>
       <c r="T16">
-        <v>0.8308550680834708</v>
+        <v>0.8378136532432989</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.075388381825235</v>
+        <v>7.425986369536034</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09910854134317394</v>
+        <v>0.09883611767479353</v>
       </c>
       <c r="C17">
-        <v>443.4179997242557</v>
+        <v>440.5789293071362</v>
       </c>
       <c r="D17">
-        <v>443.4729997242556</v>
+        <v>445.7509293071362</v>
       </c>
       <c r="E17">
-        <v>-118.145</v>
+        <v>-113.028</v>
       </c>
       <c r="F17">
-        <v>76.75500000000001</v>
+        <v>81.87200000000001</v>
       </c>
       <c r="G17">
         <v>76.7</v>
@@ -2681,28 +2681,28 @@
         <v>30.95</v>
       </c>
       <c r="M17">
-        <v>4.167796500000001</v>
+        <v>4.445649600000001</v>
       </c>
       <c r="N17">
-        <v>26.7822035</v>
+        <v>26.5043504</v>
       </c>
       <c r="O17">
-        <v>8.570305119999999</v>
+        <v>8.481392128</v>
       </c>
       <c r="P17">
-        <v>18.21189838</v>
+        <v>18.022958272</v>
       </c>
       <c r="Q17">
-        <v>35.51189838000001</v>
+        <v>35.322958272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1100822839331458</v>
+        <v>0.1106289019938018</v>
       </c>
       <c r="T17">
-        <v>0.8378136532432989</v>
+        <v>0.8449379190021705</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.425986369536036</v>
+        <v>6.961862221440033</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09883611767479353</v>
+        <v>0.0985636940064131</v>
       </c>
       <c r="C18">
-        <v>440.5789293071362</v>
+        <v>437.7633811981102</v>
       </c>
       <c r="D18">
-        <v>445.7509293071362</v>
+        <v>448.0523811981103</v>
       </c>
       <c r="E18">
-        <v>-113.028</v>
+        <v>-107.911</v>
       </c>
       <c r="F18">
-        <v>81.87200000000001</v>
+        <v>86.98900000000002</v>
       </c>
       <c r="G18">
         <v>76.7</v>
@@ -2763,28 +2763,28 @@
         <v>30.95</v>
       </c>
       <c r="M18">
-        <v>4.445649600000001</v>
+        <v>4.723502700000001</v>
       </c>
       <c r="N18">
-        <v>26.5043504</v>
+        <v>26.2264973</v>
       </c>
       <c r="O18">
-        <v>8.481392128</v>
+        <v>8.392479136</v>
       </c>
       <c r="P18">
-        <v>18.022958272</v>
+        <v>17.834018164</v>
       </c>
       <c r="Q18">
-        <v>35.322958272</v>
+        <v>35.134018164</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1106289019938018</v>
+        <v>0.1111886915739917</v>
       </c>
       <c r="T18">
-        <v>0.8449379190021705</v>
+        <v>0.8522338538154727</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.961862221440033</v>
+        <v>6.552340914296502</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0985636940064131</v>
+        <v>0.09829127033803269</v>
       </c>
       <c r="C19">
-        <v>437.7633811981102</v>
+        <v>434.9717216314152</v>
       </c>
       <c r="D19">
-        <v>448.0523811981103</v>
+        <v>450.3777216314152</v>
       </c>
       <c r="E19">
-        <v>-107.911</v>
+        <v>-102.794</v>
       </c>
       <c r="F19">
-        <v>86.98900000000002</v>
+        <v>92.10600000000002</v>
       </c>
       <c r="G19">
         <v>76.7</v>
@@ -2845,28 +2845,28 @@
         <v>30.95</v>
       </c>
       <c r="M19">
-        <v>4.723502700000001</v>
+        <v>5.001355800000002</v>
       </c>
       <c r="N19">
-        <v>26.2264973</v>
+        <v>25.9486442</v>
       </c>
       <c r="O19">
-        <v>8.392479136</v>
+        <v>8.303566143999999</v>
       </c>
       <c r="P19">
-        <v>17.834018164</v>
+        <v>17.645078056</v>
       </c>
       <c r="Q19">
-        <v>35.134018164</v>
+        <v>34.945078056</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1111886915739917</v>
+        <v>0.1117621345585764</v>
       </c>
       <c r="T19">
-        <v>0.8522338538154727</v>
+        <v>0.8597077382583675</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.552340914296502</v>
+        <v>6.188321974613362</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09829127033803269</v>
+        <v>0.09814804666965228</v>
       </c>
       <c r="C20">
-        <v>434.9717216314152</v>
+        <v>431.0869500248818</v>
       </c>
       <c r="D20">
-        <v>450.3777216314152</v>
+        <v>451.6099500248818</v>
       </c>
       <c r="E20">
-        <v>-102.794</v>
+        <v>-97.67699999999999</v>
       </c>
       <c r="F20">
-        <v>92.10600000000001</v>
+        <v>97.22300000000001</v>
       </c>
       <c r="G20">
         <v>76.7</v>
@@ -2927,45 +2927,45 @@
         <v>30.95</v>
       </c>
       <c r="M20">
-        <v>5.001355800000001</v>
+        <v>5.376431900000001</v>
       </c>
       <c r="N20">
-        <v>25.9486442</v>
+        <v>25.5735681</v>
       </c>
       <c r="O20">
-        <v>8.303566143999999</v>
+        <v>8.183541792</v>
       </c>
       <c r="P20">
-        <v>17.645078056</v>
+        <v>17.390026308</v>
       </c>
       <c r="Q20">
-        <v>34.945078056</v>
+        <v>34.690026308</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1117621345585764</v>
+        <v>0.1123497366292003</v>
       </c>
       <c r="T20">
-        <v>0.8597077382583675</v>
+        <v>0.8673661630578773</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.32</v>
       </c>
       <c r="W20">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.188321974613363</v>
+        <v>5.756605975051966</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09814804666965228</v>
+        <v>0.09788242300127184</v>
       </c>
       <c r="C21">
-        <v>431.0869500248818</v>
+        <v>428.2731894805381</v>
       </c>
       <c r="D21">
-        <v>451.6099500248818</v>
+        <v>453.9131894805382</v>
       </c>
       <c r="E21">
-        <v>-97.67699999999999</v>
+        <v>-92.55999999999999</v>
       </c>
       <c r="F21">
-        <v>97.22300000000001</v>
+        <v>102.34</v>
       </c>
       <c r="G21">
         <v>76.7</v>
@@ -3009,28 +3009,28 @@
         <v>30.95</v>
       </c>
       <c r="M21">
-        <v>5.376431900000001</v>
+        <v>5.659402000000001</v>
       </c>
       <c r="N21">
-        <v>25.5735681</v>
+        <v>25.290598</v>
       </c>
       <c r="O21">
-        <v>8.183541792</v>
+        <v>8.092991359999999</v>
       </c>
       <c r="P21">
-        <v>17.390026308</v>
+        <v>17.19760664</v>
       </c>
       <c r="Q21">
-        <v>34.690026308</v>
+        <v>34.49760664</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1123497366292003</v>
+        <v>0.1129520287515898</v>
       </c>
       <c r="T21">
-        <v>0.8673661630578773</v>
+        <v>0.8752160484773747</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.756605975051966</v>
+        <v>5.468775676299368</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09788242300127184</v>
+        <v>0.09761679933289145</v>
       </c>
       <c r="C22">
-        <v>428.2731894805381</v>
+        <v>425.4830427032059</v>
       </c>
       <c r="D22">
-        <v>453.9131894805382</v>
+        <v>456.2400427032059</v>
       </c>
       <c r="E22">
-        <v>-92.55999999999999</v>
+        <v>-87.44299999999998</v>
       </c>
       <c r="F22">
-        <v>102.34</v>
+        <v>107.457</v>
       </c>
       <c r="G22">
         <v>76.7</v>
@@ -3091,28 +3091,28 @@
         <v>30.95</v>
       </c>
       <c r="M22">
-        <v>5.659402000000001</v>
+        <v>5.942372100000002</v>
       </c>
       <c r="N22">
-        <v>25.290598</v>
+        <v>25.0076279</v>
       </c>
       <c r="O22">
-        <v>8.092991359999999</v>
+        <v>8.002440927999999</v>
       </c>
       <c r="P22">
-        <v>17.19760664</v>
+        <v>17.005186972</v>
       </c>
       <c r="Q22">
-        <v>34.49760664</v>
+        <v>34.305186972</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1129520287515898</v>
+        <v>0.113569568775812</v>
       </c>
       <c r="T22">
-        <v>0.8752160484773747</v>
+        <v>0.883264665173315</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.468775676299368</v>
+        <v>5.208357786951778</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09761679933289145</v>
+        <v>0.09735117566451101</v>
       </c>
       <c r="C23">
-        <v>425.4830427032059</v>
+        <v>422.7168747112585</v>
       </c>
       <c r="D23">
-        <v>456.2400427032059</v>
+        <v>458.5908747112585</v>
       </c>
       <c r="E23">
-        <v>-87.443</v>
+        <v>-82.32599999999999</v>
       </c>
       <c r="F23">
-        <v>107.457</v>
+        <v>112.574</v>
       </c>
       <c r="G23">
         <v>76.7</v>
@@ -3173,28 +3173,28 @@
         <v>30.95</v>
       </c>
       <c r="M23">
-        <v>5.942372100000001</v>
+        <v>6.225342200000001</v>
       </c>
       <c r="N23">
-        <v>25.0076279</v>
+        <v>24.7246578</v>
       </c>
       <c r="O23">
-        <v>8.002440928</v>
+        <v>7.911890496</v>
       </c>
       <c r="P23">
-        <v>17.005186972</v>
+        <v>16.812767304</v>
       </c>
       <c r="Q23">
-        <v>34.305186972</v>
+        <v>34.112767304</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.113569568775812</v>
+        <v>0.1142029431596295</v>
       </c>
       <c r="T23">
-        <v>0.883264665173315</v>
+        <v>0.8915196566563309</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.208357786951779</v>
+        <v>4.971614251181244</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09735117566451101</v>
+        <v>0.09708555199613059</v>
       </c>
       <c r="C24">
-        <v>422.7168747112585</v>
+        <v>419.9750580852384</v>
       </c>
       <c r="D24">
-        <v>458.5908747112585</v>
+        <v>460.9660580852384</v>
       </c>
       <c r="E24">
-        <v>-82.32599999999999</v>
+        <v>-77.20899999999999</v>
       </c>
       <c r="F24">
-        <v>112.574</v>
+        <v>117.691</v>
       </c>
       <c r="G24">
         <v>76.7</v>
@@ -3255,28 +3255,28 @@
         <v>30.95</v>
       </c>
       <c r="M24">
-        <v>6.225342200000001</v>
+        <v>6.508312300000001</v>
       </c>
       <c r="N24">
-        <v>24.7246578</v>
+        <v>24.4416877</v>
       </c>
       <c r="O24">
-        <v>7.911890496</v>
+        <v>7.821340064</v>
       </c>
       <c r="P24">
-        <v>16.812767304</v>
+        <v>16.620347636</v>
       </c>
       <c r="Q24">
-        <v>34.112767304</v>
+        <v>33.920347636</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1142029431596295</v>
+        <v>0.1148527688261436</v>
       </c>
       <c r="T24">
-        <v>0.8915196566563309</v>
+        <v>0.8999890635025417</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.971614251181244</v>
+        <v>4.755457109825537</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09708555199613059</v>
+        <v>0.09681992832775019</v>
       </c>
       <c r="C25">
-        <v>419.9750580852384</v>
+        <v>417.2579731647124</v>
       </c>
       <c r="D25">
-        <v>460.9660580852384</v>
+        <v>463.3659731647124</v>
       </c>
       <c r="E25">
-        <v>-77.20899999999999</v>
+        <v>-72.09199999999998</v>
       </c>
       <c r="F25">
-        <v>117.691</v>
+        <v>122.808</v>
       </c>
       <c r="G25">
         <v>76.7</v>
@@ -3337,28 +3337,28 @@
         <v>30.95</v>
       </c>
       <c r="M25">
-        <v>6.508312300000001</v>
+        <v>6.791282400000002</v>
       </c>
       <c r="N25">
-        <v>24.4416877</v>
+        <v>24.1587176</v>
       </c>
       <c r="O25">
-        <v>7.821340064</v>
+        <v>7.730789631999999</v>
       </c>
       <c r="P25">
-        <v>16.620347636</v>
+        <v>16.427927968</v>
       </c>
       <c r="Q25">
-        <v>33.920347636</v>
+        <v>33.727927968</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1148527688261436</v>
+        <v>0.1155196951680924</v>
       </c>
       <c r="T25">
-        <v>0.8999890635025417</v>
+        <v>0.9086813494762846</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.755457109825537</v>
+        <v>4.557313063582805</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09681992832775019</v>
+        <v>0.09697930465936976</v>
       </c>
       <c r="C26">
-        <v>417.2579731647124</v>
+        <v>410.6980155182217</v>
       </c>
       <c r="D26">
-        <v>463.3659731647124</v>
+        <v>461.9230155182216</v>
       </c>
       <c r="E26">
-        <v>-72.092</v>
+        <v>-66.97499999999999</v>
       </c>
       <c r="F26">
-        <v>122.808</v>
+        <v>127.925</v>
       </c>
       <c r="G26">
         <v>76.7</v>
@@ -3419,45 +3419,45 @@
         <v>30.95</v>
       </c>
       <c r="M26">
-        <v>6.791282400000001</v>
+        <v>7.394065000000001</v>
       </c>
       <c r="N26">
-        <v>24.1587176</v>
+        <v>23.555935</v>
       </c>
       <c r="O26">
-        <v>7.730789632</v>
+        <v>7.537899199999999</v>
       </c>
       <c r="P26">
-        <v>16.427927968</v>
+        <v>16.0180358</v>
       </c>
       <c r="Q26">
-        <v>33.727927968</v>
+        <v>33.3180358</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1155196951680924</v>
+        <v>0.116204406212493</v>
       </c>
       <c r="T26">
-        <v>0.9086813494762846</v>
+        <v>0.9176054297426606</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.32</v>
       </c>
       <c r="W26">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.557313063582807</v>
+        <v>4.185789548780001</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09697930465936976</v>
+        <v>0.09673068099098936</v>
       </c>
       <c r="C27">
-        <v>410.6980155182217</v>
+        <v>407.8359430470288</v>
       </c>
       <c r="D27">
-        <v>461.9230155182216</v>
+        <v>464.1779430470287</v>
       </c>
       <c r="E27">
-        <v>-66.97499999999999</v>
+        <v>-61.85799999999998</v>
       </c>
       <c r="F27">
-        <v>127.925</v>
+        <v>133.042</v>
       </c>
       <c r="G27">
         <v>76.7</v>
@@ -3501,28 +3501,28 @@
         <v>30.95</v>
       </c>
       <c r="M27">
-        <v>7.394065000000001</v>
+        <v>7.689827600000002</v>
       </c>
       <c r="N27">
-        <v>23.555935</v>
+        <v>23.2601724</v>
       </c>
       <c r="O27">
-        <v>7.537899199999999</v>
+        <v>7.443255167999999</v>
       </c>
       <c r="P27">
-        <v>16.0180358</v>
+        <v>15.816917232</v>
       </c>
       <c r="Q27">
-        <v>33.3180358</v>
+        <v>33.116917232</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.116204406212493</v>
+        <v>0.1169076229607964</v>
       </c>
       <c r="T27">
-        <v>0.9176054297426606</v>
+        <v>0.9267707013675873</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.185789548780001</v>
+        <v>4.024797643057692</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09673068099098936</v>
+        <v>0.09712465732260893</v>
       </c>
       <c r="C28">
-        <v>407.8359430470288</v>
+        <v>399.1558384349337</v>
       </c>
       <c r="D28">
-        <v>464.1779430470287</v>
+        <v>460.6148384349337</v>
       </c>
       <c r="E28">
-        <v>-61.85799999999998</v>
+        <v>-56.74099999999999</v>
       </c>
       <c r="F28">
-        <v>133.042</v>
+        <v>138.159</v>
       </c>
       <c r="G28">
         <v>76.7</v>
@@ -3583,45 +3583,45 @@
         <v>30.95</v>
       </c>
       <c r="M28">
-        <v>7.689827600000002</v>
+        <v>8.469146700000001</v>
       </c>
       <c r="N28">
-        <v>23.2601724</v>
+        <v>22.4808533</v>
       </c>
       <c r="O28">
-        <v>7.443255167999999</v>
+        <v>7.193873056</v>
       </c>
       <c r="P28">
-        <v>15.816917232</v>
+        <v>15.286980244</v>
       </c>
       <c r="Q28">
-        <v>33.116917232</v>
+        <v>32.586980244</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1169076229607964</v>
+        <v>0.1176301059213821</v>
       </c>
       <c r="T28">
-        <v>0.9267707013675873</v>
+        <v>0.9361870763247038</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.32</v>
       </c>
       <c r="W28">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.024797643057692</v>
+        <v>3.654441361843454</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09712465732260893</v>
+        <v>0.09689983365422852</v>
       </c>
       <c r="C29">
-        <v>399.1558384349337</v>
+        <v>396.0654031080815</v>
       </c>
       <c r="D29">
-        <v>460.6148384349337</v>
+        <v>462.6414031080815</v>
       </c>
       <c r="E29">
-        <v>-56.74099999999999</v>
+        <v>-51.62399999999997</v>
       </c>
       <c r="F29">
-        <v>138.159</v>
+        <v>143.276</v>
       </c>
       <c r="G29">
         <v>76.7</v>
@@ -3665,28 +3665,28 @@
         <v>30.95</v>
       </c>
       <c r="M29">
-        <v>8.469146700000001</v>
+        <v>8.782818800000003</v>
       </c>
       <c r="N29">
-        <v>22.4808533</v>
+        <v>22.16718119999999</v>
       </c>
       <c r="O29">
-        <v>7.193873056</v>
+        <v>7.093497983999998</v>
       </c>
       <c r="P29">
-        <v>15.286980244</v>
+        <v>15.073683216</v>
       </c>
       <c r="Q29">
-        <v>32.586980244</v>
+        <v>32.373683216</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1176301059213821</v>
+        <v>0.1183726578530952</v>
       </c>
       <c r="T29">
-        <v>0.9361870763247038</v>
+        <v>0.9458650172528513</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.654441361843454</v>
+        <v>3.523925598920473</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09689983365422852</v>
+        <v>0.0972271699858481</v>
       </c>
       <c r="C30">
-        <v>396.0654031080815</v>
+        <v>388.0036690348201</v>
       </c>
       <c r="D30">
-        <v>462.6414031080815</v>
+        <v>459.69666903482</v>
       </c>
       <c r="E30">
-        <v>-51.62399999999997</v>
+        <v>-46.50699999999998</v>
       </c>
       <c r="F30">
-        <v>143.276</v>
+        <v>148.393</v>
       </c>
       <c r="G30">
         <v>76.7</v>
@@ -3747,45 +3747,45 @@
         <v>30.95</v>
       </c>
       <c r="M30">
-        <v>8.782818800000003</v>
+        <v>9.511991300000002</v>
       </c>
       <c r="N30">
-        <v>22.16718119999999</v>
+        <v>21.4380087</v>
       </c>
       <c r="O30">
-        <v>7.093497983999998</v>
+        <v>6.860162783999999</v>
       </c>
       <c r="P30">
-        <v>15.073683216</v>
+        <v>14.577845916</v>
       </c>
       <c r="Q30">
-        <v>32.373683216</v>
+        <v>31.877845916</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1183726578530952</v>
+        <v>0.1191361267406311</v>
       </c>
       <c r="T30">
-        <v>0.9458650172528513</v>
+        <v>0.9558155762353127</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
       <c r="W30">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.523925598920473</v>
+        <v>3.25378766904465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0972271699858481</v>
+        <v>0.09702138631746768</v>
       </c>
       <c r="C31">
-        <v>388.0036690348201</v>
+        <v>384.7335160980748</v>
       </c>
       <c r="D31">
-        <v>459.69666903482</v>
+        <v>461.5435160980747</v>
       </c>
       <c r="E31">
-        <v>-46.50700000000001</v>
+        <v>-41.38999999999999</v>
       </c>
       <c r="F31">
-        <v>148.393</v>
+        <v>153.51</v>
       </c>
       <c r="G31">
         <v>76.7</v>
@@ -3829,28 +3829,28 @@
         <v>30.95</v>
       </c>
       <c r="M31">
-        <v>9.5119913</v>
+        <v>9.839991000000001</v>
       </c>
       <c r="N31">
-        <v>21.4380087</v>
+        <v>21.110009</v>
       </c>
       <c r="O31">
-        <v>6.860162783999999</v>
+        <v>6.75520288</v>
       </c>
       <c r="P31">
-        <v>14.577845916</v>
+        <v>14.35480612</v>
       </c>
       <c r="Q31">
-        <v>31.877845916</v>
+        <v>31.65480612</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1191361267406311</v>
+        <v>0.1199214090249538</v>
       </c>
       <c r="T31">
-        <v>0.9558155762353127</v>
+        <v>0.9660504369029874</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.253787669044651</v>
+        <v>3.145328080076495</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09702138631746768</v>
+        <v>0.09681560264908726</v>
       </c>
       <c r="C32">
-        <v>384.7335160980748</v>
+        <v>381.4782625624489</v>
       </c>
       <c r="D32">
-        <v>461.5435160980747</v>
+        <v>463.405262562449</v>
       </c>
       <c r="E32">
-        <v>-41.38999999999999</v>
+        <v>-36.273</v>
       </c>
       <c r="F32">
-        <v>153.51</v>
+        <v>158.627</v>
       </c>
       <c r="G32">
         <v>76.7</v>
@@ -3911,28 +3911,28 @@
         <v>30.95</v>
       </c>
       <c r="M32">
-        <v>9.839991000000001</v>
+        <v>10.1679907</v>
       </c>
       <c r="N32">
-        <v>21.110009</v>
+        <v>20.7820093</v>
       </c>
       <c r="O32">
-        <v>6.75520288</v>
+        <v>6.650242975999999</v>
       </c>
       <c r="P32">
-        <v>14.35480612</v>
+        <v>14.131766324</v>
       </c>
       <c r="Q32">
-        <v>31.65480612</v>
+        <v>31.431766324</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1199214090249538</v>
+        <v>0.1207294531146192</v>
       </c>
       <c r="T32">
-        <v>0.9660504369029874</v>
+        <v>0.9765819601987107</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.145328080076495</v>
+        <v>3.043865883944996</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09681560264908726</v>
+        <v>0.09830709898070684</v>
       </c>
       <c r="C33">
-        <v>381.4782625624489</v>
+        <v>363.1979520276379</v>
       </c>
       <c r="D33">
-        <v>463.405262562449</v>
+        <v>450.2419520276379</v>
       </c>
       <c r="E33">
-        <v>-36.273</v>
+        <v>-31.15599999999998</v>
       </c>
       <c r="F33">
-        <v>158.627</v>
+        <v>163.744</v>
       </c>
       <c r="G33">
         <v>76.7</v>
@@ -3993,45 +3993,45 @@
         <v>30.95</v>
       </c>
       <c r="M33">
-        <v>10.1679907</v>
+        <v>11.7731936</v>
       </c>
       <c r="N33">
-        <v>20.7820093</v>
+        <v>19.1768064</v>
       </c>
       <c r="O33">
-        <v>6.650242975999999</v>
+        <v>6.136578047999999</v>
       </c>
       <c r="P33">
-        <v>14.131766324</v>
+        <v>13.040228352</v>
       </c>
       <c r="Q33">
-        <v>31.431766324</v>
+        <v>30.340228352</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1207294531146192</v>
+        <v>0.1215612632069218</v>
       </c>
       <c r="T33">
-        <v>0.9765819601987107</v>
+        <v>0.9874232341796022</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.32</v>
       </c>
       <c r="W33">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.043865883944996</v>
+        <v>2.628853397942933</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09830709898070684</v>
+        <v>0.09815435531232643</v>
       </c>
       <c r="C34">
-        <v>363.1979520276379</v>
+        <v>359.3945315188033</v>
       </c>
       <c r="D34">
-        <v>450.2419520276379</v>
+        <v>451.5555315188033</v>
       </c>
       <c r="E34">
-        <v>-31.15599999999998</v>
+        <v>-26.03899999999999</v>
       </c>
       <c r="F34">
-        <v>163.744</v>
+        <v>168.861</v>
       </c>
       <c r="G34">
         <v>76.7</v>
@@ -4075,28 +4075,28 @@
         <v>30.95</v>
       </c>
       <c r="M34">
-        <v>11.7731936</v>
+        <v>12.1411059</v>
       </c>
       <c r="N34">
-        <v>19.1768064</v>
+        <v>18.8088941</v>
       </c>
       <c r="O34">
-        <v>6.136578047999999</v>
+        <v>6.018846111999999</v>
       </c>
       <c r="P34">
-        <v>13.040228352</v>
+        <v>12.790047988</v>
       </c>
       <c r="Q34">
-        <v>30.340228352</v>
+        <v>30.090047988</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1215612632069218</v>
+        <v>0.1224179034512335</v>
       </c>
       <c r="T34">
-        <v>0.9874232341796022</v>
+        <v>0.9985881282793264</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.628853397942933</v>
+        <v>2.549191173762844</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09815435531232643</v>
+        <v>0.09890329164394601</v>
       </c>
       <c r="C35">
-        <v>359.3945315188033</v>
+        <v>347.9090686075823</v>
       </c>
       <c r="D35">
-        <v>451.5555315188033</v>
+        <v>445.1870686075824</v>
       </c>
       <c r="E35">
-        <v>-26.03899999999999</v>
+        <v>-20.92199999999997</v>
       </c>
       <c r="F35">
-        <v>168.861</v>
+        <v>173.978</v>
       </c>
       <c r="G35">
         <v>76.7</v>
@@ -4157,45 +4157,45 @@
         <v>30.95</v>
       </c>
       <c r="M35">
-        <v>12.1411059</v>
+        <v>13.1875324</v>
       </c>
       <c r="N35">
-        <v>18.8088941</v>
+        <v>17.76246759999999</v>
       </c>
       <c r="O35">
-        <v>6.018846111999999</v>
+        <v>5.683989631999999</v>
       </c>
       <c r="P35">
-        <v>12.790047988</v>
+        <v>12.07847796799999</v>
       </c>
       <c r="Q35">
-        <v>30.090047988</v>
+        <v>29.378477968</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1224179034512335</v>
+        <v>0.1233005024908273</v>
       </c>
       <c r="T35">
-        <v>0.9985881282793264</v>
+        <v>1.010091352503285</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.32</v>
       </c>
       <c r="W35">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.549191173762844</v>
+        <v>2.34691366521306</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09890329164394601</v>
+        <v>0.0987770679755656</v>
       </c>
       <c r="C36">
-        <v>347.9090686075823</v>
+        <v>343.8527755712273</v>
       </c>
       <c r="D36">
-        <v>445.1870686075824</v>
+        <v>446.2477755712273</v>
       </c>
       <c r="E36">
-        <v>-20.92199999999997</v>
+        <v>-15.80499999999998</v>
       </c>
       <c r="F36">
-        <v>173.978</v>
+        <v>179.095</v>
       </c>
       <c r="G36">
         <v>76.7</v>
@@ -4239,28 +4239,28 @@
         <v>30.95</v>
       </c>
       <c r="M36">
-        <v>13.1875324</v>
+        <v>13.575401</v>
       </c>
       <c r="N36">
-        <v>17.76246759999999</v>
+        <v>17.374599</v>
       </c>
       <c r="O36">
-        <v>5.683989631999999</v>
+        <v>5.559871679999999</v>
       </c>
       <c r="P36">
-        <v>12.07847796799999</v>
+        <v>11.81472732</v>
       </c>
       <c r="Q36">
-        <v>29.378477968</v>
+        <v>29.11472732</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1233005024908273</v>
+        <v>0.1242102584239471</v>
       </c>
       <c r="T36">
-        <v>1.010091352503285</v>
+        <v>1.02194852208798</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.34691366521306</v>
+        <v>2.279858989064116</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0987770679755656</v>
+        <v>0.09865084430718518</v>
       </c>
       <c r="C37">
-        <v>343.8527755712273</v>
+        <v>339.8015491076312</v>
       </c>
       <c r="D37">
-        <v>446.2477755712273</v>
+        <v>447.3135491076312</v>
       </c>
       <c r="E37">
-        <v>-15.80499999999998</v>
+        <v>-10.68799999999996</v>
       </c>
       <c r="F37">
-        <v>179.095</v>
+        <v>184.212</v>
       </c>
       <c r="G37">
         <v>76.7</v>
@@ -4321,28 +4321,28 @@
         <v>30.95</v>
       </c>
       <c r="M37">
-        <v>13.575401</v>
+        <v>13.9632696</v>
       </c>
       <c r="N37">
-        <v>17.374599</v>
+        <v>16.9867304</v>
       </c>
       <c r="O37">
-        <v>5.559871679999999</v>
+        <v>5.435753727999999</v>
       </c>
       <c r="P37">
-        <v>11.81472732</v>
+        <v>11.550976672</v>
       </c>
       <c r="Q37">
-        <v>29.11472732</v>
+        <v>28.850976672</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1242102584239471</v>
+        <v>0.1251484442299769</v>
       </c>
       <c r="T37">
-        <v>1.02194852208798</v>
+        <v>1.034176228222197</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.279858989064116</v>
+        <v>2.216529572701224</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09865084430718518</v>
+        <v>0.09852462063880477</v>
       </c>
       <c r="C38">
-        <v>339.8015491076312</v>
+        <v>335.7554256051868</v>
       </c>
       <c r="D38">
-        <v>447.3135491076312</v>
+        <v>448.3844256051867</v>
       </c>
       <c r="E38">
-        <v>-10.68799999999999</v>
+        <v>-5.570999999999998</v>
       </c>
       <c r="F38">
-        <v>184.212</v>
+        <v>189.329</v>
       </c>
       <c r="G38">
         <v>76.7</v>
@@ -4403,28 +4403,28 @@
         <v>30.95</v>
       </c>
       <c r="M38">
-        <v>13.9632696</v>
+        <v>14.3511382</v>
       </c>
       <c r="N38">
-        <v>16.9867304</v>
+        <v>16.5988618</v>
       </c>
       <c r="O38">
-        <v>5.435753728</v>
+        <v>5.311635775999999</v>
       </c>
       <c r="P38">
-        <v>11.550976672</v>
+        <v>11.287226024</v>
       </c>
       <c r="Q38">
-        <v>28.850976672</v>
+        <v>28.587226024</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1251484442299768</v>
+        <v>0.1261164137123885</v>
       </c>
       <c r="T38">
-        <v>1.034176228222197</v>
+        <v>1.046792115503532</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.216529572701225</v>
+        <v>2.156623368033624</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09852462063880477</v>
+        <v>0.09839839697042435</v>
       </c>
       <c r="C39">
-        <v>335.7554256051868</v>
+        <v>331.7144418015806</v>
       </c>
       <c r="D39">
-        <v>448.3844256051867</v>
+        <v>449.4604418015806</v>
       </c>
       <c r="E39">
-        <v>-5.570999999999998</v>
+        <v>-0.4539999999999793</v>
       </c>
       <c r="F39">
-        <v>189.329</v>
+        <v>194.446</v>
       </c>
       <c r="G39">
         <v>76.7</v>
@@ -4485,28 +4485,28 @@
         <v>30.95</v>
       </c>
       <c r="M39">
-        <v>14.3511382</v>
+        <v>14.7390068</v>
       </c>
       <c r="N39">
-        <v>16.5988618</v>
+        <v>16.2109932</v>
       </c>
       <c r="O39">
-        <v>5.311635775999999</v>
+        <v>5.187517824</v>
       </c>
       <c r="P39">
-        <v>11.287226024</v>
+        <v>11.023475376</v>
       </c>
       <c r="Q39">
-        <v>28.587226024</v>
+        <v>28.323475376</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1261164137123885</v>
+        <v>0.1271156080168135</v>
       </c>
       <c r="T39">
-        <v>1.046792115503532</v>
+        <v>1.059814966890717</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.156623368033624</v>
+        <v>2.099870121506423</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09839839697042435</v>
+        <v>0.09827217330204394</v>
       </c>
       <c r="C40">
-        <v>331.7144418015806</v>
+        <v>327.6786347879948</v>
       </c>
       <c r="D40">
-        <v>449.4604418015806</v>
+        <v>450.5416347879948</v>
       </c>
       <c r="E40">
-        <v>-0.4539999999999793</v>
+        <v>4.663000000000011</v>
       </c>
       <c r="F40">
-        <v>194.446</v>
+        <v>199.563</v>
       </c>
       <c r="G40">
         <v>76.7</v>
@@ -4567,28 +4567,28 @@
         <v>30.95</v>
       </c>
       <c r="M40">
-        <v>14.7390068</v>
+        <v>15.1268754</v>
       </c>
       <c r="N40">
-        <v>16.2109932</v>
+        <v>15.8231246</v>
       </c>
       <c r="O40">
-        <v>5.187517824</v>
+        <v>5.063399871999999</v>
       </c>
       <c r="P40">
-        <v>11.023475376</v>
+        <v>10.759724728</v>
       </c>
       <c r="Q40">
-        <v>28.323475376</v>
+        <v>28.059724728</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1271156080168135</v>
+        <v>0.128147562790236</v>
       </c>
       <c r="T40">
-        <v>1.059814966890717</v>
+        <v>1.073264797011907</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.099870121506423</v>
+        <v>2.046027297878053</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09827217330204394</v>
+        <v>0.1020083496336635</v>
       </c>
       <c r="C41">
-        <v>327.6786347879948</v>
+        <v>292.6140735577686</v>
       </c>
       <c r="D41">
-        <v>450.5416347879948</v>
+        <v>420.5940735577686</v>
       </c>
       <c r="E41">
-        <v>4.663000000000011</v>
+        <v>9.78000000000003</v>
       </c>
       <c r="F41">
-        <v>199.563</v>
+        <v>204.68</v>
       </c>
       <c r="G41">
         <v>76.7</v>
@@ -4649,45 +4649,45 @@
         <v>30.95</v>
       </c>
       <c r="M41">
-        <v>15.1268754</v>
+        <v>18.4212</v>
       </c>
       <c r="N41">
-        <v>15.8231246</v>
+        <v>12.5288</v>
       </c>
       <c r="O41">
-        <v>5.063399871999999</v>
+        <v>4.009215999999999</v>
       </c>
       <c r="P41">
-        <v>10.759724728</v>
+        <v>8.519583999999998</v>
       </c>
       <c r="Q41">
-        <v>28.059724728</v>
+        <v>25.819584</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.128147562790236</v>
+        <v>0.1292139160561059</v>
       </c>
       <c r="T41">
-        <v>1.073264797011907</v>
+        <v>1.087162954803804</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.32</v>
       </c>
       <c r="W41">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.046027297878053</v>
+        <v>1.680129416107528</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1020083496336635</v>
+        <v>0.1019786859652831</v>
       </c>
       <c r="C42">
-        <v>292.6140735577686</v>
+        <v>287.7191571274785</v>
       </c>
       <c r="D42">
-        <v>420.5940735577686</v>
+        <v>420.8161571274785</v>
       </c>
       <c r="E42">
-        <v>9.78000000000003</v>
+        <v>14.89700000000002</v>
       </c>
       <c r="F42">
-        <v>204.68</v>
+        <v>209.797</v>
       </c>
       <c r="G42">
         <v>76.7</v>
@@ -4731,28 +4731,28 @@
         <v>30.95</v>
       </c>
       <c r="M42">
-        <v>18.4212</v>
+        <v>18.88173</v>
       </c>
       <c r="N42">
-        <v>12.5288</v>
+        <v>12.06827</v>
       </c>
       <c r="O42">
-        <v>4.009215999999999</v>
+        <v>3.8618464</v>
       </c>
       <c r="P42">
-        <v>8.519583999999998</v>
+        <v>8.206423599999999</v>
       </c>
       <c r="Q42">
-        <v>25.819584</v>
+        <v>25.5064236</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1292139160561059</v>
+        <v>0.1303164168903103</v>
       </c>
       <c r="T42">
-        <v>1.087162954803804</v>
+        <v>1.101532236588647</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.680129416107528</v>
+        <v>1.639150649861003</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1019786859652831</v>
+        <v>0.1019490222969027</v>
       </c>
       <c r="C43">
-        <v>287.7191571274785</v>
+        <v>282.824475351795</v>
       </c>
       <c r="D43">
-        <v>420.8161571274785</v>
+        <v>421.0384753517951</v>
       </c>
       <c r="E43">
-        <v>14.89700000000002</v>
+        <v>20.01400000000004</v>
       </c>
       <c r="F43">
-        <v>209.797</v>
+        <v>214.914</v>
       </c>
       <c r="G43">
         <v>76.7</v>
@@ -4813,28 +4813,28 @@
         <v>30.95</v>
       </c>
       <c r="M43">
-        <v>18.88173</v>
+        <v>19.34226</v>
       </c>
       <c r="N43">
-        <v>12.06827</v>
+        <v>11.60774</v>
       </c>
       <c r="O43">
-        <v>3.8618464</v>
+        <v>3.714476799999999</v>
       </c>
       <c r="P43">
-        <v>8.206423599999999</v>
+        <v>7.893263199999997</v>
       </c>
       <c r="Q43">
-        <v>25.5064236</v>
+        <v>25.1932632</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1303164168903103</v>
+        <v>0.1314569349946598</v>
       </c>
       <c r="T43">
-        <v>1.101532236588647</v>
+        <v>1.116397010848829</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.639150649861003</v>
+        <v>1.600123253435741</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1019490222969027</v>
+        <v>0.1019193586285223</v>
       </c>
       <c r="C44">
-        <v>282.8244753517949</v>
+        <v>277.9300286028202</v>
       </c>
       <c r="D44">
-        <v>421.038475351795</v>
+        <v>421.2610286028203</v>
       </c>
       <c r="E44">
-        <v>20.01400000000001</v>
+        <v>25.131</v>
       </c>
       <c r="F44">
-        <v>214.914</v>
+        <v>220.031</v>
       </c>
       <c r="G44">
         <v>76.7</v>
@@ -4895,28 +4895,28 @@
         <v>30.95</v>
       </c>
       <c r="M44">
-        <v>19.34226</v>
+        <v>19.80279</v>
       </c>
       <c r="N44">
-        <v>11.60774</v>
+        <v>11.14721</v>
       </c>
       <c r="O44">
-        <v>3.7144768</v>
+        <v>3.567107200000001</v>
       </c>
       <c r="P44">
-        <v>7.8932632</v>
+        <v>7.580102800000001</v>
       </c>
       <c r="Q44">
-        <v>25.1932632</v>
+        <v>24.8801028</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1314569349946598</v>
+        <v>0.1326374712781092</v>
       </c>
       <c r="T44">
-        <v>1.116397010848829</v>
+        <v>1.131783356135684</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.600123253435741</v>
+        <v>1.562911084751189</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1019193586285223</v>
+        <v>0.1018896949601418</v>
       </c>
       <c r="C45">
-        <v>277.9300286028202</v>
+        <v>273.035817253444</v>
       </c>
       <c r="D45">
-        <v>421.2610286028203</v>
+        <v>421.483817253444</v>
       </c>
       <c r="E45">
-        <v>25.131</v>
+        <v>30.24800000000002</v>
       </c>
       <c r="F45">
-        <v>220.031</v>
+        <v>225.148</v>
       </c>
       <c r="G45">
         <v>76.7</v>
@@ -4977,28 +4977,28 @@
         <v>30.95</v>
       </c>
       <c r="M45">
-        <v>19.80279</v>
+        <v>20.26332</v>
       </c>
       <c r="N45">
-        <v>11.14721</v>
+        <v>10.68668</v>
       </c>
       <c r="O45">
-        <v>3.567107200000001</v>
+        <v>3.4197376</v>
       </c>
       <c r="P45">
-        <v>7.580102800000001</v>
+        <v>7.2669424</v>
       </c>
       <c r="Q45">
-        <v>24.8801028</v>
+        <v>24.5669424</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1326374712781092</v>
+        <v>0.1338601695716819</v>
       </c>
       <c r="T45">
-        <v>1.131783356135684</v>
+        <v>1.147719213754213</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.562911084751189</v>
+        <v>1.527390378279571</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1018896949601418</v>
+        <v>0.1217224796445165</v>
       </c>
       <c r="C46">
-        <v>273.035817253444</v>
+        <v>157.8170682763921</v>
       </c>
       <c r="D46">
-        <v>421.483817253444</v>
+        <v>311.3820682763921</v>
       </c>
       <c r="E46">
-        <v>30.24800000000002</v>
+        <v>35.36500000000001</v>
       </c>
       <c r="F46">
-        <v>225.148</v>
+        <v>230.265</v>
       </c>
       <c r="G46">
         <v>76.7</v>
@@ -5059,45 +5059,45 @@
         <v>30.95</v>
       </c>
       <c r="M46">
-        <v>20.26332</v>
+        <v>33.802902</v>
       </c>
       <c r="N46">
-        <v>10.68668</v>
+        <v>-2.852902000000004</v>
       </c>
       <c r="O46">
-        <v>3.4197376</v>
+        <v>-0.9129286400000013</v>
       </c>
       <c r="P46">
-        <v>7.2669424</v>
+        <v>-1.939973360000002</v>
       </c>
       <c r="Q46">
-        <v>24.5669424</v>
+        <v>15.36002664</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1338601695716819</v>
+        <v>0.1363955827601368</v>
       </c>
       <c r="T46">
-        <v>1.147719213754213</v>
+        <v>1.180764147069119</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.32</v>
+        <v>0.2929925957244736</v>
       </c>
       <c r="W46">
-        <v>0.06119999999999999</v>
+        <v>0.1037886869476473</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.527390378279571</v>
+        <v>0.9156018616389798</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1217224796445165</v>
+        <v>0.1227324796445165</v>
       </c>
       <c r="C47">
-        <v>157.8170682763921</v>
+        <v>148.6121214116564</v>
       </c>
       <c r="D47">
-        <v>311.3820682763921</v>
+        <v>307.2941214116564</v>
       </c>
       <c r="E47">
-        <v>35.36500000000001</v>
+        <v>40.48200000000003</v>
       </c>
       <c r="F47">
-        <v>230.265</v>
+        <v>235.382</v>
       </c>
       <c r="G47">
         <v>76.7</v>
@@ -5141,37 +5141,37 @@
         <v>30.95</v>
       </c>
       <c r="M47">
-        <v>33.802902</v>
+        <v>34.55407760000001</v>
       </c>
       <c r="N47">
-        <v>-2.852902000000004</v>
+        <v>-3.604077600000007</v>
       </c>
       <c r="O47">
-        <v>-0.9129286400000013</v>
+        <v>-1.153304832000002</v>
       </c>
       <c r="P47">
-        <v>-1.939973360000002</v>
+        <v>-2.450772768000005</v>
       </c>
       <c r="Q47">
-        <v>15.36002664</v>
+        <v>14.849227232</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1363955827601368</v>
+        <v>0.1380732787371764</v>
       </c>
       <c r="T47">
-        <v>1.180764147069119</v>
+        <v>1.202630149792622</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2929925957244736</v>
+        <v>0.2866231914695937</v>
       </c>
       <c r="W47">
-        <v>0.1037886869476473</v>
+        <v>0.1047237154922637</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9156018616389798</v>
+        <v>0.8956974733424803</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1227324796445165</v>
+        <v>0.1237424796445166</v>
       </c>
       <c r="C48">
-        <v>148.6121214116564</v>
+        <v>139.5131200172778</v>
       </c>
       <c r="D48">
-        <v>307.2941214116564</v>
+        <v>303.3121200172778</v>
       </c>
       <c r="E48">
-        <v>40.48200000000003</v>
+        <v>45.59900000000002</v>
       </c>
       <c r="F48">
-        <v>235.382</v>
+        <v>240.499</v>
       </c>
       <c r="G48">
         <v>76.7</v>
@@ -5223,37 +5223,37 @@
         <v>30.95</v>
       </c>
       <c r="M48">
-        <v>34.55407760000001</v>
+        <v>35.30525320000001</v>
       </c>
       <c r="N48">
-        <v>-3.604077600000007</v>
+        <v>-4.355253200000011</v>
       </c>
       <c r="O48">
-        <v>-1.153304832000002</v>
+        <v>-1.393681024000003</v>
       </c>
       <c r="P48">
-        <v>-2.450772768000005</v>
+        <v>-2.961572176000007</v>
       </c>
       <c r="Q48">
-        <v>14.849227232</v>
+        <v>14.33842782399999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1380732787371764</v>
+        <v>0.1398142839963684</v>
       </c>
       <c r="T48">
-        <v>1.202630149792622</v>
+        <v>1.22532128469437</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2866231914695937</v>
+        <v>0.2805248256936448</v>
       </c>
       <c r="W48">
-        <v>0.1047237154922637</v>
+        <v>0.105618955588173</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8956974733424803</v>
+        <v>0.8766400802926402</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1237424796445166</v>
+        <v>0.1247524796445166</v>
       </c>
       <c r="C49">
-        <v>139.5131200172778</v>
+        <v>130.5159981693413</v>
       </c>
       <c r="D49">
-        <v>303.3121200172778</v>
+        <v>299.4319981693414</v>
       </c>
       <c r="E49">
-        <v>45.59900000000002</v>
+        <v>50.71600000000004</v>
       </c>
       <c r="F49">
-        <v>240.499</v>
+        <v>245.616</v>
       </c>
       <c r="G49">
         <v>76.7</v>
@@ -5305,37 +5305,37 @@
         <v>30.95</v>
       </c>
       <c r="M49">
-        <v>35.30525320000001</v>
+        <v>36.05642880000001</v>
       </c>
       <c r="N49">
-        <v>-4.355253200000011</v>
+        <v>-5.106428800000007</v>
       </c>
       <c r="O49">
-        <v>-1.393681024000003</v>
+        <v>-1.634057216000002</v>
       </c>
       <c r="P49">
-        <v>-2.961572176000007</v>
+        <v>-3.472371584000005</v>
       </c>
       <c r="Q49">
-        <v>14.33842782399999</v>
+        <v>13.827628416</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1398142839963684</v>
+        <v>0.1416222509962986</v>
       </c>
       <c r="T49">
-        <v>1.22532128469437</v>
+        <v>1.248885155553876</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2805248256936448</v>
+        <v>0.274680558491694</v>
       </c>
       <c r="W49">
-        <v>0.105618955588173</v>
+        <v>0.1064768940134193</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8766400802926402</v>
+        <v>0.8583767452865436</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1247524796445166</v>
+        <v>0.1257624796445165</v>
       </c>
       <c r="C50">
-        <v>130.5159981693414</v>
+        <v>121.6168953694344</v>
       </c>
       <c r="D50">
-        <v>299.4319981693414</v>
+        <v>295.6498953694344</v>
       </c>
       <c r="E50">
-        <v>50.71600000000001</v>
+        <v>55.833</v>
       </c>
       <c r="F50">
-        <v>245.616</v>
+        <v>250.733</v>
       </c>
       <c r="G50">
         <v>76.7</v>
@@ -5387,37 +5387,37 @@
         <v>30.95</v>
       </c>
       <c r="M50">
-        <v>36.05642880000001</v>
+        <v>36.8076044</v>
       </c>
       <c r="N50">
-        <v>-5.106428800000007</v>
+        <v>-5.857604400000003</v>
       </c>
       <c r="O50">
-        <v>-1.634057216000002</v>
+        <v>-1.874433408000001</v>
       </c>
       <c r="P50">
-        <v>-3.472371584000005</v>
+        <v>-3.983170992000002</v>
       </c>
       <c r="Q50">
-        <v>13.827628416</v>
+        <v>13.316829008</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1416222509962986</v>
+        <v>0.1435011186628927</v>
       </c>
       <c r="T50">
-        <v>1.248885155553876</v>
+        <v>1.273373099780423</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.274680558491694</v>
+        <v>0.26907483280819</v>
       </c>
       <c r="W50">
-        <v>0.1064768940134193</v>
+        <v>0.1072998145437577</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8583767452865436</v>
+        <v>0.8408588525255938</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1257624796445165</v>
+        <v>0.1267724796445165</v>
       </c>
       <c r="C51">
-        <v>121.6168953694344</v>
+        <v>112.8121437329023</v>
       </c>
       <c r="D51">
-        <v>295.6498953694344</v>
+        <v>291.9621437329023</v>
       </c>
       <c r="E51">
-        <v>55.833</v>
+        <v>60.95000000000002</v>
       </c>
       <c r="F51">
-        <v>250.733</v>
+        <v>255.85</v>
       </c>
       <c r="G51">
         <v>76.7</v>
@@ -5469,37 +5469,37 @@
         <v>30.95</v>
       </c>
       <c r="M51">
-        <v>36.8076044</v>
+        <v>37.55878000000001</v>
       </c>
       <c r="N51">
-        <v>-5.857604400000003</v>
+        <v>-6.608780000000007</v>
       </c>
       <c r="O51">
-        <v>-1.874433408000001</v>
+        <v>-2.114809600000002</v>
       </c>
       <c r="P51">
-        <v>-3.983170992000002</v>
+        <v>-4.493970400000004</v>
       </c>
       <c r="Q51">
-        <v>13.316829008</v>
+        <v>12.8060296</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1435011186628927</v>
+        <v>0.1454551410361505</v>
       </c>
       <c r="T51">
-        <v>1.273373099780423</v>
+        <v>1.298840561776032</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.26907483280819</v>
+        <v>0.2636933361520262</v>
       </c>
       <c r="W51">
-        <v>0.1072998145437577</v>
+        <v>0.1080898182528826</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8408588525255938</v>
+        <v>0.8240416754750819</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1267724796445165</v>
+        <v>0.1277824796445166</v>
       </c>
       <c r="C52">
-        <v>112.8121437329023</v>
+        <v>104.0982561241245</v>
       </c>
       <c r="D52">
-        <v>291.9621437329023</v>
+        <v>288.3652561241246</v>
       </c>
       <c r="E52">
-        <v>60.95000000000002</v>
+        <v>66.06700000000004</v>
       </c>
       <c r="F52">
-        <v>255.85</v>
+        <v>260.967</v>
       </c>
       <c r="G52">
         <v>76.7</v>
@@ -5551,37 +5551,37 @@
         <v>30.95</v>
       </c>
       <c r="M52">
-        <v>37.55878000000001</v>
+        <v>38.30995560000001</v>
       </c>
       <c r="N52">
-        <v>-6.608780000000007</v>
+        <v>-7.35995560000001</v>
       </c>
       <c r="O52">
-        <v>-2.114809600000002</v>
+        <v>-2.355185792000003</v>
       </c>
       <c r="P52">
-        <v>-4.493970400000004</v>
+        <v>-5.004769808000006</v>
       </c>
       <c r="Q52">
-        <v>12.8060296</v>
+        <v>12.29523019199999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1454551410361505</v>
+        <v>0.1474889194246434</v>
       </c>
       <c r="T52">
-        <v>1.298840561776032</v>
+        <v>1.325347512016359</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2636933361520262</v>
+        <v>0.2585228785804178</v>
       </c>
       <c r="W52">
-        <v>0.1080898182528826</v>
+        <v>0.1088488414243947</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8240416754750819</v>
+        <v>0.8078839955638056</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1277824796445166</v>
+        <v>0.1589075174729203</v>
       </c>
       <c r="C53">
-        <v>104.0982561241245</v>
+        <v>19.62862151776824</v>
       </c>
       <c r="D53">
-        <v>288.3652561241246</v>
+        <v>209.0126215177683</v>
       </c>
       <c r="E53">
-        <v>66.06700000000004</v>
+        <v>71.18400000000005</v>
       </c>
       <c r="F53">
-        <v>260.967</v>
+        <v>266.0840000000001</v>
       </c>
       <c r="G53">
         <v>76.7</v>
@@ -5633,45 +5633,45 @@
         <v>30.95</v>
       </c>
       <c r="M53">
-        <v>38.30995560000001</v>
+        <v>53.42966720000001</v>
       </c>
       <c r="N53">
-        <v>-7.35995560000001</v>
+        <v>-22.47966720000001</v>
       </c>
       <c r="O53">
-        <v>-2.355185792000003</v>
+        <v>-7.193493504000004</v>
       </c>
       <c r="P53">
-        <v>-5.004769808000006</v>
+        <v>-15.28617369600001</v>
       </c>
       <c r="Q53">
-        <v>12.29523019199999</v>
+        <v>2.013826303999991</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1474889194246434</v>
+        <v>0.1538471007218312</v>
       </c>
       <c r="T53">
-        <v>1.325347512016359</v>
+        <v>1.408215928859174</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.2585228785804178</v>
+        <v>0.1853651822858443</v>
       </c>
       <c r="W53">
-        <v>0.1088488414243947</v>
+        <v>0.1635786713970025</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8078839955638056</v>
+        <v>0.5792661946432636</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1589075174729203</v>
+        <v>0.1604575174729203</v>
       </c>
       <c r="C54">
-        <v>19.62862151776824</v>
+        <v>11.68608010981779</v>
       </c>
       <c r="D54">
-        <v>209.0126215177683</v>
+        <v>206.1870801098178</v>
       </c>
       <c r="E54">
-        <v>71.18400000000005</v>
+        <v>76.30100000000002</v>
       </c>
       <c r="F54">
-        <v>266.0840000000001</v>
+        <v>271.201</v>
       </c>
       <c r="G54">
         <v>76.7</v>
@@ -5715,37 +5715,37 @@
         <v>30.95</v>
       </c>
       <c r="M54">
-        <v>53.42966720000001</v>
+        <v>54.4571608</v>
       </c>
       <c r="N54">
-        <v>-22.47966720000001</v>
+        <v>-23.5071608</v>
       </c>
       <c r="O54">
-        <v>-7.193493504000004</v>
+        <v>-7.522291456000001</v>
       </c>
       <c r="P54">
-        <v>-15.28617369600001</v>
+        <v>-15.984869344</v>
       </c>
       <c r="Q54">
-        <v>2.013826303999991</v>
+        <v>1.315130655999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1538471007218312</v>
+        <v>0.1561459752052744</v>
       </c>
       <c r="T54">
-        <v>1.408215928859174</v>
+        <v>1.438177969898731</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1853651822858443</v>
+        <v>0.1818677260163001</v>
       </c>
       <c r="W54">
-        <v>0.1635786713970025</v>
+        <v>0.164280960615927</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5792661946432636</v>
+        <v>0.5683366438009378</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1604575174729203</v>
+        <v>0.1620075174729202</v>
       </c>
       <c r="C55">
-        <v>11.68608010981779</v>
+        <v>3.818914017983957</v>
       </c>
       <c r="D55">
-        <v>206.1870801098178</v>
+        <v>203.436914017984</v>
       </c>
       <c r="E55">
-        <v>76.30100000000002</v>
+        <v>81.41800000000003</v>
       </c>
       <c r="F55">
-        <v>271.201</v>
+        <v>276.318</v>
       </c>
       <c r="G55">
         <v>76.7</v>
@@ -5797,37 +5797,37 @@
         <v>30.95</v>
       </c>
       <c r="M55">
-        <v>54.4571608</v>
+        <v>55.48465440000001</v>
       </c>
       <c r="N55">
-        <v>-23.5071608</v>
+        <v>-24.53465440000001</v>
       </c>
       <c r="O55">
-        <v>-7.522291456000001</v>
+        <v>-7.851089408000004</v>
       </c>
       <c r="P55">
-        <v>-15.984869344</v>
+        <v>-16.68356499200001</v>
       </c>
       <c r="Q55">
-        <v>1.315130655999997</v>
+        <v>0.6164350079999927</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1561459752052744</v>
+        <v>0.1585448007532152</v>
       </c>
       <c r="T55">
-        <v>1.438177969898731</v>
+        <v>1.46944270837479</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1818677260163001</v>
+        <v>0.1784998051641464</v>
       </c>
       <c r="W55">
-        <v>0.164280960615927</v>
+        <v>0.1649572391230394</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5683366438009378</v>
+        <v>0.5578118911379575</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1620075174729202</v>
+        <v>0.1635575174729202</v>
       </c>
       <c r="C56">
-        <v>3.818914017983957</v>
+        <v>-3.97585317255141</v>
       </c>
       <c r="D56">
-        <v>203.436914017984</v>
+        <v>200.7591468274486</v>
       </c>
       <c r="E56">
-        <v>81.41800000000003</v>
+        <v>86.53500000000005</v>
       </c>
       <c r="F56">
-        <v>276.318</v>
+        <v>281.4350000000001</v>
       </c>
       <c r="G56">
         <v>76.7</v>
@@ -5879,37 +5879,37 @@
         <v>30.95</v>
       </c>
       <c r="M56">
-        <v>55.48465440000001</v>
+        <v>56.51214800000001</v>
       </c>
       <c r="N56">
-        <v>-24.53465440000001</v>
+        <v>-25.56214800000001</v>
       </c>
       <c r="O56">
-        <v>-7.851089408000004</v>
+        <v>-8.179887360000004</v>
       </c>
       <c r="P56">
-        <v>-16.68356499200001</v>
+        <v>-17.38226064000001</v>
       </c>
       <c r="Q56">
-        <v>0.6164350079999927</v>
+        <v>-0.08226064000000477</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1585448007532152</v>
+        <v>0.1610502407699533</v>
       </c>
       <c r="T56">
-        <v>1.46944270837479</v>
+        <v>1.502096990783119</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1784998051641464</v>
+        <v>0.1752543541611619</v>
       </c>
       <c r="W56">
-        <v>0.1649572391230394</v>
+        <v>0.1656089256844387</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5578118911379575</v>
+        <v>0.547669856753631</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1635575174729202</v>
+        <v>0.1651075174729203</v>
       </c>
       <c r="C57">
-        <v>-3.97585317255141</v>
+        <v>-11.70104320259861</v>
       </c>
       <c r="D57">
-        <v>200.7591468274486</v>
+        <v>198.1509567974015</v>
       </c>
       <c r="E57">
-        <v>86.53500000000005</v>
+        <v>91.65200000000007</v>
       </c>
       <c r="F57">
-        <v>281.4350000000001</v>
+        <v>286.5520000000001</v>
       </c>
       <c r="G57">
         <v>76.7</v>
@@ -5961,37 +5961,37 @@
         <v>30.95</v>
       </c>
       <c r="M57">
-        <v>56.51214800000001</v>
+        <v>57.53964160000002</v>
       </c>
       <c r="N57">
-        <v>-25.56214800000001</v>
+        <v>-26.58964160000002</v>
       </c>
       <c r="O57">
-        <v>-8.179887360000004</v>
+        <v>-8.508685312000006</v>
       </c>
       <c r="P57">
-        <v>-17.38226064000001</v>
+        <v>-18.08095628800001</v>
       </c>
       <c r="Q57">
-        <v>-0.08226064000000477</v>
+        <v>-0.7809562880000094</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1610502407699533</v>
+        <v>0.1636695644238159</v>
       </c>
       <c r="T57">
-        <v>1.502096990783119</v>
+        <v>1.536235558755463</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1752543541611619</v>
+        <v>0.1721248121225697</v>
       </c>
       <c r="W57">
-        <v>0.1656089256844387</v>
+        <v>0.166237337725788</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.547669856753631</v>
+        <v>0.5378900378830304</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1651075174729203</v>
+        <v>0.1666575174729203</v>
       </c>
       <c r="C58">
-        <v>-11.70104320259861</v>
+        <v>-19.35933305744601</v>
       </c>
       <c r="D58">
-        <v>198.1509567974015</v>
+        <v>195.609666942554</v>
       </c>
       <c r="E58">
-        <v>91.65200000000007</v>
+        <v>96.76900000000003</v>
       </c>
       <c r="F58">
-        <v>286.5520000000001</v>
+        <v>291.669</v>
       </c>
       <c r="G58">
         <v>76.7</v>
@@ -6043,37 +6043,37 @@
         <v>30.95</v>
       </c>
       <c r="M58">
-        <v>57.53964160000002</v>
+        <v>58.56713520000001</v>
       </c>
       <c r="N58">
-        <v>-26.58964160000002</v>
+        <v>-27.61713520000001</v>
       </c>
       <c r="O58">
-        <v>-8.508685312000006</v>
+        <v>-8.837483264000003</v>
       </c>
       <c r="P58">
-        <v>-18.08095628800001</v>
+        <v>-18.77965193600001</v>
       </c>
       <c r="Q58">
-        <v>-0.7809562880000094</v>
+        <v>-1.479651936000007</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1636695644238159</v>
+        <v>0.1664107170848348</v>
       </c>
       <c r="T58">
-        <v>1.536235558755463</v>
+        <v>1.571961967098613</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1721248121225697</v>
+        <v>0.1691050785765598</v>
       </c>
       <c r="W58">
-        <v>0.166237337725788</v>
+        <v>0.1668437002218268</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5378900378830304</v>
+        <v>0.5284533705517491</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1666575174729203</v>
+        <v>0.1682075174729203</v>
       </c>
       <c r="C59">
-        <v>-19.35933305744601</v>
+        <v>-26.95326413178157</v>
       </c>
       <c r="D59">
-        <v>195.609666942554</v>
+        <v>193.1327358682185</v>
       </c>
       <c r="E59">
-        <v>96.76900000000003</v>
+        <v>101.8860000000001</v>
       </c>
       <c r="F59">
-        <v>291.669</v>
+        <v>296.7860000000001</v>
       </c>
       <c r="G59">
         <v>76.7</v>
@@ -6125,37 +6125,37 @@
         <v>30.95</v>
       </c>
       <c r="M59">
-        <v>58.56713520000001</v>
+        <v>59.59462880000002</v>
       </c>
       <c r="N59">
-        <v>-27.61713520000001</v>
+        <v>-28.64462880000002</v>
       </c>
       <c r="O59">
-        <v>-8.837483264000003</v>
+        <v>-9.166281216000005</v>
       </c>
       <c r="P59">
-        <v>-18.77965193600001</v>
+        <v>-19.47834758400001</v>
       </c>
       <c r="Q59">
-        <v>-1.479651936000007</v>
+        <v>-2.178347584000011</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1664107170848348</v>
+        <v>0.16928240082495</v>
       </c>
       <c r="T59">
-        <v>1.571961967098613</v>
+        <v>1.609389632981913</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1691050785765598</v>
+        <v>0.1661894737735156</v>
       </c>
       <c r="W59">
-        <v>0.1668437002218268</v>
+        <v>0.1674291536662781</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5284533705517491</v>
+        <v>0.5193421055422363</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1682075174729202</v>
+        <v>0.1697575174729202</v>
       </c>
       <c r="C60">
-        <v>-26.95326413178145</v>
+        <v>-34.48525070700987</v>
       </c>
       <c r="D60">
-        <v>193.1327358682185</v>
+        <v>190.7177492929902</v>
       </c>
       <c r="E60">
-        <v>101.886</v>
+        <v>107.003</v>
       </c>
       <c r="F60">
-        <v>296.786</v>
+        <v>301.903</v>
       </c>
       <c r="G60">
         <v>76.7</v>
@@ -6207,37 +6207,37 @@
         <v>30.95</v>
       </c>
       <c r="M60">
-        <v>59.5946288</v>
+        <v>60.62212240000001</v>
       </c>
       <c r="N60">
-        <v>-28.6446288</v>
+        <v>-29.67212240000001</v>
       </c>
       <c r="O60">
-        <v>-9.166281216000002</v>
+        <v>-9.495079168000004</v>
       </c>
       <c r="P60">
-        <v>-19.478347584</v>
+        <v>-20.17704323200001</v>
       </c>
       <c r="Q60">
-        <v>-2.178347584000001</v>
+        <v>-2.877043232000005</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1692824008249499</v>
+        <v>0.1722941666987292</v>
       </c>
       <c r="T60">
-        <v>1.609389632981913</v>
+        <v>1.648643038664399</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1661894737735156</v>
+        <v>0.1633727030315916</v>
       </c>
       <c r="W60">
-        <v>0.1674291536662781</v>
+        <v>0.1679947612312564</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5193421055422364</v>
+        <v>0.5105396969737238</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1697575174729202</v>
+        <v>0.1713075174729203</v>
       </c>
       <c r="C61">
-        <v>-34.48525070700987</v>
+        <v>-41.95758780040688</v>
       </c>
       <c r="D61">
-        <v>190.7177492929902</v>
+        <v>188.3624121995932</v>
       </c>
       <c r="E61">
-        <v>107.003</v>
+        <v>112.12</v>
       </c>
       <c r="F61">
-        <v>301.903</v>
+        <v>307.02</v>
       </c>
       <c r="G61">
         <v>76.7</v>
@@ -6289,37 +6289,37 @@
         <v>30.95</v>
       </c>
       <c r="M61">
-        <v>60.62212240000001</v>
+        <v>61.64961600000001</v>
       </c>
       <c r="N61">
-        <v>-29.67212240000001</v>
+        <v>-30.69961600000001</v>
       </c>
       <c r="O61">
-        <v>-9.495079168000004</v>
+        <v>-9.823877120000004</v>
       </c>
       <c r="P61">
-        <v>-20.17704323200001</v>
+        <v>-20.87573888000001</v>
       </c>
       <c r="Q61">
-        <v>-2.877043232000005</v>
+        <v>-3.575738880000007</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1722941666987292</v>
+        <v>0.1754565208661974</v>
       </c>
       <c r="T61">
-        <v>1.648643038664399</v>
+        <v>1.689859114631008</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1633727030315916</v>
+        <v>0.1606498246477318</v>
       </c>
       <c r="W61">
-        <v>0.1679947612312564</v>
+        <v>0.1685415152107355</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5105396969737238</v>
+        <v>0.5020307020241618</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1713075174729203</v>
+        <v>0.1950286798172122</v>
       </c>
       <c r="C62">
-        <v>-41.95758780040688</v>
+        <v>-77.01638829627655</v>
       </c>
       <c r="D62">
-        <v>188.3624121995932</v>
+        <v>158.4206117037235</v>
       </c>
       <c r="E62">
-        <v>112.12</v>
+        <v>117.237</v>
       </c>
       <c r="F62">
-        <v>307.02</v>
+        <v>312.137</v>
       </c>
       <c r="G62">
         <v>76.7</v>
@@ -6371,45 +6371,45 @@
         <v>30.95</v>
       </c>
       <c r="M62">
-        <v>61.64961600000001</v>
+        <v>73.6019046</v>
       </c>
       <c r="N62">
-        <v>-30.69961600000001</v>
+        <v>-42.65190459999999</v>
       </c>
       <c r="O62">
-        <v>-9.823877120000004</v>
+        <v>-13.648609472</v>
       </c>
       <c r="P62">
-        <v>-20.87573888000001</v>
+        <v>-29.003295128</v>
       </c>
       <c r="Q62">
-        <v>-3.575738880000007</v>
+        <v>-11.703295128</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1754565208661974</v>
+        <v>0.1808865915147972</v>
       </c>
       <c r="T62">
-        <v>1.689859114631008</v>
+        <v>1.760631138416038</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1606498246477318</v>
+        <v>0.1345617352407481</v>
       </c>
       <c r="W62">
-        <v>0.1685415152107355</v>
+        <v>0.2040703428302316</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5020307020241618</v>
+        <v>0.4205054226273379</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1950286798172122</v>
+        <v>0.1969286798172122</v>
       </c>
       <c r="C63">
-        <v>-77.01638829627655</v>
+        <v>-84.12506295790354</v>
       </c>
       <c r="D63">
-        <v>158.4206117037235</v>
+        <v>156.4289370420965</v>
       </c>
       <c r="E63">
-        <v>117.237</v>
+        <v>122.354</v>
       </c>
       <c r="F63">
-        <v>312.137</v>
+        <v>317.254</v>
       </c>
       <c r="G63">
         <v>76.7</v>
@@ -6453,37 +6453,37 @@
         <v>30.95</v>
       </c>
       <c r="M63">
-        <v>73.6019046</v>
+        <v>74.8084932</v>
       </c>
       <c r="N63">
-        <v>-42.65190459999999</v>
+        <v>-43.8584932</v>
       </c>
       <c r="O63">
-        <v>-13.648609472</v>
+        <v>-14.034717824</v>
       </c>
       <c r="P63">
-        <v>-29.003295128</v>
+        <v>-29.823775376</v>
       </c>
       <c r="Q63">
-        <v>-11.703295128</v>
+        <v>-12.523775376</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1808865915147972</v>
+        <v>0.1844415018178182</v>
       </c>
       <c r="T63">
-        <v>1.760631138416038</v>
+        <v>1.806963536795408</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1345617352407481</v>
+        <v>0.1323913846723489</v>
       </c>
       <c r="W63">
-        <v>0.2040703428302316</v>
+        <v>0.2045821114942601</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4205054226273379</v>
+        <v>0.4137230771010905</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1969286798172122</v>
+        <v>0.1988286798172122</v>
       </c>
       <c r="C64">
-        <v>-84.12506295790354</v>
+        <v>-91.18428046075985</v>
       </c>
       <c r="D64">
-        <v>156.4289370420965</v>
+        <v>154.4867195392402</v>
       </c>
       <c r="E64">
-        <v>122.354</v>
+        <v>127.471</v>
       </c>
       <c r="F64">
-        <v>317.254</v>
+        <v>322.371</v>
       </c>
       <c r="G64">
         <v>76.7</v>
@@ -6535,37 +6535,37 @@
         <v>30.95</v>
       </c>
       <c r="M64">
-        <v>74.8084932</v>
+        <v>76.01508180000002</v>
       </c>
       <c r="N64">
-        <v>-43.8584932</v>
+        <v>-45.06508180000002</v>
       </c>
       <c r="O64">
-        <v>-14.034717824</v>
+        <v>-14.42082617600001</v>
       </c>
       <c r="P64">
-        <v>-29.823775376</v>
+        <v>-30.64425562400001</v>
       </c>
       <c r="Q64">
-        <v>-12.523775376</v>
+        <v>-13.34425562400001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1844415018178182</v>
+        <v>0.188188569434516</v>
       </c>
       <c r="T64">
-        <v>1.806963536795408</v>
+        <v>1.85580038914123</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1323913846723489</v>
+        <v>0.1302899341219942</v>
       </c>
       <c r="W64">
-        <v>0.2045821114942601</v>
+        <v>0.2050776335340338</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4137230771010905</v>
+        <v>0.4071560441312319</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1988286798172122</v>
+        <v>0.2007286798172122</v>
       </c>
       <c r="C65">
-        <v>-91.18428046075985</v>
+        <v>-98.19586038922029</v>
       </c>
       <c r="D65">
-        <v>154.4867195392402</v>
+        <v>152.5921396107798</v>
       </c>
       <c r="E65">
-        <v>127.471</v>
+        <v>132.5880000000001</v>
       </c>
       <c r="F65">
-        <v>322.371</v>
+        <v>327.4880000000001</v>
       </c>
       <c r="G65">
         <v>76.7</v>
@@ -6617,37 +6617,37 @@
         <v>30.95</v>
       </c>
       <c r="M65">
-        <v>76.01508180000002</v>
+        <v>77.22167040000002</v>
       </c>
       <c r="N65">
-        <v>-45.06508180000002</v>
+        <v>-46.27167040000002</v>
       </c>
       <c r="O65">
-        <v>-14.42082617600001</v>
+        <v>-14.80693452800001</v>
       </c>
       <c r="P65">
-        <v>-30.64425562400001</v>
+        <v>-31.46473587200001</v>
       </c>
       <c r="Q65">
-        <v>-13.34425562400001</v>
+        <v>-14.16473587200001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.188188569434516</v>
+        <v>0.1921438074743637</v>
       </c>
       <c r="T65">
-        <v>1.85580038914123</v>
+        <v>1.907350399950708</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1302899341219942</v>
+        <v>0.128254153901338</v>
       </c>
       <c r="W65">
-        <v>0.2050776335340338</v>
+        <v>0.2055576705100645</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4071560441312319</v>
+        <v>0.4007942309416813</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2007286798172122</v>
+        <v>0.2026286798172122</v>
       </c>
       <c r="C66">
-        <v>-98.19586038922029</v>
+        <v>-105.1615341496472</v>
       </c>
       <c r="D66">
-        <v>152.5921396107798</v>
+        <v>150.7434658503528</v>
       </c>
       <c r="E66">
-        <v>132.5880000000001</v>
+        <v>137.705</v>
       </c>
       <c r="F66">
-        <v>327.4880000000001</v>
+        <v>332.605</v>
       </c>
       <c r="G66">
         <v>76.7</v>
@@ -6699,37 +6699,37 @@
         <v>30.95</v>
       </c>
       <c r="M66">
-        <v>77.22167040000002</v>
+        <v>78.42825900000001</v>
       </c>
       <c r="N66">
-        <v>-46.27167040000002</v>
+        <v>-47.47825900000001</v>
       </c>
       <c r="O66">
-        <v>-14.80693452800001</v>
+        <v>-15.19304288</v>
       </c>
       <c r="P66">
-        <v>-31.46473587200001</v>
+        <v>-32.28521612</v>
       </c>
       <c r="Q66">
-        <v>-14.16473587200001</v>
+        <v>-14.98521612</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1921438074743637</v>
+        <v>0.1963250591164884</v>
       </c>
       <c r="T66">
-        <v>1.907350399950708</v>
+        <v>1.961846125663586</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.128254153901338</v>
+        <v>0.1262810130720867</v>
       </c>
       <c r="W66">
-        <v>0.2055576705100645</v>
+        <v>0.206022937117602</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4007942309416813</v>
+        <v>0.3946281658502708</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2026286798172122</v>
+        <v>0.2045286798172122</v>
       </c>
       <c r="C67">
-        <v>-105.1615341496472</v>
+        <v>-112.0829502478942</v>
       </c>
       <c r="D67">
-        <v>150.7434658503528</v>
+        <v>148.9390497521058</v>
       </c>
       <c r="E67">
-        <v>137.705</v>
+        <v>142.822</v>
       </c>
       <c r="F67">
-        <v>332.605</v>
+        <v>337.722</v>
       </c>
       <c r="G67">
         <v>76.7</v>
@@ -6781,37 +6781,37 @@
         <v>30.95</v>
       </c>
       <c r="M67">
-        <v>78.42825900000001</v>
+        <v>79.63484760000001</v>
       </c>
       <c r="N67">
-        <v>-47.47825900000001</v>
+        <v>-48.68484760000001</v>
       </c>
       <c r="O67">
-        <v>-15.19304288</v>
+        <v>-15.579151232</v>
       </c>
       <c r="P67">
-        <v>-32.28521612</v>
+        <v>-33.10569636800001</v>
       </c>
       <c r="Q67">
-        <v>-14.98521612</v>
+        <v>-15.80569636800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1963250591164884</v>
+        <v>0.2007522667375616</v>
       </c>
       <c r="T67">
-        <v>1.961846125663586</v>
+        <v>2.01954748230075</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1262810130720867</v>
+        <v>0.1243676643891762</v>
       </c>
       <c r="W67">
-        <v>0.206022937117602</v>
+        <v>0.2064741047370323</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3946281658502708</v>
+        <v>0.3886489512161758</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2045286798172122</v>
+        <v>0.2064286798172122</v>
       </c>
       <c r="C68">
-        <v>-112.0829502478942</v>
+        <v>-118.9616791922585</v>
       </c>
       <c r="D68">
-        <v>148.9390497521058</v>
+        <v>147.1773208077415</v>
       </c>
       <c r="E68">
-        <v>142.822</v>
+        <v>147.939</v>
       </c>
       <c r="F68">
-        <v>337.722</v>
+        <v>342.8390000000001</v>
       </c>
       <c r="G68">
         <v>76.7</v>
@@ -6863,37 +6863,37 @@
         <v>30.95</v>
       </c>
       <c r="M68">
-        <v>79.63484760000001</v>
+        <v>80.84143620000002</v>
       </c>
       <c r="N68">
-        <v>-48.68484760000001</v>
+        <v>-49.89143620000002</v>
       </c>
       <c r="O68">
-        <v>-15.579151232</v>
+        <v>-15.96525958400001</v>
       </c>
       <c r="P68">
-        <v>-33.10569636800001</v>
+        <v>-33.92617661600001</v>
       </c>
       <c r="Q68">
-        <v>-15.80569636800001</v>
+        <v>-16.62617661600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2007522667375616</v>
+        <v>0.2054477899720331</v>
       </c>
       <c r="T68">
-        <v>2.01954748230075</v>
+        <v>2.080745890855318</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1243676643891762</v>
+        <v>0.1225114305923229</v>
       </c>
       <c r="W68">
-        <v>0.2064741047370323</v>
+        <v>0.2069118046663303</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3886489512161758</v>
+        <v>0.382848220601009</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2064286798172122</v>
+        <v>0.2083286798172122</v>
       </c>
       <c r="C69">
-        <v>-118.9616791922585</v>
+        <v>-125.7992180525335</v>
       </c>
       <c r="D69">
-        <v>147.1773208077415</v>
+        <v>145.4567819474665</v>
       </c>
       <c r="E69">
-        <v>147.939</v>
+        <v>153.0560000000001</v>
       </c>
       <c r="F69">
-        <v>342.8390000000001</v>
+        <v>347.9560000000001</v>
       </c>
       <c r="G69">
         <v>76.7</v>
@@ -6945,37 +6945,37 @@
         <v>30.95</v>
       </c>
       <c r="M69">
-        <v>80.84143620000002</v>
+        <v>82.04802480000002</v>
       </c>
       <c r="N69">
-        <v>-49.89143620000002</v>
+        <v>-51.09802480000002</v>
       </c>
       <c r="O69">
-        <v>-15.96525958400001</v>
+        <v>-16.35136793600001</v>
       </c>
       <c r="P69">
-        <v>-33.92617661600001</v>
+        <v>-34.74665686400002</v>
       </c>
       <c r="Q69">
-        <v>-16.62617661600001</v>
+        <v>-17.44665686400002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2054477899720331</v>
+        <v>0.2104367834086592</v>
       </c>
       <c r="T69">
-        <v>2.080745890855318</v>
+        <v>2.145769199944547</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1225114305923229</v>
+        <v>0.1207097919071416</v>
       </c>
       <c r="W69">
-        <v>0.2069118046663303</v>
+        <v>0.207336631068296</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.382848220601009</v>
+        <v>0.3772180997098177</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2083286798172122</v>
+        <v>0.2102286798172122</v>
       </c>
       <c r="C70">
-        <v>-125.7992180525335</v>
+        <v>-132.596994702978</v>
       </c>
       <c r="D70">
-        <v>145.4567819474665</v>
+        <v>143.776005297022</v>
       </c>
       <c r="E70">
-        <v>153.0560000000001</v>
+        <v>158.173</v>
       </c>
       <c r="F70">
-        <v>347.9560000000001</v>
+        <v>353.073</v>
       </c>
       <c r="G70">
         <v>76.7</v>
@@ -7027,37 +7027,37 @@
         <v>30.95</v>
       </c>
       <c r="M70">
-        <v>82.04802480000002</v>
+        <v>83.25461340000001</v>
       </c>
       <c r="N70">
-        <v>-51.09802480000002</v>
+        <v>-52.30461340000001</v>
       </c>
       <c r="O70">
-        <v>-16.35136793600001</v>
+        <v>-16.737476288</v>
       </c>
       <c r="P70">
-        <v>-34.74665686400002</v>
+        <v>-35.567137112</v>
       </c>
       <c r="Q70">
-        <v>-17.44665686400002</v>
+        <v>-18.267137112</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2104367834086592</v>
+        <v>0.2157476473895837</v>
       </c>
       <c r="T70">
-        <v>2.145769199944547</v>
+        <v>2.214987561233081</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1207097919071416</v>
+        <v>0.1189603746331251</v>
       </c>
       <c r="W70">
-        <v>0.207336631068296</v>
+        <v>0.2077491436615091</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3772180997098177</v>
+        <v>0.371751170728516</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2102286798172122</v>
+        <v>0.2121286798172122</v>
       </c>
       <c r="C71">
-        <v>-132.596994702978</v>
+        <v>-139.3563717744761</v>
       </c>
       <c r="D71">
-        <v>143.776005297022</v>
+        <v>142.1336282255239</v>
       </c>
       <c r="E71">
-        <v>158.173</v>
+        <v>163.29</v>
       </c>
       <c r="F71">
-        <v>353.073</v>
+        <v>358.1900000000001</v>
       </c>
       <c r="G71">
         <v>76.7</v>
@@ -7109,37 +7109,37 @@
         <v>30.95</v>
       </c>
       <c r="M71">
-        <v>83.25461340000001</v>
+        <v>84.46120200000001</v>
       </c>
       <c r="N71">
-        <v>-52.30461340000001</v>
+        <v>-53.51120200000001</v>
       </c>
       <c r="O71">
-        <v>-16.737476288</v>
+        <v>-17.12358464</v>
       </c>
       <c r="P71">
-        <v>-35.567137112</v>
+        <v>-36.38761736000001</v>
       </c>
       <c r="Q71">
-        <v>-18.267137112</v>
+        <v>-19.08761736000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2157476473895837</v>
+        <v>0.2214125689692364</v>
       </c>
       <c r="T71">
-        <v>2.214987561233081</v>
+        <v>2.28882047994085</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1189603746331251</v>
+        <v>0.1172609407097947</v>
       </c>
       <c r="W71">
-        <v>0.2077491436615091</v>
+        <v>0.2081498701806304</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.371751170728516</v>
+        <v>0.3664404397181087</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2121286798172122</v>
+        <v>0.2140286798172122</v>
       </c>
       <c r="C72">
-        <v>-139.3563717744761</v>
+        <v>-146.0786503388798</v>
       </c>
       <c r="D72">
-        <v>142.1336282255239</v>
+        <v>140.5283496611203</v>
       </c>
       <c r="E72">
-        <v>163.29</v>
+        <v>168.4070000000001</v>
       </c>
       <c r="F72">
-        <v>358.1900000000001</v>
+        <v>363.3070000000001</v>
       </c>
       <c r="G72">
         <v>76.7</v>
@@ -7191,37 +7191,37 @@
         <v>30.95</v>
       </c>
       <c r="M72">
-        <v>84.46120200000001</v>
+        <v>85.66779060000002</v>
       </c>
       <c r="N72">
-        <v>-53.51120200000001</v>
+        <v>-54.71779060000001</v>
       </c>
       <c r="O72">
-        <v>-17.12358464</v>
+        <v>-17.50969299200001</v>
       </c>
       <c r="P72">
-        <v>-36.38761736000001</v>
+        <v>-37.20809760800001</v>
       </c>
       <c r="Q72">
-        <v>-19.08761736000001</v>
+        <v>-19.90809760800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2214125689692364</v>
+        <v>0.2274681747957619</v>
       </c>
       <c r="T72">
-        <v>2.28882047994085</v>
+        <v>2.367745324076742</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1172609407097947</v>
+        <v>0.1156093781645864</v>
       </c>
       <c r="W72">
-        <v>0.2081498701806304</v>
+        <v>0.2085393086287905</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3664404397181087</v>
+        <v>0.3612793067643325</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2140286798172122</v>
+        <v>0.2159286798172122</v>
       </c>
       <c r="C73">
-        <v>-146.0786503388798</v>
+        <v>-152.7650733464703</v>
       </c>
       <c r="D73">
-        <v>140.5283496611203</v>
+        <v>138.9589266535298</v>
       </c>
       <c r="E73">
-        <v>168.407</v>
+        <v>173.524</v>
       </c>
       <c r="F73">
-        <v>363.307</v>
+        <v>368.424</v>
       </c>
       <c r="G73">
         <v>76.7</v>
@@ -7273,37 +7273,37 @@
         <v>30.95</v>
       </c>
       <c r="M73">
-        <v>85.6677906</v>
+        <v>86.87437920000001</v>
       </c>
       <c r="N73">
-        <v>-54.7177906</v>
+        <v>-55.9243792</v>
       </c>
       <c r="O73">
-        <v>-17.509692992</v>
+        <v>-17.895801344</v>
       </c>
       <c r="P73">
-        <v>-37.208097608</v>
+        <v>-38.028577856</v>
       </c>
       <c r="Q73">
-        <v>-19.908097608</v>
+        <v>-20.728577856</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2274681747957618</v>
+        <v>0.2339563238956104</v>
       </c>
       <c r="T73">
-        <v>2.367745324076741</v>
+        <v>2.452307657079482</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1156093781645864</v>
+        <v>0.1140036923567449</v>
       </c>
       <c r="W73">
-        <v>0.2085393086287905</v>
+        <v>0.2089179293422796</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3612793067643325</v>
+        <v>0.3562615386148279</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2159286798172122</v>
+        <v>0.2178286798172122</v>
       </c>
       <c r="C74">
-        <v>-152.7650733464703</v>
+        <v>-159.4168288356261</v>
       </c>
       <c r="D74">
-        <v>138.9589266535298</v>
+        <v>137.4241711643739</v>
       </c>
       <c r="E74">
-        <v>173.524</v>
+        <v>178.641</v>
       </c>
       <c r="F74">
-        <v>368.424</v>
+        <v>373.541</v>
       </c>
       <c r="G74">
         <v>76.7</v>
@@ -7355,37 +7355,37 @@
         <v>30.95</v>
       </c>
       <c r="M74">
-        <v>86.87437920000001</v>
+        <v>88.0809678</v>
       </c>
       <c r="N74">
-        <v>-55.9243792</v>
+        <v>-57.13096779999999</v>
       </c>
       <c r="O74">
-        <v>-17.895801344</v>
+        <v>-18.281909696</v>
       </c>
       <c r="P74">
-        <v>-38.028577856</v>
+        <v>-38.84905810399999</v>
       </c>
       <c r="Q74">
-        <v>-20.728577856</v>
+        <v>-21.54905810399999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2339563238956104</v>
+        <v>0.2409250766324849</v>
       </c>
       <c r="T74">
-        <v>2.452307657079482</v>
+        <v>2.543133866600944</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1140036923567449</v>
+        <v>0.1124419979408991</v>
       </c>
       <c r="W74">
-        <v>0.2089179293422796</v>
+        <v>0.209286176885536</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3562615386148279</v>
+        <v>0.3513812435653098</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2178286798172122</v>
+        <v>0.2197286798172122</v>
       </c>
       <c r="C75">
-        <v>-159.4168288356261</v>
+        <v>-166.0350529321162</v>
       </c>
       <c r="D75">
-        <v>137.4241711643739</v>
+        <v>135.9229470678838</v>
       </c>
       <c r="E75">
-        <v>178.641</v>
+        <v>183.758</v>
       </c>
       <c r="F75">
-        <v>373.541</v>
+        <v>378.658</v>
       </c>
       <c r="G75">
         <v>76.7</v>
@@ -7437,37 +7437,37 @@
         <v>30.95</v>
       </c>
       <c r="M75">
-        <v>88.0809678</v>
+        <v>89.28755640000001</v>
       </c>
       <c r="N75">
-        <v>-57.13096779999999</v>
+        <v>-58.33755640000001</v>
       </c>
       <c r="O75">
-        <v>-18.281909696</v>
+        <v>-18.668018048</v>
       </c>
       <c r="P75">
-        <v>-38.84905810399999</v>
+        <v>-39.669538352</v>
       </c>
       <c r="Q75">
-        <v>-21.54905810399999</v>
+        <v>-22.369538352</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2409250766324849</v>
+        <v>0.2484298872721959</v>
       </c>
       <c r="T75">
-        <v>2.543133866600944</v>
+        <v>2.640946707624057</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1124419979408991</v>
+        <v>0.1109225114822383</v>
       </c>
       <c r="W75">
-        <v>0.209286176885536</v>
+        <v>0.2096444717924882</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3513812435653098</v>
+        <v>0.3466328483819947</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2197286798172122</v>
+        <v>0.2216286798172122</v>
       </c>
       <c r="C76">
-        <v>-166.0350529321162</v>
+        <v>-172.620832653931</v>
       </c>
       <c r="D76">
-        <v>135.9229470678838</v>
+        <v>134.4541673460691</v>
       </c>
       <c r="E76">
-        <v>183.758</v>
+        <v>188.875</v>
       </c>
       <c r="F76">
-        <v>378.658</v>
+        <v>383.775</v>
       </c>
       <c r="G76">
         <v>76.7</v>
@@ -7519,37 +7519,37 @@
         <v>30.95</v>
       </c>
       <c r="M76">
-        <v>89.28755640000001</v>
+        <v>90.49414500000002</v>
       </c>
       <c r="N76">
-        <v>-58.33755640000001</v>
+        <v>-59.54414500000001</v>
       </c>
       <c r="O76">
-        <v>-18.668018048</v>
+        <v>-19.0541264</v>
       </c>
       <c r="P76">
-        <v>-39.669538352</v>
+        <v>-40.49001860000001</v>
       </c>
       <c r="Q76">
-        <v>-22.369538352</v>
+        <v>-23.19001860000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2484298872721959</v>
+        <v>0.2565350827630837</v>
       </c>
       <c r="T76">
-        <v>2.640946707624057</v>
+        <v>2.74658457592902</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1109225114822383</v>
+        <v>0.1094435446624751</v>
       </c>
       <c r="W76">
-        <v>0.2096444717924882</v>
+        <v>0.2099932121685884</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3466328483819947</v>
+        <v>0.3420110770702347</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2216286798172122</v>
+        <v>0.2235286798172122</v>
       </c>
       <c r="C77">
-        <v>-172.620832653931</v>
+        <v>-179.1752085362043</v>
       </c>
       <c r="D77">
-        <v>134.4541673460691</v>
+        <v>133.0167914637958</v>
       </c>
       <c r="E77">
-        <v>188.875</v>
+        <v>193.992</v>
       </c>
       <c r="F77">
-        <v>383.775</v>
+        <v>388.8920000000001</v>
       </c>
       <c r="G77">
         <v>76.7</v>
@@ -7601,37 +7601,37 @@
         <v>30.95</v>
       </c>
       <c r="M77">
-        <v>90.49414500000002</v>
+        <v>91.70073360000002</v>
       </c>
       <c r="N77">
-        <v>-59.54414500000001</v>
+        <v>-60.75073360000002</v>
       </c>
       <c r="O77">
-        <v>-19.0541264</v>
+        <v>-19.44023475200001</v>
       </c>
       <c r="P77">
-        <v>-40.49001860000001</v>
+        <v>-41.31049884800001</v>
       </c>
       <c r="Q77">
-        <v>-23.19001860000001</v>
+        <v>-24.01049884800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2565350827630837</v>
+        <v>0.2653157112115456</v>
       </c>
       <c r="T77">
-        <v>2.74658457592902</v>
+        <v>2.861025599926063</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1094435446624751</v>
+        <v>0.1080034980221794</v>
       </c>
       <c r="W77">
-        <v>0.2099932121685884</v>
+        <v>0.2103327751663701</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3420110770702347</v>
+        <v>0.3375109313193105</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2235286798172122</v>
+        <v>0.2254286798172122</v>
       </c>
       <c r="C78">
-        <v>-179.1752085362043</v>
+        <v>-185.6991770895466</v>
       </c>
       <c r="D78">
-        <v>133.0167914637958</v>
+        <v>131.6098229104535</v>
       </c>
       <c r="E78">
-        <v>193.992</v>
+        <v>199.1090000000001</v>
       </c>
       <c r="F78">
-        <v>388.8920000000001</v>
+        <v>394.0090000000001</v>
       </c>
       <c r="G78">
         <v>76.7</v>
@@ -7683,37 +7683,37 @@
         <v>30.95</v>
       </c>
       <c r="M78">
-        <v>91.70073360000002</v>
+        <v>92.90732220000002</v>
       </c>
       <c r="N78">
-        <v>-60.75073360000002</v>
+        <v>-61.95732220000002</v>
       </c>
       <c r="O78">
-        <v>-19.44023475200001</v>
+        <v>-19.82634310400001</v>
       </c>
       <c r="P78">
-        <v>-41.31049884800001</v>
+        <v>-42.13097909600002</v>
       </c>
       <c r="Q78">
-        <v>-24.01049884800001</v>
+        <v>-24.83097909600002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2653157112115456</v>
+        <v>0.2748598725685693</v>
       </c>
       <c r="T78">
-        <v>2.861025599926063</v>
+        <v>2.985418017314152</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1080034980221794</v>
+        <v>0.1066008551907225</v>
       </c>
       <c r="W78">
-        <v>0.2103327751663701</v>
+        <v>0.2106635183460276</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3375109313193105</v>
+        <v>0.3331276724710078</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2254286798172122</v>
+        <v>0.2273286798172122</v>
       </c>
       <c r="C79">
-        <v>-185.6991770895466</v>
+        <v>-192.1936931039949</v>
       </c>
       <c r="D79">
-        <v>131.6098229104535</v>
+        <v>130.2323068960052</v>
       </c>
       <c r="E79">
-        <v>199.1090000000001</v>
+        <v>204.226</v>
       </c>
       <c r="F79">
-        <v>394.0090000000001</v>
+        <v>399.126</v>
       </c>
       <c r="G79">
         <v>76.7</v>
@@ -7765,37 +7765,37 @@
         <v>30.95</v>
       </c>
       <c r="M79">
-        <v>92.90732220000002</v>
+        <v>94.11391080000001</v>
       </c>
       <c r="N79">
-        <v>-61.95732220000002</v>
+        <v>-63.16391080000001</v>
       </c>
       <c r="O79">
-        <v>-19.82634310400001</v>
+        <v>-20.212451456</v>
       </c>
       <c r="P79">
-        <v>-42.13097909600002</v>
+        <v>-42.95145934400001</v>
       </c>
       <c r="Q79">
-        <v>-24.83097909600002</v>
+        <v>-25.65145934400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2748598725685693</v>
+        <v>0.2852716849580497</v>
       </c>
       <c r="T79">
-        <v>2.985418017314152</v>
+        <v>3.121118836282977</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1066008551907225</v>
+        <v>0.1052341775600722</v>
       </c>
       <c r="W79">
-        <v>0.2106635183460276</v>
+        <v>0.210985780931335</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3331276724710078</v>
+        <v>0.3288568048752257</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2273286798172122</v>
+        <v>0.2292286798172122</v>
       </c>
       <c r="C80">
-        <v>-192.1936931039949</v>
+        <v>-198.659671809773</v>
       </c>
       <c r="D80">
-        <v>130.2323068960052</v>
+        <v>128.8833281902271</v>
       </c>
       <c r="E80">
-        <v>204.226</v>
+        <v>209.343</v>
       </c>
       <c r="F80">
-        <v>399.126</v>
+        <v>404.2430000000001</v>
       </c>
       <c r="G80">
         <v>76.7</v>
@@ -7847,37 +7847,37 @@
         <v>30.95</v>
       </c>
       <c r="M80">
-        <v>94.11391080000001</v>
+        <v>95.32049940000002</v>
       </c>
       <c r="N80">
-        <v>-63.16391080000001</v>
+        <v>-64.37049940000001</v>
       </c>
       <c r="O80">
-        <v>-20.212451456</v>
+        <v>-20.598559808</v>
       </c>
       <c r="P80">
-        <v>-42.95145934400001</v>
+        <v>-43.77193959200001</v>
       </c>
       <c r="Q80">
-        <v>-25.65145934400001</v>
+        <v>-26.47193959200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2852716849580497</v>
+        <v>0.2966750985274807</v>
       </c>
       <c r="T80">
-        <v>3.121118836282977</v>
+        <v>3.269743542772644</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1052341775600722</v>
+        <v>0.1039020993631093</v>
       </c>
       <c r="W80">
-        <v>0.210985780931335</v>
+        <v>0.2112998849701788</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3288568048752257</v>
+        <v>0.3246940605097165</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2292286798172122</v>
+        <v>0.2311286798172122</v>
       </c>
       <c r="C81">
-        <v>-198.659671809773</v>
+        <v>-205.0979909051389</v>
       </c>
       <c r="D81">
-        <v>128.8833281902271</v>
+        <v>127.5620090948612</v>
       </c>
       <c r="E81">
-        <v>209.343</v>
+        <v>214.4600000000001</v>
       </c>
       <c r="F81">
-        <v>404.2430000000001</v>
+        <v>409.3600000000001</v>
       </c>
       <c r="G81">
         <v>76.7</v>
@@ -7929,37 +7929,37 @@
         <v>30.95</v>
       </c>
       <c r="M81">
-        <v>95.32049940000002</v>
+        <v>96.52708800000002</v>
       </c>
       <c r="N81">
-        <v>-64.37049940000001</v>
+        <v>-65.57708800000002</v>
       </c>
       <c r="O81">
-        <v>-20.598559808</v>
+        <v>-20.98466816000001</v>
       </c>
       <c r="P81">
-        <v>-43.77193959200001</v>
+        <v>-44.59241984000001</v>
       </c>
       <c r="Q81">
-        <v>-26.47193959200001</v>
+        <v>-27.29241984000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2966750985274807</v>
+        <v>0.3092188534538547</v>
       </c>
       <c r="T81">
-        <v>3.269743542772644</v>
+        <v>3.433230719911275</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1039020993631093</v>
+        <v>0.1026033231210704</v>
       </c>
       <c r="W81">
-        <v>0.2112998849701788</v>
+        <v>0.2116061364080516</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3246940605097165</v>
+        <v>0.3206353847533451</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2311286798172122</v>
+        <v>0.2330286798172122</v>
       </c>
       <c r="C82">
-        <v>-205.0979909051389</v>
+        <v>-211.5094924607598</v>
       </c>
       <c r="D82">
-        <v>127.5620090948612</v>
+        <v>126.2675075392403</v>
       </c>
       <c r="E82">
-        <v>214.4600000000001</v>
+        <v>219.5770000000001</v>
       </c>
       <c r="F82">
-        <v>409.3600000000001</v>
+        <v>414.4770000000001</v>
       </c>
       <c r="G82">
         <v>76.7</v>
@@ -8011,37 +8011,37 @@
         <v>30.95</v>
       </c>
       <c r="M82">
-        <v>96.52708800000002</v>
+        <v>97.73367660000002</v>
       </c>
       <c r="N82">
-        <v>-65.57708800000002</v>
+        <v>-66.78367660000002</v>
       </c>
       <c r="O82">
-        <v>-20.98466816000001</v>
+        <v>-21.37077651200001</v>
       </c>
       <c r="P82">
-        <v>-44.59241984000001</v>
+        <v>-45.41290008800001</v>
       </c>
       <c r="Q82">
-        <v>-27.29241984000001</v>
+        <v>-28.11290008800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3092188534538547</v>
+        <v>0.3230830036356365</v>
       </c>
       <c r="T82">
-        <v>3.433230719911275</v>
+        <v>3.613927073590816</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1026033231210704</v>
+        <v>0.1013366154282177</v>
       </c>
       <c r="W82">
-        <v>0.2116061364080516</v>
+        <v>0.2119048260820263</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3206353847533451</v>
+        <v>0.3166769232131803</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2330286798172122</v>
+        <v>0.2349286798172122</v>
       </c>
       <c r="C83">
-        <v>-211.5094924607598</v>
+        <v>-217.8949847092989</v>
       </c>
       <c r="D83">
-        <v>126.2675075392403</v>
+        <v>124.9990152907012</v>
       </c>
       <c r="E83">
-        <v>219.5770000000001</v>
+        <v>224.694</v>
       </c>
       <c r="F83">
-        <v>414.4770000000001</v>
+        <v>419.5940000000001</v>
       </c>
       <c r="G83">
         <v>76.7</v>
@@ -8093,37 +8093,37 @@
         <v>30.95</v>
       </c>
       <c r="M83">
-        <v>97.73367660000002</v>
+        <v>98.94026520000001</v>
       </c>
       <c r="N83">
-        <v>-66.78367660000002</v>
+        <v>-67.99026520000001</v>
       </c>
       <c r="O83">
-        <v>-21.37077651200001</v>
+        <v>-21.756884864</v>
       </c>
       <c r="P83">
-        <v>-45.41290008800001</v>
+        <v>-46.23338033600001</v>
       </c>
       <c r="Q83">
-        <v>-28.11290008800001</v>
+        <v>-28.93338033600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3230830036356365</v>
+        <v>0.3384876149487275</v>
       </c>
       <c r="T83">
-        <v>3.613927073590816</v>
+        <v>3.814700799901418</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1013366154282177</v>
+        <v>0.1001008030449468</v>
       </c>
       <c r="W83">
-        <v>0.2119048260820263</v>
+        <v>0.2121962306420016</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3166769232131803</v>
+        <v>0.3128150095154586</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2349286798172122</v>
+        <v>0.2368286798172122</v>
       </c>
       <c r="C84">
-        <v>-217.8949847092989</v>
+        <v>-224.2552437282042</v>
       </c>
       <c r="D84">
-        <v>124.9990152907012</v>
+        <v>123.7557562717959</v>
       </c>
       <c r="E84">
-        <v>224.694</v>
+        <v>229.8110000000001</v>
       </c>
       <c r="F84">
-        <v>419.5940000000001</v>
+        <v>424.7110000000001</v>
       </c>
       <c r="G84">
         <v>76.7</v>
@@ -8175,37 +8175,37 @@
         <v>30.95</v>
       </c>
       <c r="M84">
-        <v>98.94026520000001</v>
+        <v>100.1468538</v>
       </c>
       <c r="N84">
-        <v>-67.99026520000001</v>
+        <v>-69.19685380000001</v>
       </c>
       <c r="O84">
-        <v>-21.756884864</v>
+        <v>-22.142993216</v>
       </c>
       <c r="P84">
-        <v>-46.23338033600001</v>
+        <v>-47.05386058400001</v>
       </c>
       <c r="Q84">
-        <v>-28.93338033600001</v>
+        <v>-29.75386058400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3384876149487275</v>
+        <v>0.3557045334751233</v>
       </c>
       <c r="T84">
-        <v>3.814700799901418</v>
+        <v>4.039094964601501</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1001008030449468</v>
+        <v>0.09889476927332089</v>
       </c>
       <c r="W84">
-        <v>0.2121962306420016</v>
+        <v>0.212480613405351</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3128150095154586</v>
+        <v>0.3090461539791278</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2368286798172122</v>
+        <v>0.2387286798172122</v>
       </c>
       <c r="C85">
-        <v>-224.2552437282042</v>
+        <v>-230.591015023064</v>
       </c>
       <c r="D85">
-        <v>123.7557562717959</v>
+        <v>122.5369849769361</v>
       </c>
       <c r="E85">
-        <v>229.8110000000001</v>
+        <v>234.9280000000001</v>
       </c>
       <c r="F85">
-        <v>424.7110000000001</v>
+        <v>429.8280000000001</v>
       </c>
       <c r="G85">
         <v>76.7</v>
@@ -8257,37 +8257,37 @@
         <v>30.95</v>
       </c>
       <c r="M85">
-        <v>100.1468538</v>
+        <v>101.3534424</v>
       </c>
       <c r="N85">
-        <v>-69.19685380000001</v>
+        <v>-70.40344240000002</v>
       </c>
       <c r="O85">
-        <v>-22.142993216</v>
+        <v>-22.52910156800001</v>
       </c>
       <c r="P85">
-        <v>-47.05386058400001</v>
+        <v>-47.87434083200002</v>
       </c>
       <c r="Q85">
-        <v>-29.75386058400001</v>
+        <v>-30.57434083200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3557045334751233</v>
+        <v>0.3750735668173185</v>
       </c>
       <c r="T85">
-        <v>4.039094964601501</v>
+        <v>4.291538399889096</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09889476927332089</v>
+        <v>0.09771745059149563</v>
       </c>
       <c r="W85">
-        <v>0.212480613405351</v>
+        <v>0.2127582251505253</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3090461539791278</v>
+        <v>0.3053670330984238</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2387286798172122</v>
+        <v>0.2406286798172122</v>
       </c>
       <c r="C86">
-        <v>-230.591015023064</v>
+        <v>-236.9030150183141</v>
       </c>
       <c r="D86">
-        <v>122.536984976936</v>
+        <v>121.3419849816859</v>
       </c>
       <c r="E86">
-        <v>234.928</v>
+        <v>240.045</v>
       </c>
       <c r="F86">
-        <v>429.828</v>
+        <v>434.9450000000001</v>
       </c>
       <c r="G86">
         <v>76.7</v>
@@ -8339,37 +8339,37 @@
         <v>30.95</v>
       </c>
       <c r="M86">
-        <v>101.3534424</v>
+        <v>102.560031</v>
       </c>
       <c r="N86">
-        <v>-70.4034424</v>
+        <v>-71.61003100000001</v>
       </c>
       <c r="O86">
-        <v>-22.529101568</v>
+        <v>-22.91520992</v>
       </c>
       <c r="P86">
-        <v>-47.874340832</v>
+        <v>-48.69482108</v>
       </c>
       <c r="Q86">
-        <v>-30.574340832</v>
+        <v>-31.39482108</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3750735668173182</v>
+        <v>0.3970251379384728</v>
       </c>
       <c r="T86">
-        <v>4.291538399889093</v>
+        <v>4.577640959881699</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09771745059149564</v>
+        <v>0.09656783352571333</v>
       </c>
       <c r="W86">
-        <v>0.2127582251505253</v>
+        <v>0.2130293048546368</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3053670330984239</v>
+        <v>0.3017744797678542</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2406286798172122</v>
+        <v>0.2425286798172122</v>
       </c>
       <c r="C87">
-        <v>-236.9030150183141</v>
+        <v>-243.1919324615635</v>
       </c>
       <c r="D87">
-        <v>121.3419849816859</v>
+        <v>120.1700675384366</v>
       </c>
       <c r="E87">
-        <v>240.045</v>
+        <v>245.162</v>
       </c>
       <c r="F87">
-        <v>434.9450000000001</v>
+        <v>440.062</v>
       </c>
       <c r="G87">
         <v>76.7</v>
@@ -8421,37 +8421,37 @@
         <v>30.95</v>
       </c>
       <c r="M87">
-        <v>102.560031</v>
+        <v>103.7666196</v>
       </c>
       <c r="N87">
-        <v>-71.61003100000001</v>
+        <v>-72.81661960000001</v>
       </c>
       <c r="O87">
-        <v>-22.91520992</v>
+        <v>-23.301318272</v>
       </c>
       <c r="P87">
-        <v>-48.69482108</v>
+        <v>-49.51530132800001</v>
       </c>
       <c r="Q87">
-        <v>-31.39482108</v>
+        <v>-32.21530132800001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3970251379384728</v>
+        <v>0.4221126477912209</v>
       </c>
       <c r="T87">
-        <v>4.577640959881699</v>
+        <v>4.904615314158963</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09656783352571333</v>
+        <v>0.09544495174053061</v>
       </c>
       <c r="W87">
-        <v>0.2130293048546368</v>
+        <v>0.2132940803795829</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3017744797678542</v>
+        <v>0.2982654741891582</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2425286798172122</v>
+        <v>0.2444286798172122</v>
       </c>
       <c r="C88">
-        <v>-243.1919324615635</v>
+        <v>-249.4584297473187</v>
       </c>
       <c r="D88">
-        <v>120.1700675384366</v>
+        <v>119.0205702526813</v>
       </c>
       <c r="E88">
-        <v>245.162</v>
+        <v>250.279</v>
       </c>
       <c r="F88">
-        <v>440.062</v>
+        <v>445.179</v>
       </c>
       <c r="G88">
         <v>76.7</v>
@@ -8503,37 +8503,37 @@
         <v>30.95</v>
       </c>
       <c r="M88">
-        <v>103.7666196</v>
+        <v>104.9732082</v>
       </c>
       <c r="N88">
-        <v>-72.81661960000001</v>
+        <v>-74.02320820000001</v>
       </c>
       <c r="O88">
-        <v>-23.301318272</v>
+        <v>-23.687426624</v>
       </c>
       <c r="P88">
-        <v>-49.51530132800001</v>
+        <v>-50.33578157600001</v>
       </c>
       <c r="Q88">
-        <v>-32.21530132800001</v>
+        <v>-33.03578157600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4221126477912209</v>
+        <v>0.4510597745443918</v>
       </c>
       <c r="T88">
-        <v>4.904615314158963</v>
+        <v>5.281893415248115</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09544495174053061</v>
+        <v>0.09434788332971993</v>
       </c>
       <c r="W88">
-        <v>0.2132940803795829</v>
+        <v>0.2135527691108521</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2982654741891582</v>
+        <v>0.2948371354053748</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2444286798172122</v>
+        <v>0.2463286798172122</v>
       </c>
       <c r="C89">
-        <v>-249.4584297473187</v>
+        <v>-255.703144165457</v>
       </c>
       <c r="D89">
-        <v>119.0205702526813</v>
+        <v>117.892855834543</v>
       </c>
       <c r="E89">
-        <v>250.279</v>
+        <v>255.396</v>
       </c>
       <c r="F89">
-        <v>445.179</v>
+        <v>450.296</v>
       </c>
       <c r="G89">
         <v>76.7</v>
@@ -8585,37 +8585,37 @@
         <v>30.95</v>
       </c>
       <c r="M89">
-        <v>104.9732082</v>
+        <v>106.1797968</v>
       </c>
       <c r="N89">
-        <v>-74.02320820000001</v>
+        <v>-75.22979680000002</v>
       </c>
       <c r="O89">
-        <v>-23.687426624</v>
+        <v>-24.073534976</v>
       </c>
       <c r="P89">
-        <v>-50.33578157600001</v>
+        <v>-51.15626182400001</v>
       </c>
       <c r="Q89">
-        <v>-33.03578157600001</v>
+        <v>-33.85626182400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4510597745443918</v>
+        <v>0.4848314224230911</v>
       </c>
       <c r="T89">
-        <v>5.281893415248115</v>
+        <v>5.722051199852125</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09434788332971993</v>
+        <v>0.09327574829188219</v>
       </c>
       <c r="W89">
-        <v>0.2135527691108521</v>
+        <v>0.2138055785527742</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2948371354053748</v>
+        <v>0.2914867134121318</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2463286798172122</v>
+        <v>0.2482286798172122</v>
       </c>
       <c r="C90">
-        <v>-255.703144165457</v>
+        <v>-261.9266890793886</v>
       </c>
       <c r="D90">
-        <v>117.892855834543</v>
+        <v>116.7863109206115</v>
       </c>
       <c r="E90">
-        <v>255.396</v>
+        <v>260.513</v>
       </c>
       <c r="F90">
-        <v>450.296</v>
+        <v>455.4130000000001</v>
       </c>
       <c r="G90">
         <v>76.7</v>
@@ -8667,37 +8667,37 @@
         <v>30.95</v>
       </c>
       <c r="M90">
-        <v>106.1797968</v>
+        <v>107.3863854</v>
       </c>
       <c r="N90">
-        <v>-75.22979680000002</v>
+        <v>-76.43638540000002</v>
       </c>
       <c r="O90">
-        <v>-24.073534976</v>
+        <v>-24.45964332800001</v>
       </c>
       <c r="P90">
-        <v>-51.15626182400001</v>
+        <v>-51.97674207200001</v>
       </c>
       <c r="Q90">
-        <v>-33.85626182400001</v>
+        <v>-34.67674207200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4848314224230911</v>
+        <v>0.5247433699160994</v>
       </c>
       <c r="T90">
-        <v>5.722051199852125</v>
+        <v>6.242237672565954</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09327574829188219</v>
+        <v>0.09222770617624307</v>
       </c>
       <c r="W90">
-        <v>0.2138055785527742</v>
+        <v>0.2140527068836419</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2914867134121318</v>
+        <v>0.2882115818007596</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2482286798172122</v>
+        <v>0.2501286798172122</v>
       </c>
       <c r="C91">
-        <v>-261.9266890793886</v>
+        <v>-268.1296550384877</v>
       </c>
       <c r="D91">
-        <v>116.7863109206115</v>
+        <v>115.7003449615123</v>
       </c>
       <c r="E91">
-        <v>260.513</v>
+        <v>265.63</v>
       </c>
       <c r="F91">
-        <v>455.4130000000001</v>
+        <v>460.53</v>
       </c>
       <c r="G91">
         <v>76.7</v>
@@ -8749,37 +8749,37 @@
         <v>30.95</v>
       </c>
       <c r="M91">
-        <v>107.3863854</v>
+        <v>108.592974</v>
       </c>
       <c r="N91">
-        <v>-76.43638540000002</v>
+        <v>-77.64297400000001</v>
       </c>
       <c r="O91">
-        <v>-24.45964332800001</v>
+        <v>-24.84575168</v>
       </c>
       <c r="P91">
-        <v>-51.97674207200001</v>
+        <v>-52.79722232</v>
       </c>
       <c r="Q91">
-        <v>-34.67674207200001</v>
+        <v>-35.49722232000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5247433699160994</v>
+        <v>0.5726377069077093</v>
       </c>
       <c r="T91">
-        <v>6.242237672565954</v>
+        <v>6.866461439822551</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09222770617624307</v>
+        <v>0.09120295388539593</v>
       </c>
       <c r="W91">
-        <v>0.2140527068836419</v>
+        <v>0.2142943434738236</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2882115818007596</v>
+        <v>0.2850092308918623</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2501286798172122</v>
+        <v>0.2520286798172122</v>
       </c>
       <c r="C92">
-        <v>-268.1296550384877</v>
+        <v>-274.3126108290292</v>
       </c>
       <c r="D92">
-        <v>115.7003449615123</v>
+        <v>114.6343891709708</v>
       </c>
       <c r="E92">
-        <v>265.63</v>
+        <v>270.7470000000001</v>
       </c>
       <c r="F92">
-        <v>460.53</v>
+        <v>465.647</v>
       </c>
       <c r="G92">
         <v>76.7</v>
@@ -8831,37 +8831,37 @@
         <v>30.95</v>
       </c>
       <c r="M92">
-        <v>108.592974</v>
+        <v>109.7995626</v>
       </c>
       <c r="N92">
-        <v>-77.64297400000001</v>
+        <v>-78.84956260000001</v>
       </c>
       <c r="O92">
-        <v>-24.84575168</v>
+        <v>-25.231860032</v>
       </c>
       <c r="P92">
-        <v>-52.79722232</v>
+        <v>-53.61770256800001</v>
       </c>
       <c r="Q92">
-        <v>-35.49722232000001</v>
+        <v>-36.31770256800002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5726377069077093</v>
+        <v>0.6311752298974549</v>
       </c>
       <c r="T92">
-        <v>6.866461439822551</v>
+        <v>7.629401599802835</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09120295388539593</v>
+        <v>0.09020072362291905</v>
       </c>
       <c r="W92">
-        <v>0.2142943434738236</v>
+        <v>0.2145306693697157</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2850092308918623</v>
+        <v>0.2818772613216221</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2520286798172122</v>
+        <v>0.2539286798172122</v>
       </c>
       <c r="C93">
-        <v>-274.3126108290292</v>
+        <v>-280.4761044675615</v>
       </c>
       <c r="D93">
-        <v>114.6343891709708</v>
+        <v>113.5878955324385</v>
       </c>
       <c r="E93">
-        <v>270.7470000000001</v>
+        <v>275.864</v>
       </c>
       <c r="F93">
-        <v>465.647</v>
+        <v>470.7640000000001</v>
       </c>
       <c r="G93">
         <v>76.7</v>
@@ -8913,37 +8913,37 @@
         <v>30.95</v>
       </c>
       <c r="M93">
-        <v>109.7995626</v>
+        <v>111.0061512</v>
       </c>
       <c r="N93">
-        <v>-78.84956260000001</v>
+        <v>-80.05615120000002</v>
       </c>
       <c r="O93">
-        <v>-25.231860032</v>
+        <v>-25.617968384</v>
       </c>
       <c r="P93">
-        <v>-53.61770256800001</v>
+        <v>-54.43818281600001</v>
       </c>
       <c r="Q93">
-        <v>-36.31770256800002</v>
+        <v>-37.13818281600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6311752298974549</v>
+        <v>0.704347133634637</v>
       </c>
       <c r="T93">
-        <v>7.629401599802835</v>
+        <v>8.583076799778192</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09020072362291905</v>
+        <v>0.08922028097484384</v>
       </c>
       <c r="W93">
-        <v>0.2145306693697157</v>
+        <v>0.2147618577461319</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2818772613216221</v>
+        <v>0.2788133780463871</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2539286798172122</v>
+        <v>0.2558286798172122</v>
       </c>
       <c r="C94">
-        <v>-280.4761044675615</v>
+        <v>-286.6206641403617</v>
       </c>
       <c r="D94">
-        <v>113.5878955324385</v>
+        <v>112.5603358596383</v>
       </c>
       <c r="E94">
-        <v>275.864</v>
+        <v>280.9810000000001</v>
       </c>
       <c r="F94">
-        <v>470.7640000000001</v>
+        <v>475.8810000000001</v>
       </c>
       <c r="G94">
         <v>76.7</v>
@@ -8995,37 +8995,37 @@
         <v>30.95</v>
       </c>
       <c r="M94">
-        <v>111.0061512</v>
+        <v>112.2127398</v>
       </c>
       <c r="N94">
-        <v>-80.05615120000002</v>
+        <v>-81.26273980000002</v>
       </c>
       <c r="O94">
-        <v>-25.617968384</v>
+        <v>-26.00407673600001</v>
       </c>
       <c r="P94">
-        <v>-54.43818281600001</v>
+        <v>-55.25866306400002</v>
       </c>
       <c r="Q94">
-        <v>-37.13818281600001</v>
+        <v>-37.95866306400002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.704347133634637</v>
+        <v>0.7984252955824422</v>
       </c>
       <c r="T94">
-        <v>8.583076799778192</v>
+        <v>9.809230628317934</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08922028097484384</v>
+        <v>0.08826092311489929</v>
       </c>
       <c r="W94">
-        <v>0.2147618577461319</v>
+        <v>0.2149880743295068</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2788133780463871</v>
+        <v>0.2758153847340603</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2558286798172122</v>
+        <v>0.2577286798172122</v>
       </c>
       <c r="C95">
-        <v>-286.6206641403617</v>
+        <v>-292.7467990923548</v>
       </c>
       <c r="D95">
-        <v>112.5603358596383</v>
+        <v>111.5512009076452</v>
       </c>
       <c r="E95">
-        <v>280.9810000000001</v>
+        <v>286.0980000000001</v>
       </c>
       <c r="F95">
-        <v>475.8810000000001</v>
+        <v>480.998</v>
       </c>
       <c r="G95">
         <v>76.7</v>
@@ -9077,37 +9077,37 @@
         <v>30.95</v>
       </c>
       <c r="M95">
-        <v>112.2127398</v>
+        <v>113.4193284</v>
       </c>
       <c r="N95">
-        <v>-81.26273980000002</v>
+        <v>-82.46932840000001</v>
       </c>
       <c r="O95">
-        <v>-26.00407673600001</v>
+        <v>-26.390185088</v>
       </c>
       <c r="P95">
-        <v>-55.25866306400002</v>
+        <v>-56.07914331200001</v>
       </c>
       <c r="Q95">
-        <v>-37.95866306400002</v>
+        <v>-38.779143312</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7984252955824422</v>
+        <v>0.923862844846183</v>
       </c>
       <c r="T95">
-        <v>9.809230628317934</v>
+        <v>11.44410239970426</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08826092311489929</v>
+        <v>0.08732197712431525</v>
       </c>
       <c r="W95">
-        <v>0.2149880743295068</v>
+        <v>0.2152094777940865</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2758153847340603</v>
+        <v>0.2728811785134851</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2577286798172122</v>
+        <v>0.2596286798172122</v>
       </c>
       <c r="C96">
-        <v>-292.7467990923548</v>
+        <v>-298.8550004686422</v>
       </c>
       <c r="D96">
-        <v>111.5512009076452</v>
+        <v>110.5599995313578</v>
       </c>
       <c r="E96">
-        <v>286.0980000000001</v>
+        <v>291.215</v>
       </c>
       <c r="F96">
-        <v>480.998</v>
+        <v>486.1150000000001</v>
       </c>
       <c r="G96">
         <v>76.7</v>
@@ -9159,37 +9159,37 @@
         <v>30.95</v>
       </c>
       <c r="M96">
-        <v>113.4193284</v>
+        <v>114.625917</v>
       </c>
       <c r="N96">
-        <v>-82.46932840000001</v>
+        <v>-83.67591700000001</v>
       </c>
       <c r="O96">
-        <v>-26.390185088</v>
+        <v>-26.77629344</v>
       </c>
       <c r="P96">
-        <v>-56.07914331200001</v>
+        <v>-56.89962356000001</v>
       </c>
       <c r="Q96">
-        <v>-38.779143312</v>
+        <v>-39.59962356000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.923862844846183</v>
+        <v>1.09947541381542</v>
       </c>
       <c r="T96">
-        <v>11.44410239970426</v>
+        <v>13.73292287964512</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08732197712431525</v>
+        <v>0.08640279841774351</v>
       </c>
       <c r="W96">
-        <v>0.2152094777940865</v>
+        <v>0.2154262201330961</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2728811785134851</v>
+        <v>0.2700087450554485</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2596286798172122</v>
+        <v>0.2615286798172122</v>
       </c>
       <c r="C97">
-        <v>-298.8550004686422</v>
+        <v>-304.9457421115595</v>
       </c>
       <c r="D97">
-        <v>110.5599995313578</v>
+        <v>109.5862578884406</v>
       </c>
       <c r="E97">
-        <v>291.215</v>
+        <v>296.3320000000001</v>
       </c>
       <c r="F97">
-        <v>486.1150000000001</v>
+        <v>491.2320000000001</v>
       </c>
       <c r="G97">
         <v>76.7</v>
@@ -9241,37 +9241,37 @@
         <v>30.95</v>
       </c>
       <c r="M97">
-        <v>114.625917</v>
+        <v>115.8325056</v>
       </c>
       <c r="N97">
-        <v>-83.67591700000001</v>
+        <v>-84.88250560000002</v>
       </c>
       <c r="O97">
-        <v>-26.77629344</v>
+        <v>-27.162401792</v>
       </c>
       <c r="P97">
-        <v>-56.89962356000001</v>
+        <v>-57.72010380800001</v>
       </c>
       <c r="Q97">
-        <v>-39.59962356000001</v>
+        <v>-40.42010380800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.09947541381542</v>
+        <v>1.362894267269275</v>
       </c>
       <c r="T97">
-        <v>13.73292287964512</v>
+        <v>17.1661535995564</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08640279841774351</v>
+        <v>0.08550276926755868</v>
       </c>
       <c r="W97">
-        <v>0.2154262201330961</v>
+        <v>0.2156384470067097</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2700087450554485</v>
+        <v>0.2671961539611208</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2615286798172122</v>
+        <v>0.2634286798172122</v>
       </c>
       <c r="C98">
-        <v>-304.9457421115594</v>
+        <v>-311.0194813159828</v>
       </c>
       <c r="D98">
-        <v>109.5862578884406</v>
+        <v>108.6295186840172</v>
       </c>
       <c r="E98">
-        <v>296.332</v>
+        <v>301.4490000000001</v>
       </c>
       <c r="F98">
-        <v>491.232</v>
+        <v>496.349</v>
       </c>
       <c r="G98">
         <v>76.7</v>
@@ -9323,37 +9323,37 @@
         <v>30.95</v>
       </c>
       <c r="M98">
-        <v>115.8325056</v>
+        <v>117.0390942</v>
       </c>
       <c r="N98">
-        <v>-84.8825056</v>
+        <v>-86.08909420000002</v>
       </c>
       <c r="O98">
-        <v>-27.162401792</v>
+        <v>-27.54851014400001</v>
       </c>
       <c r="P98">
-        <v>-57.720103808</v>
+        <v>-58.54058405600001</v>
       </c>
       <c r="Q98">
-        <v>-40.42010380800001</v>
+        <v>-41.24058405600002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.362894267269272</v>
+        <v>1.801925689692363</v>
       </c>
       <c r="T98">
-        <v>17.16615359955636</v>
+        <v>22.88820479940848</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08550276926755869</v>
+        <v>0.08462129741943951</v>
       </c>
       <c r="W98">
-        <v>0.2156384470067097</v>
+        <v>0.2158462980684962</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.267196153961121</v>
+        <v>0.2644415544357485</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2634286798172122</v>
+        <v>0.2653286798172122</v>
       </c>
       <c r="C99">
-        <v>-311.0194813159828</v>
+        <v>-317.0766595454127</v>
       </c>
       <c r="D99">
-        <v>108.6295186840172</v>
+        <v>107.6893404545873</v>
       </c>
       <c r="E99">
-        <v>301.4490000000001</v>
+        <v>306.566</v>
       </c>
       <c r="F99">
-        <v>496.349</v>
+        <v>501.466</v>
       </c>
       <c r="G99">
         <v>76.7</v>
@@ -9405,37 +9405,37 @@
         <v>30.95</v>
       </c>
       <c r="M99">
-        <v>117.0390942</v>
+        <v>118.2456828</v>
       </c>
       <c r="N99">
-        <v>-86.08909420000002</v>
+        <v>-87.29568280000001</v>
       </c>
       <c r="O99">
-        <v>-27.54851014400001</v>
+        <v>-27.934618496</v>
       </c>
       <c r="P99">
-        <v>-58.54058405600001</v>
+        <v>-59.36106430400001</v>
       </c>
       <c r="Q99">
-        <v>-41.24058405600002</v>
+        <v>-42.06106430400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.801925689692363</v>
+        <v>2.679988534538544</v>
       </c>
       <c r="T99">
-        <v>22.88820479940848</v>
+        <v>34.33230719911272</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08462129741943951</v>
+        <v>0.08375781479271055</v>
       </c>
       <c r="W99">
-        <v>0.2158462980684962</v>
+        <v>0.2160499072718789</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2644415544357485</v>
+        <v>0.2617431712272205</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2653286798172122</v>
+        <v>0.2672286798172122</v>
       </c>
       <c r="C100">
-        <v>-317.0766595454127</v>
+        <v>-323.1177031111903</v>
       </c>
       <c r="D100">
-        <v>107.6893404545873</v>
+        <v>106.7652968888097</v>
       </c>
       <c r="E100">
-        <v>306.566</v>
+        <v>311.683</v>
       </c>
       <c r="F100">
-        <v>501.466</v>
+        <v>506.583</v>
       </c>
       <c r="G100">
         <v>76.7</v>
@@ -9487,37 +9487,37 @@
         <v>30.95</v>
       </c>
       <c r="M100">
-        <v>118.2456828</v>
+        <v>119.4522714</v>
       </c>
       <c r="N100">
-        <v>-87.29568280000001</v>
+        <v>-88.50227140000001</v>
       </c>
       <c r="O100">
-        <v>-27.934618496</v>
+        <v>-28.320726848</v>
       </c>
       <c r="P100">
-        <v>-59.36106430400001</v>
+        <v>-60.18154455200001</v>
       </c>
       <c r="Q100">
-        <v>-42.06106430400001</v>
+        <v>-42.88154455200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.679988534538544</v>
+        <v>5.314177069077089</v>
       </c>
       <c r="T100">
-        <v>34.33230719911272</v>
+        <v>68.66461439822544</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08375781479271055</v>
+        <v>0.08291177625945084</v>
       </c>
       <c r="W100">
-        <v>0.2160499072718789</v>
+        <v>0.2162494031580215</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2617431712272205</v>
+        <v>0.2590993008107839</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2672286798172122</v>
-      </c>
-      <c r="C101">
-        <v>-323.1177031111903</v>
-      </c>
-      <c r="D101">
-        <v>106.7652968888097</v>
-      </c>
-      <c r="E101">
-        <v>311.683</v>
-      </c>
-      <c r="F101">
-        <v>506.583</v>
-      </c>
-      <c r="G101">
-        <v>76.7</v>
-      </c>
-      <c r="H101">
-        <v>316.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>48.25</v>
-      </c>
-      <c r="K101">
-        <v>17.3</v>
-      </c>
-      <c r="L101">
-        <v>30.95</v>
-      </c>
-      <c r="M101">
-        <v>119.4522714</v>
-      </c>
-      <c r="N101">
-        <v>-88.50227140000001</v>
-      </c>
-      <c r="O101">
-        <v>-28.320726848</v>
-      </c>
-      <c r="P101">
-        <v>-60.18154455200001</v>
-      </c>
-      <c r="Q101">
-        <v>-42.88154455200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.314177069077089</v>
-      </c>
-      <c r="T101">
-        <v>68.66461439822544</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08291177625945084</v>
-      </c>
-      <c r="W101">
-        <v>0.2162494031580215</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2590993008107839</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
